--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4301</v>
+        <v>4302</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>4356</v>
+        <v>3985</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>93995</v>
+        <v>94018</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23064</v>
+        <v>23070</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23448</v>
+        <v>23582</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>23064</v>
+        <v>23070</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>46128</v>
+        <v>46139</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>41544</v>
+        <v>41555</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>83030</v>
+        <v>83051</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -916,20 +916,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>123008</v>
+        <v>123038</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>138384</v>
+        <v>138418</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>246015</v>
+        <v>246077</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>345959</v>
+        <v>346045</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>345959</v>
+        <v>346045</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>691918</v>
+        <v>692090</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1002,18 +1002,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5909</v>
+        <v>5826</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5741</v>
+        <v>5773</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6126</v>
+        <v>6123</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8457</v>
+        <v>8459</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>123</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8698</v>
+        <v>9720</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8267</v>
+        <v>8301</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1098,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8262</v>
+        <v>9625</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>146032</v>
+        <v>146068</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>16914</v>
+        <v>16918</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13531</v>
+        <v>13534</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13531</v>
+        <v>13534</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1162,20 +1162,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13531</v>
+        <v>13534</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>41283</v>
+        <v>41293</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>33827</v>
+        <v>33836</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1216,20 +1216,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>21589</v>
+        <v>21595</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>38440</v>
+        <v>38449</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>21526</v>
+        <v>21532</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1270,20 +1270,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>91362</v>
+        <v>91385</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>91362</v>
+        <v>91385</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>21526</v>
+        <v>21532</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1324,20 +1324,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>261238</v>
+        <v>261303</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1378,20 +1378,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>33330</v>
+        <v>33339</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>62290</v>
+        <v>62305</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5228</v>
+        <v>5229</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14198</v>
+        <v>14202</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14198</v>
+        <v>14202</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1442,20 +1442,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>21912</v>
+        <v>21918</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>62290</v>
+        <v>62305</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5228</v>
+        <v>5229</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
         <v>769</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1538</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1573,17 +1573,17 @@
         <v>1538</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>221428</v>
+        <v>221483</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1624,20 +1624,20 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>261391</v>
+        <v>261456</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5535</v>
+        <v>5537</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5535</v>
+        <v>5537</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1688,20 +1688,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5535</v>
+        <v>5537</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>21526</v>
+        <v>21532</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11071</v>
+        <v>11073</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>10763</v>
+        <v>10766</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10763</v>
+        <v>10766</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1752,20 +1752,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>10763</v>
+        <v>10766</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>35934</v>
+        <v>35943</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>21526</v>
+        <v>21532</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1806,20 +1806,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>20758</v>
+        <v>20763</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>135724</v>
+        <v>135757</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1860,20 +1860,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>38440</v>
+        <v>38449</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>312649</v>
+        <v>312726</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>76880</v>
+        <v>76899</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1925,20 +1925,20 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1759</v>
+        <v>1739</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1989,20 +1989,20 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>308</v>
+        <v>1067</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2046,17 +2046,17 @@
         <v>1230</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>26</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2075,18 +2075,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1142</v>
+        <v>769</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1067</v>
+        <v>1001</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2107,20 +2107,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1056</v>
+        <v>1323</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1533512</v>
+        <v>1533894</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1538</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2139,18 +2139,18 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1841</v>
+        <v>1867</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2171,20 +2171,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1841</v>
+        <v>2418</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2235,20 +2235,20 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>16566</v>
+        <v>16570</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>46</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
         <v>615</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1230</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2353,20 +2353,20 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11217</v>
+        <v>11220</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="O31" s="2" t="n">
         <v>63</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2385,18 +2385,18 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1126</v>
+        <v>1458</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>990</v>
+        <v>1042</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2417,20 +2417,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>615038</v>
+        <v>615191</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1538</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>9</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2484,17 +2484,17 @@
         <v>2159</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12456</v>
+        <v>12459</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O33" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2513,18 +2513,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3490</v>
+        <v>3487</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3429</v>
+        <v>3442</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2545,20 +2545,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3693</v>
+        <v>3076</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>20553</v>
+        <v>20558</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O34" s="2" t="n">
         <v>56</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>29720</v>
+        <v>29728</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
         <v>769</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6106</v>
+        <v>6107</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1538</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2732,17 +2732,17 @@
         <v>2382</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O37" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2761,18 +2761,18 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3506</v>
+        <v>3756</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3161</v>
+        <v>3261</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2789,20 +2789,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3755</v>
+        <v>3110</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>307519</v>
+        <v>307596</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2853,20 +2853,20 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>140762</v>
+        <v>140797</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>47</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2907,20 +2907,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4720</v>
+        <v>4722</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>16915</v>
+        <v>16919</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2939,18 +2939,18 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2971,20 +2971,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>14710</v>
+        <v>14714</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3031,20 +3031,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>4371</v>
+        <v>3499</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>5955</v>
+        <v>5957</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3063,18 +3063,18 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>7099</v>
+        <v>7199</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6371</v>
+        <v>6538</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3091,20 +3091,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>7165</v>
+        <v>7530</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8641</v>
+        <v>8643</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>7301</v>
+        <v>7610</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>11266</v>
+        <v>11269</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9893</v>
+        <v>9983</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3151,20 +3151,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>11094</v>
+        <v>10990</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>13389</v>
+        <v>13393</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>12109</v>
+        <v>12156</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3208,17 +3208,17 @@
         <v>1538</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8477</v>
+        <v>8479</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3269,20 +3269,20 @@
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="L47" s="3" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>5711</v>
+        <v>5712</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>769</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
         <v>935</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1538</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3444,17 +3444,17 @@
         <v>1121</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O49" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3501,10 +3501,10 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>4032</v>
+        <v>4033</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>769</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3551,10 +3551,10 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4242</v>
+        <v>4243</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1538</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>7073</v>
+        <v>7075</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>4</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>5580</v>
+        <v>5581</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3611,20 +3611,20 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6458</v>
+        <v>6460</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>7357</v>
+        <v>7782</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
         <v>761</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4688</v>
+        <v>4689</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>769</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
         <v>2</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3729,20 +3729,20 @@
         </is>
       </c>
       <c r="L54" s="3" t="n">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>10980</v>
+        <v>10983</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="O54" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3796,17 +3796,17 @@
         <v>3340</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>29742</v>
+        <v>29749</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O55" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>8220</v>
+        <v>8222</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>6</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>6064</v>
+        <v>6065</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3856,15 +3856,21 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L56" s="3" t="inlineStr"/>
-      <c r="M56" s="3" t="inlineStr"/>
+      <c r="L56" s="3" t="n">
+        <v>8533</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>8533</v>
+      </c>
       <c r="N56" s="3" t="n">
-        <v>6722</v>
-      </c>
-      <c r="O56" s="2" t="inlineStr"/>
+        <v>6724</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3883,18 +3889,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>14054</v>
+        <v>9236</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9634</v>
+        <v>9763</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3915,20 +3921,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>13220</v>
+        <v>9722</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>29780</v>
+        <v>29788</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12301</v>
+        <v>12338</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3947,18 +3953,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3775</v>
+        <v>3802</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3723</v>
+        <v>3717</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3979,20 +3985,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3576</v>
+        <v>3956</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10037</v>
+        <v>10040</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3945</v>
+        <v>3903</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4028,7 @@
         <v>4</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4043,20 +4049,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>4082</v>
+        <v>4143</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>2575</v>
+        <v>2507</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4103,7 @@
         </is>
       </c>
       <c r="L60" s="3" t="n">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="M60" s="3" t="n">
         <v>2768</v>
@@ -4110,7 +4116,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4151,20 +4157,20 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4213,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9533</v>
+        <v>9535</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4237,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -4242,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4263,20 +4269,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4325,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4373,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4413,20 +4419,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>49203</v>
+        <v>49215</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4467,20 +4473,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>21526</v>
+        <v>21532</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4523,12 +4529,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>21526</v>
+        <v>21532</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4572,17 +4578,17 @@
         <v>308</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3601</v>
+        <v>3602</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>1538</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4632,17 @@
         <v>615</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>4897</v>
+        <v>4898</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O70" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4677,20 +4683,20 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4079</v>
+        <v>4080</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>4890</v>
+        <v>4891</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4715,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -4720,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4741,20 +4747,20 @@
         </is>
       </c>
       <c r="L72" s="3" t="n">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1442330</v>
+        <v>1442688</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11071</v>
+        <v>11073</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4795,20 +4801,20 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4620</v>
+        <v>4622</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7268</v>
+        <v>7270</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4849,20 +4855,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8457</v>
+        <v>8459</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20372</v>
+        <v>20377</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>16914</v>
+        <v>16918</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4903,20 +4909,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>16914</v>
+        <v>16918</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>26296</v>
+        <v>26303</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4976,7 @@
         <v>292</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6197</v>
+        <v>6198</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>308</v>
@@ -4980,7 +4986,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5030,7 @@
         <v>1153</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5042</v>
+        <v>5043</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>615</v>
@@ -5034,7 +5040,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5094,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5129,20 +5135,20 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5535</v>
+        <v>5537</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5535</v>
+        <v>5537</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5191,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5231,20 +5237,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>22489</v>
+        <v>22494</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>22489</v>
+        <v>22494</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>9841</v>
+        <v>9843</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5293,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>19681</v>
+        <v>19686</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5342,17 +5348,17 @@
         <v>154</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1537442</v>
+        <v>1537825</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>769</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5402,17 +5408,17 @@
         <v>707</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>33612</v>
+        <v>33620</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1538</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5452,17 +5458,17 @@
         <v>1947</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O85" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5502,17 +5508,17 @@
         <v>1230</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5551,12 +5557,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>9841</v>
+        <v>9843</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5595,12 +5601,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>13838</v>
+        <v>13842</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5645,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>16914</v>
+        <v>16918</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5700,7 @@
         <v>486</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>83565</v>
+        <v>83586</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>769</v>
@@ -5704,7 +5710,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5750,7 @@
         <v>769</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5111</v>
+        <v>5112</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1538</v>
@@ -5754,7 +5760,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5791,20 +5797,20 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5849,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5887,12 +5893,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>9841</v>
+        <v>9843</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5931,12 +5937,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>13838</v>
+        <v>13842</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -5975,12 +5981,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>16914</v>
+        <v>16918</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6030,7 @@
         <v>1556</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="N97" s="3" t="n">
         <v>2768</v>
@@ -6034,7 +6040,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6081,14 +6087,14 @@
         <v>1999</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6129,20 +6135,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>4587</v>
+        <v>4588</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5033</v>
+        <v>5034</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9533</v>
+        <v>9535</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6183,20 +6189,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6245,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6285,20 +6291,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>17469</v>
+        <v>17473</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>17469</v>
+        <v>17473</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6347,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>49203</v>
+        <v>49215</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6387,10 +6393,10 @@
         </is>
       </c>
       <c r="L104" s="3" t="n">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="N104" s="3" t="n">
         <v>2768</v>
@@ -6400,7 +6406,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6443,12 +6449,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6491,12 +6497,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9533</v>
+        <v>9535</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6521,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -6526,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -6549,12 +6555,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6597,12 +6603,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6651,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6693,12 +6699,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>49203</v>
+        <v>49215</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6741,12 +6747,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>76880</v>
+        <v>76899</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6787,20 +6793,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>84568</v>
+        <v>84589</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>94399</v>
+        <v>94423</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>107632</v>
+        <v>107658</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6841,20 +6847,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>107632</v>
+        <v>107658</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>107632</v>
+        <v>107658</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>138384</v>
+        <v>138418</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6895,20 +6901,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>123008</v>
+        <v>123038</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>123008</v>
+        <v>123038</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6949,20 +6955,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>184512</v>
+        <v>184557</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7003,20 +7009,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>207575</v>
+        <v>207627</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>246015</v>
+        <v>246077</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>246015</v>
+        <v>246077</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7066,7 @@
         <v>1639</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="N117" s="3" t="n">
         <v>2153</v>
@@ -7070,7 +7076,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7111,20 +7117,20 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3687</v>
+        <v>3688</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>5686</v>
+        <v>5687</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7167,12 +7173,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7213,20 +7219,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>13838</v>
+        <v>13842</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>13838</v>
+        <v>13842</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7269,12 +7275,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22141</v>
+        <v>22147</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7315,20 +7321,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7369,20 +7375,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>39919</v>
+        <v>39929</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7423,10 +7429,10 @@
         </is>
       </c>
       <c r="L124" s="3" t="n">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>2153</v>
@@ -7436,7 +7442,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7477,20 +7483,20 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5522</v>
+        <v>5523</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7531,20 +7537,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6280</v>
+        <v>6281</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6280</v>
+        <v>6281</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7585,20 +7591,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11552</v>
+        <v>11555</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>13838</v>
+        <v>13842</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7641,12 +7647,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22141</v>
+        <v>22147</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7689,12 +7695,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7737,12 +7743,12 @@
       <c r="L130" s="3" t="inlineStr"/>
       <c r="M130" s="3" t="inlineStr"/>
       <c r="N130" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7783,20 +7789,20 @@
         </is>
       </c>
       <c r="L131" s="3" t="n">
-        <v>4785</v>
+        <v>4786</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>4785</v>
+        <v>4786</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O131" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7837,20 +7843,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7891,20 +7897,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15461</v>
+        <v>15464</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7947,12 +7953,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>27677</v>
+        <v>27684</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7993,20 +7999,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>20758</v>
+        <v>20763</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>20758</v>
+        <v>20763</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>46128</v>
+        <v>46139</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8031,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>27677</v>
+        <v>27684</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8036,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>27677</v>
+        <v>27684</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8057,20 +8063,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>27677</v>
+        <v>27684</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>27677</v>
+        <v>27684</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>69192</v>
+        <v>69209</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8111,20 +8117,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8143,18 +8149,18 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
         <v>12</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6228</v>
+        <v>6227</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8175,20 +8181,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12388</v>
+        <v>12391</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O138" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8238,7 @@
         <v>1024</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="N139" s="3" t="n">
         <v>308</v>
@@ -8242,7 +8248,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8302,7 @@
         <v>564</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5020</v>
+        <v>5021</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>317</v>
@@ -8306,7 +8312,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8366,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8420,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8455,20 +8461,20 @@
         </is>
       </c>
       <c r="L143" s="3" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O143" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8519,20 +8525,20 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>2060</v>
+        <v>1999</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10437</v>
+        <v>10440</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="O144" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8581,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8621,20 +8627,20 @@
         </is>
       </c>
       <c r="L146" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>51998</v>
+        <v>52011</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8677,12 +8683,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8707,7 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
@@ -8712,7 +8718,7 @@
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -8733,20 +8739,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>16849</v>
+        <v>16853</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8795,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8813,18 +8819,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>17928</v>
+        <v>17499</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15582</v>
+        <v>15652</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8845,20 +8851,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>17496</v>
+        <v>17490</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>38440</v>
+        <v>38449</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8883,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8885,10 +8891,10 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8909,20 +8915,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>81708</v>
+        <v>81728</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>73805</v>
+        <v>73823</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8947,7 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>99944</v>
+        <v>99969</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -8952,7 +8958,7 @@
         <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>99944</v>
+        <v>99969</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -8973,20 +8979,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>99944</v>
+        <v>99969</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>99944</v>
+        <v>99969</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>199887</v>
+        <v>199937</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9046,7 @@
         <v>154</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10059</v>
+        <v>10061</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>308</v>
@@ -9050,7 +9056,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9120,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9164,17 +9170,17 @@
         <v>769</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15065</v>
+        <v>15069</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1538</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9221,20 +9227,20 @@
       </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="3" t="n">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O156" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9271,20 +9277,20 @@
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9334,7 @@
         <v>769</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1538</v>
@@ -9338,7 +9344,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9392,17 +9398,17 @@
         <v>1538</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>18646</v>
+        <v>18651</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O159" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9427,7 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
@@ -9432,7 +9438,7 @@
         <v>1</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -9453,20 +9459,20 @@
         </is>
       </c>
       <c r="L160" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6432</v>
+        <v>6433</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9526,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9580,7 @@
         <v>1744</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>29337</v>
+        <v>29345</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1538</v>
@@ -9584,7 +9590,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9603,18 +9609,18 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>2611</v>
+        <v>3562</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F163" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>3177</v>
+        <v>3146</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -9635,20 +9641,20 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3561</v>
+        <v>3691</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3075</v>
+        <v>3917</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9667,18 +9673,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3644</v>
+        <v>4168</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3873</v>
+        <v>3897</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9699,20 +9705,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>4225</v>
+        <v>4317</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>9994</v>
+        <v>9997</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9731,18 +9737,18 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -9763,20 +9769,20 @@
         </is>
       </c>
       <c r="L165" s="3" t="n">
-        <v>186</v>
+        <v>277</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9827,10 +9833,10 @@
         </is>
       </c>
       <c r="L166" s="3" t="n">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="M166" s="3" t="n">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="N166" s="3" t="n">
         <v>615</v>
@@ -9840,7 +9846,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9859,18 +9865,18 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>1470</v>
+        <v>680</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1292</v>
+        <v>1216</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -9894,17 +9900,17 @@
         <v>1538</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9450</v>
+        <v>9452</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>1568</v>
+        <v>1295</v>
       </c>
       <c r="O167" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9954,7 @@
         <v>1538</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5243</v>
+        <v>5245</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>308</v>
@@ -9958,7 +9964,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10008,7 @@
         <v>303</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>308</v>
@@ -10012,7 +10018,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10053,20 +10059,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>92256</v>
+        <v>92279</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>92256</v>
+        <v>92279</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>123008</v>
+        <v>123038</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10109,12 +10115,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10170,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10211,20 +10217,20 @@
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="3" t="n">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10263,12 +10269,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10305,20 +10311,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>13809</v>
+        <v>13813</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>13838</v>
+        <v>13842</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10355,20 +10361,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11071</v>
+        <v>11073</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11071</v>
+        <v>11073</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22141</v>
+        <v>22147</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10405,20 +10411,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>15453</v>
+        <v>15457</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10461,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>18605</v>
+        <v>18610</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10511,12 +10517,12 @@
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10557,20 +10563,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10613,12 +10619,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10659,20 +10665,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10715,12 +10721,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>27677</v>
+        <v>27684</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10761,20 +10767,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>20758</v>
+        <v>20763</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>20758</v>
+        <v>20763</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>41515</v>
+        <v>41525</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10815,20 +10821,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>27677</v>
+        <v>27684</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>27677</v>
+        <v>27684</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>55353</v>
+        <v>55367</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10878,7 @@
         <v>154</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>308</v>
@@ -10882,7 +10888,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10932,7 @@
         <v>154</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>308</v>
@@ -10936,7 +10942,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10986,7 @@
         <v>154</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>100039</v>
+        <v>100064</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>308</v>
@@ -10990,7 +10996,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11044,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11098,7 @@
         <v>154</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>28359</v>
+        <v>28366</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>308</v>
@@ -11102,7 +11108,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11152,7 @@
         <v>154</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>151811</v>
+        <v>151849</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>308</v>
@@ -11156,7 +11162,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11216,7 @@
         <v>154</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>308</v>
@@ -11220,7 +11226,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11274,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11312,17 +11318,17 @@
         <v>154</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11376,17 +11382,17 @@
         <v>154</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11440,17 +11446,17 @@
         <v>154</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11504,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11549,20 +11555,20 @@
         </is>
       </c>
       <c r="L198" s="3" t="n">
-        <v>1230</v>
+        <v>784</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11603,20 +11609,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20023</v>
+        <v>20028</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20023</v>
+        <v>20028</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11641,7 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
@@ -11646,7 +11652,7 @@
         <v>2</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -11667,20 +11673,20 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>5998</v>
+        <v>6000</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6130</v>
+        <v>6132</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11705,7 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -11710,7 +11716,7 @@
         <v>1</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -11731,20 +11737,20 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10476</v>
+        <v>10478</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7380</v>
+        <v>7382</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11785,20 +11791,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10062</v>
+        <v>10065</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>9841</v>
+        <v>9843</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11839,20 +11845,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>7995</v>
+        <v>7997</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>268418</v>
+        <v>268485</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>13531</v>
+        <v>13534</v>
       </c>
       <c r="O203" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11893,20 +11899,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15193</v>
+        <v>15197</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>15594</v>
+        <v>15598</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11924,13 +11930,23 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D205" s="3" t="inlineStr"/>
-      <c r="E205" s="2" t="inlineStr"/>
-      <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="3" t="inlineStr"/>
+      <c r="D205" s="3" t="n">
+        <v>19686</v>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>19686</v>
+      </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I205" s="2" t="n">
@@ -11947,20 +11963,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>19681</v>
+        <v>36584</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>47433</v>
+        <v>47445</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="O205" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12003,12 +12019,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22141</v>
+        <v>22147</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12026,23 +12042,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D207" s="3" t="n">
-        <v>498</v>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" s="3" t="n">
-        <v>498</v>
-      </c>
+      <c r="D207" s="3" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="3" t="inlineStr"/>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I207" s="2" t="n">
@@ -12072,7 +12078,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12132,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12167,10 +12173,10 @@
         </is>
       </c>
       <c r="L209" s="3" t="n">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="M209" s="3" t="n">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="N209" s="3" t="n">
         <v>2153</v>
@@ -12180,7 +12186,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12224,17 +12230,17 @@
         <v>1999</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4347</v>
+        <v>4348</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>3998</v>
+        <v>3999</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12275,20 +12281,20 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12329,20 +12335,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>6995</v>
+        <v>6921</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>13838</v>
+        <v>13842</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12385,12 +12391,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22141</v>
+        <v>22147</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12431,20 +12437,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12485,10 +12491,10 @@
         </is>
       </c>
       <c r="L215" s="3" t="n">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="M215" s="3" t="n">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="N215" s="3" t="n">
         <v>2153</v>
@@ -12498,7 +12504,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12542,17 +12548,17 @@
         <v>1999</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11546</v>
+        <v>11549</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>3998</v>
+        <v>3999</v>
       </c>
       <c r="O216" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12570,23 +12576,13 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D217" s="3" t="n">
-        <v>13531</v>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="F217" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G217" s="3" t="n">
-        <v>13531</v>
-      </c>
+      <c r="D217" s="3" t="inlineStr"/>
+      <c r="E217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="3" t="inlineStr"/>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I217" s="2" t="n">
@@ -12603,20 +12599,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15139</v>
+        <v>15143</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>36426</v>
+        <v>36435</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12657,20 +12653,20 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>5641</v>
+        <v>5643</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12711,20 +12707,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>13838</v>
+        <v>13842</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12767,12 +12763,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12813,20 +12809,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12886,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12909,11 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G223" s="3" t="n">
         <v>1538</v>
@@ -12944,17 +12940,17 @@
         <v>1538</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>3935</v>
+        <v>3936</v>
       </c>
       <c r="N223" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -12973,7 +12969,7 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
@@ -12984,7 +12980,7 @@
         <v>1</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -13005,20 +13001,20 @@
         </is>
       </c>
       <c r="L224" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>6998</v>
+        <v>6999</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13044,7 @@
         <v>2</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -13069,10 +13065,10 @@
         </is>
       </c>
       <c r="L225" s="3" t="n">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>7494</v>
+        <v>7496</v>
       </c>
       <c r="N225" s="3" t="n">
         <v>1538</v>
@@ -13082,7 +13078,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13133,20 +13129,20 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="M226" s="3" t="n">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="N226" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O226" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13165,7 +13161,7 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -13176,7 +13172,7 @@
         <v>1</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -13197,20 +13193,20 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>3676</v>
+        <v>3677</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13250,7 @@
         <v>154</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>308</v>
@@ -13264,7 +13260,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13304,7 @@
         <v>154</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>308</v>
@@ -13318,7 +13314,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13358,7 @@
         <v>154</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>308</v>
@@ -13372,7 +13368,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13412,7 @@
         <v>769</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1538</v>
@@ -13426,7 +13422,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13480,17 +13476,17 @@
         <v>1538</v>
       </c>
       <c r="M232" s="3" t="n">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="N232" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O232" s="2" t="n">
         <v>59</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13531,20 +13527,20 @@
         </is>
       </c>
       <c r="L233" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7005</v>
+        <v>7007</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>34</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13595,10 +13591,10 @@
         </is>
       </c>
       <c r="L234" s="3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M234" s="3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N234" s="3" t="n">
         <v>308</v>
@@ -13608,7 +13604,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13626,13 +13622,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D235" s="3" t="inlineStr"/>
-      <c r="E235" s="2" t="inlineStr"/>
-      <c r="F235" s="2" t="inlineStr"/>
-      <c r="G235" s="3" t="inlineStr"/>
+      <c r="D235" s="3" t="n">
+        <v>2624</v>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" s="3" t="n">
+        <v>2624</v>
+      </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I235" s="2" t="n">
@@ -13649,20 +13655,20 @@
         </is>
       </c>
       <c r="L235" s="3" t="n">
-        <v>2623</v>
+        <v>3828</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>4144</v>
+        <v>4145</v>
       </c>
       <c r="N235" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O235" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13703,20 +13709,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6341</v>
+        <v>6343</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13759,12 +13765,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13789,7 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>7093</v>
+        <v>7095</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -13794,7 +13800,7 @@
         <v>1</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>7093</v>
+        <v>7095</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -13815,20 +13821,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>10719</v>
+        <v>10721</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>7802</v>
+        <v>7804</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13871,12 +13877,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13901,7 @@
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>10185</v>
+        <v>10188</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -13906,7 +13912,7 @@
         <v>1</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>10185</v>
+        <v>10188</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -13929,12 +13935,12 @@
       <c r="L240" s="3" t="inlineStr"/>
       <c r="M240" s="3" t="inlineStr"/>
       <c r="N240" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13959,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>20259</v>
+        <v>20264</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -13964,7 +13970,7 @@
         <v>6</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>18212</v>
+        <v>18216</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -13985,20 +13991,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>21020</v>
+        <v>21026</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>29789</v>
+        <v>29797</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14039,20 +14045,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>41554</v>
+        <v>40835</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>56971</v>
+        <v>56985</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>73805</v>
+        <v>73823</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14071,18 +14077,18 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>29165</v>
+        <v>24306</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>18184</v>
+        <v>18698</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14099,20 +14105,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>26730</v>
+        <v>25278</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>30751920</v>
+        <v>30759570</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14155,12 +14161,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14201,20 +14207,20 @@
         </is>
       </c>
       <c r="L245" s="3" t="n">
-        <v>923</v>
+        <v>486</v>
       </c>
       <c r="M245" s="3" t="n">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="N245" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O245" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14233,18 +14239,18 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>2428</v>
+        <v>154</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2148</v>
+        <v>1967</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14265,20 +14271,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>2546</v>
+        <v>2072</v>
       </c>
       <c r="O246" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14303,7 @@
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
@@ -14308,7 +14314,7 @@
         <v>1</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -14329,20 +14335,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15099</v>
+        <v>15103</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>22670</v>
+        <v>22676</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17221</v>
+        <v>17225</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14367,7 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -14372,7 +14378,7 @@
         <v>2</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -14393,20 +14399,20 @@
         </is>
       </c>
       <c r="L248" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="M248" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>17221</v>
+        <v>17225</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14442,7 @@
         <v>3</v>
       </c>
       <c r="G249" s="3" t="n">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -14456,7 +14462,7 @@
         <v>769</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9027</v>
+        <v>9029</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1538</v>
@@ -14466,7 +14472,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14520,7 +14526,7 @@
       <c r="O250" s="2" t="inlineStr"/>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14570,7 @@
         <v>154</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>94548</v>
+        <v>94572</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>308</v>
@@ -14574,7 +14580,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14615,20 +14621,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>48994</v>
+        <v>49006</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>48994</v>
+        <v>49006</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14647,7 +14653,7 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>7331</v>
+        <v>7333</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
@@ -14658,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>7331</v>
+        <v>7333</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -14681,12 +14687,12 @@
       <c r="L253" s="3" t="inlineStr"/>
       <c r="M253" s="3" t="inlineStr"/>
       <c r="N253" s="3" t="n">
-        <v>7380</v>
+        <v>7382</v>
       </c>
       <c r="O253" s="2" t="inlineStr"/>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14727,20 +14733,20 @@
         </is>
       </c>
       <c r="L254" s="3" t="n">
-        <v>7643</v>
+        <v>7645</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>184512</v>
+        <v>184557</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>9841</v>
+        <v>9843</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14781,7 +14787,7 @@
         </is>
       </c>
       <c r="L255" s="3" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="M255" s="3" t="n">
         <v>1538</v>
@@ -14794,7 +14800,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14848,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14886,17 +14892,17 @@
         <v>283</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O257" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14919,7 +14925,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
@@ -14950,17 +14956,17 @@
         <v>308</v>
       </c>
       <c r="M258" s="3" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="N258" s="3" t="n">
         <v>615</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -14978,13 +14984,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D259" s="3" t="inlineStr"/>
-      <c r="E259" s="2" t="inlineStr"/>
-      <c r="F259" s="2" t="inlineStr"/>
-      <c r="G259" s="3" t="inlineStr"/>
+      <c r="D259" s="3" t="n">
+        <v>769</v>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G259" s="3" t="n">
+        <v>769</v>
+      </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I259" s="2" t="n">
@@ -15004,17 +15020,17 @@
         <v>1184</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>20793</v>
+        <v>20798</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1538</v>
       </c>
       <c r="O259" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15060,7 @@
         <v>4</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -15065,20 +15081,20 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3570</v>
+        <v>3571</v>
       </c>
       <c r="N260" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O260" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15113,7 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -15108,7 +15124,7 @@
         <v>4</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -15129,20 +15145,20 @@
         </is>
       </c>
       <c r="L261" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>6821</v>
+        <v>6822</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15161,7 +15177,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -15172,7 +15188,7 @@
         <v>15</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6245</v>
+        <v>6247</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15193,20 +15209,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15276,7 @@
         <v>769</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10268</v>
+        <v>10271</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1538</v>
@@ -15270,7 +15286,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15321,20 +15337,20 @@
         </is>
       </c>
       <c r="L264" s="3" t="n">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="M264" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="N264" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O264" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15374,21 +15390,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L265" s="3" t="n">
-        <v>4859</v>
-      </c>
-      <c r="M265" s="3" t="n">
-        <v>4859</v>
-      </c>
+      <c r="L265" s="3" t="inlineStr"/>
+      <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6150</v>
-      </c>
-      <c r="O265" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>6152</v>
+      </c>
+      <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15417,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15418,7 +15428,7 @@
         <v>2</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15439,20 +15449,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9370</v>
+        <v>9372</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15471,7 +15481,7 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -15482,7 +15492,7 @@
         <v>9</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15503,20 +15513,20 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>18911</v>
+        <v>18916</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="O267" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15535,7 +15545,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>9362</v>
+        <v>9365</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15546,7 +15556,7 @@
         <v>1</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>9362</v>
+        <v>9365</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15567,20 +15577,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>12387</v>
+        <v>12390</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>13851</v>
+        <v>13854</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>13531</v>
+        <v>13534</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15623,12 +15633,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15671,12 +15681,12 @@
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15717,20 +15727,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>22291</v>
+        <v>22296</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>22294</v>
+        <v>22299</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15774,17 +15784,17 @@
         <v>154</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O272" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15824,7 @@
         <v>2</v>
       </c>
       <c r="G273" s="3" t="n">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -15838,7 +15848,7 @@
         <v>154</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>20364</v>
+        <v>20369</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>308</v>
@@ -15848,7 +15858,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15902,7 @@
         <v>154</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>30853</v>
+        <v>30861</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>308</v>
@@ -15902,7 +15912,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15956,17 +15966,17 @@
         <v>154</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15453</v>
+        <v>15457</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O275" s="2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15993,10 +16003,10 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>1740</v>
+        <v>1949</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16020,7 +16030,7 @@
         <v>154</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>153297</v>
+        <v>153335</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>1850</v>
@@ -16030,7 +16040,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16090,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16099,7 +16109,7 @@
         </is>
       </c>
       <c r="D278" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
@@ -16110,7 +16120,7 @@
         <v>2</v>
       </c>
       <c r="G278" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -16131,20 +16141,20 @@
         </is>
       </c>
       <c r="L278" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>6685</v>
+        <v>6687</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16185,20 +16195,20 @@
         </is>
       </c>
       <c r="L279" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9621</v>
+        <v>9623</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7380</v>
+        <v>7382</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16239,20 +16249,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8368</v>
+        <v>8370</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>9841</v>
+        <v>9843</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16295,12 +16305,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>13531</v>
+        <v>13534</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16343,12 +16353,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16391,12 +16401,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16437,20 +16447,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>32290</v>
+        <v>32298</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>32785</v>
+        <v>32793</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16469,18 +16479,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>8892</v>
+        <v>8750</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>8470</v>
+        <v>8515</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16501,20 +16511,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>8844</v>
+        <v>8799</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>8730</v>
+        <v>9111</v>
       </c>
       <c r="O285" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16541,7 +16551,7 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G286" s="3" t="n">
         <v>154</v>
@@ -16568,7 +16578,7 @@
         <v>154</v>
       </c>
       <c r="M286" s="3" t="n">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="N286" s="3" t="n">
         <v>308</v>
@@ -16578,7 +16588,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16597,18 +16607,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5345</v>
+        <v>6320</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>4847</v>
+        <v>4925</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16627,12 +16637,12 @@
       <c r="L287" s="3" t="inlineStr"/>
       <c r="M287" s="3" t="inlineStr"/>
       <c r="N287" s="3" t="n">
-        <v>5640</v>
+        <v>5932</v>
       </c>
       <c r="O287" s="2" t="inlineStr"/>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16651,18 +16661,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>7645</v>
+        <v>7776</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>7109</v>
+        <v>7178</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16679,20 +16689,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7483</v>
+        <v>6869</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8452</v>
+        <v>7942</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>8034</v>
+        <v>8242</v>
       </c>
       <c r="O288" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16711,18 +16721,18 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9038</v>
+        <v>9479</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9379</v>
+        <v>9400</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16739,20 +16749,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9476</v>
+        <v>9489</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11369</v>
+        <v>11372</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>10001</v>
+        <v>10109</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16793,10 +16803,10 @@
         </is>
       </c>
       <c r="L290" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M290" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="N290" s="3" t="n">
         <v>1538</v>
@@ -16806,7 +16816,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16825,18 +16835,18 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>2420</v>
+        <v>3999</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F291" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>2933</v>
+        <v>2983</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -16857,20 +16867,20 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>3998</v>
+        <v>4265</v>
       </c>
       <c r="M291" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="N291" s="3" t="n">
-        <v>3075</v>
+        <v>3530</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16899,7 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>4605</v>
+        <v>4606</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -16897,10 +16907,10 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>3695</v>
+        <v>3756</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16921,20 +16931,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>4920</v>
+        <v>4922</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5443</v>
+        <v>5383</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16988,7 +16998,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17007,18 +17017,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>8547</v>
+        <v>8523</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
         <v>21</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>6890</v>
+        <v>7029</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17039,20 +17049,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>8165</v>
+        <v>6933</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>27492</v>
+        <v>27499</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>9774</v>
+        <v>8191</v>
       </c>
       <c r="O294" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17093,20 +17103,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>49976</v>
+        <v>49989</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>679219</v>
+        <v>679388</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>38440</v>
+        <v>38449</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17125,7 +17135,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17136,7 +17146,7 @@
         <v>4</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17157,20 +17167,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>66853</v>
+        <v>66870</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>38440</v>
+        <v>38449</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17189,7 +17199,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>61504</v>
+        <v>61519</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17200,7 +17210,7 @@
         <v>3</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>61504</v>
+        <v>61519</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17221,20 +17231,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>61504</v>
+        <v>61519</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>123008</v>
+        <v>123038</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>76880</v>
+        <v>76899</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17263,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>123008</v>
+        <v>123038</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17264,7 +17274,7 @@
         <v>1</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>123008</v>
+        <v>123038</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17285,20 +17295,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>123008</v>
+        <v>123038</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>123266</v>
+        <v>123297</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>153760</v>
+        <v>153798</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17317,7 +17327,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>246015</v>
+        <v>246077</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17328,7 +17338,7 @@
         <v>1</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>246015</v>
+        <v>246077</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17349,20 +17359,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>246015</v>
+        <v>246077</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>246015</v>
+        <v>246077</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>307519</v>
+        <v>307596</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17381,18 +17391,18 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>430527</v>
+        <v>430634</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F300" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>430527</v>
+        <v>430634</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17413,20 +17423,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>430527</v>
+        <v>430634</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>894581</v>
+        <v>894804</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>615038</v>
+        <v>615191</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17445,18 +17455,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>2130</v>
+        <v>2467</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
         <v>41</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>3065</v>
+        <v>2948</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17477,20 +17487,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>1944</v>
+        <v>2290</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2998</v>
+        <v>2927</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17509,7 +17519,7 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
@@ -17517,10 +17527,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1649</v>
+        <v>1470</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17541,20 +17551,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1942</v>
+        <v>1601</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>4664</v>
+        <v>4665</v>
       </c>
       <c r="N302" s="3" t="n">
         <v>2153</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17573,18 +17583,18 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>3893</v>
+        <v>3917</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4114</v>
+        <v>4072</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17605,20 +17615,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>3916</v>
+        <v>3923</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15374</v>
+        <v>15378</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4324</v>
+        <v>4336</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17637,7 +17647,7 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -17669,20 +17679,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>1404</v>
+        <v>1361</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="N304" s="3" t="n">
         <v>2153</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17733,7 +17743,7 @@
         </is>
       </c>
       <c r="L305" s="3" t="n">
-        <v>486</v>
+        <v>392</v>
       </c>
       <c r="M305" s="3" t="n">
         <v>1421</v>
@@ -17746,7 +17756,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17800,17 +17810,17 @@
         <v>154</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>308</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>19064</v>
+        <v>19073</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17854,7 +17864,7 @@
         <v>1476</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>308</v>
@@ -17864,7 +17874,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17918,17 +17928,17 @@
         <v>1999</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1230077</v>
+        <v>1230383</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="O308" s="2" t="n">
         <v>225</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17947,7 +17957,7 @@
         </is>
       </c>
       <c r="D309" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
@@ -17958,7 +17968,7 @@
         <v>2</v>
       </c>
       <c r="G309" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
@@ -17979,20 +17989,20 @@
         </is>
       </c>
       <c r="L309" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>31090</v>
+        <v>31098</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O309" s="2" t="n">
         <v>122</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18036,17 +18046,17 @@
         <v>1538</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>5858</v>
+        <v>5860</v>
       </c>
       <c r="N310" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O310" s="2" t="n">
         <v>71</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18065,7 +18075,7 @@
         </is>
       </c>
       <c r="D311" s="3" t="n">
-        <v>4708</v>
+        <v>4709</v>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
@@ -18076,7 +18086,7 @@
         <v>1</v>
       </c>
       <c r="G311" s="3" t="n">
-        <v>4708</v>
+        <v>4709</v>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
@@ -18097,20 +18107,20 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>5867</v>
+        <v>5869</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18153,12 +18163,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18187,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18188,7 +18198,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18209,20 +18219,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>25423</v>
+        <v>25429</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>45</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18263,20 +18273,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15042</v>
+        <v>15046</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15042</v>
+        <v>15046</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18295,18 +18305,18 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18327,20 +18337,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18369,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18370,7 +18380,7 @@
         <v>1</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18391,20 +18401,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>36902</v>
+        <v>36911</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>73805</v>
+        <v>73823</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18445,20 +18455,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>99944</v>
+        <v>99969</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>99944</v>
+        <v>99969</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>199887</v>
+        <v>199937</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18498,7 @@
         <v>7</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18512,17 +18522,17 @@
         <v>921</v>
       </c>
       <c r="M318" s="3" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="N318" s="3" t="n">
-        <v>864</v>
+        <v>1047</v>
       </c>
       <c r="O318" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18576,7 +18586,7 @@
         <v>1355</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15271</v>
+        <v>15275</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>1438</v>
@@ -18586,7 +18596,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18605,18 +18615,18 @@
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>1696</v>
+        <v>1453</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>2072</v>
+        <v>2034</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18637,10 +18647,10 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>1453</v>
+        <v>1847</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9553</v>
+        <v>9555</v>
       </c>
       <c r="N320" s="3" t="n">
         <v>2153</v>
@@ -18650,7 +18660,7 @@
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18669,18 +18679,18 @@
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>2303</v>
+        <v>2433</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18701,20 +18711,20 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3075</v>
+        <v>3380</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>5718</v>
+        <v>5720</v>
       </c>
       <c r="N321" s="3" t="n">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18778,7 +18788,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18797,7 +18807,7 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -18829,20 +18839,20 @@
         </is>
       </c>
       <c r="L323" s="3" t="n">
-        <v>2099</v>
+        <v>1701</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>2791</v>
+        <v>2153</v>
       </c>
       <c r="O323" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18906,7 @@
         <v>308</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5437</v>
+        <v>5438</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>308</v>
@@ -18906,7 +18916,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18925,18 +18935,18 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>2798</v>
+        <v>3050</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2453</v>
+        <v>2514</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18957,20 +18967,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15271</v>
+        <v>15275</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2583</v>
+        <v>2755</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18989,7 +18999,7 @@
         </is>
       </c>
       <c r="D326" s="3" t="n">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
@@ -19000,7 +19010,7 @@
         <v>3</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -19021,10 +19031,10 @@
         </is>
       </c>
       <c r="L326" s="3" t="n">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N326" s="3" t="n">
         <v>2888</v>
@@ -19034,7 +19044,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19053,7 +19063,7 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
@@ -19061,10 +19071,10 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>2189</v>
+        <v>2033</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19085,20 +19095,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>3793</v>
+        <v>3794</v>
       </c>
       <c r="N327" s="3" t="n">
         <v>2153</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19117,18 +19127,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>22716</v>
+        <v>22867</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
         <v>28</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>21705</v>
+        <v>21758</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19149,20 +19159,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>22849</v>
+        <v>22762</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>31691</v>
+        <v>31699</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>23740</v>
+        <v>23553</v>
       </c>
       <c r="O328" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19181,18 +19191,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7387</v>
+        <v>6456</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>6955</v>
+        <v>6971</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19216,17 +19226,17 @@
         <v>7270</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9496</v>
+        <v>9499</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7513</v>
+        <v>7484</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19245,18 +19255,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5494</v>
+        <v>5815</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5769</v>
+        <v>5780</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19277,20 +19287,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5346</v>
+        <v>6261</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8414</v>
+        <v>8416</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6304</v>
+        <v>6260</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19331,10 +19341,10 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="M331" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="N331" s="3" t="n">
         <v>308</v>
@@ -19344,7 +19354,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19363,18 +19373,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>955</v>
+        <v>972</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19395,20 +19405,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19472,7 @@
         <v>154</v>
       </c>
       <c r="M333" s="3" t="n">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="N333" s="3" t="n">
         <v>308</v>
@@ -19472,7 +19482,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19512,7 @@
         <v>11</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19526,7 +19536,7 @@
         <v>320</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9158</v>
+        <v>9160</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>337</v>
@@ -19536,7 +19546,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19590,7 +19600,7 @@
         <v>2765</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15376</v>
+        <v>15380</v>
       </c>
       <c r="N335" s="3" t="n">
         <v>2153</v>
@@ -19600,7 +19610,7 @@
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19627,10 +19637,10 @@
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19651,20 +19661,20 @@
         </is>
       </c>
       <c r="L336" s="3" t="n">
-        <v>860</v>
+        <v>678</v>
       </c>
       <c r="M336" s="3" t="n">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="N336" s="3" t="n">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="O336" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19694,7 +19704,7 @@
         <v>13</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19718,7 +19728,7 @@
         <v>280</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15055</v>
+        <v>15058</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>308</v>
@@ -19728,7 +19738,7 @@
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19792,7 +19802,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19811,18 +19821,18 @@
         </is>
       </c>
       <c r="D339" s="3" t="n">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F339" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G339" s="3" t="n">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
@@ -19843,20 +19853,20 @@
         </is>
       </c>
       <c r="L339" s="3" t="n">
-        <v>457</v>
+        <v>486</v>
       </c>
       <c r="M339" s="3" t="n">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="N339" s="3" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O339" s="2" t="n">
         <v>379</v>
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19879,14 +19889,14 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F340" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G340" s="3" t="n">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
@@ -19910,17 +19920,17 @@
         <v>824</v>
       </c>
       <c r="M340" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="N340" s="3" t="n">
-        <v>612</v>
+        <v>711</v>
       </c>
       <c r="O340" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -19943,14 +19953,14 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19977,14 +19987,14 @@
         <v>2365</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20034,11 +20044,11 @@
         <v>308</v>
       </c>
       <c r="O342" s="2" t="n">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20098,11 +20108,11 @@
         <v>308</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20129,10 +20139,10 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20156,17 +20166,17 @@
         <v>2027</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>56085</v>
+        <v>56099</v>
       </c>
       <c r="N344" s="3" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O344" s="2" t="n">
         <v>30</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20193,10 +20203,10 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>2267</v>
+        <v>2304</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20220,17 +20230,17 @@
         <v>1999</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1537596</v>
+        <v>1537978</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20249,7 +20259,7 @@
         </is>
       </c>
       <c r="D346" s="3" t="n">
-        <v>3875</v>
+        <v>3876</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
@@ -20260,7 +20270,7 @@
         <v>3</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>4109</v>
+        <v>4110</v>
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
@@ -20283,12 +20293,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4976</v>
+        <v>4977</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20317,7 @@
         </is>
       </c>
       <c r="D347" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
@@ -20318,7 +20328,7 @@
         <v>4</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
@@ -20339,20 +20349,20 @@
         </is>
       </c>
       <c r="L347" s="3" t="n">
-        <v>4305</v>
+        <v>4306</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>7923</v>
+        <v>7718</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6150</v>
+        <v>6152</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20393,20 +20403,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>7739</v>
+        <v>7741</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12301</v>
+        <v>12304</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20425,7 +20435,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20436,7 +20446,7 @@
         <v>2</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20457,20 +20467,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9226</v>
+        <v>9228</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>18451</v>
+        <v>18456</v>
       </c>
       <c r="O349" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20513,12 +20523,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>24602</v>
+        <v>24608</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20537,18 +20547,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>18285</v>
+        <v>21321</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16559</v>
+        <v>16699</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20569,20 +20579,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>18360</v>
+        <v>19626</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>30752</v>
+        <v>30760</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20611,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>44475</v>
+        <v>44486</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20612,7 +20622,7 @@
         <v>12</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>43381</v>
+        <v>43392</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20635,12 +20645,12 @@
       <c r="L352" s="3" t="inlineStr"/>
       <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="3" t="n">
-        <v>73805</v>
+        <v>73823</v>
       </c>
       <c r="O352" s="2" t="inlineStr"/>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20683,12 +20693,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>199887</v>
+        <v>199937</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20752,7 @@
         <v>538</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>9112</v>
+        <v>9114</v>
       </c>
       <c r="N354" s="3" t="n">
         <v>308</v>
@@ -20752,7 +20762,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20793,20 +20803,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>18413</v>
+        <v>18417</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17221</v>
+        <v>17225</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20835,7 @@
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -20836,7 +20846,7 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
@@ -20857,20 +20867,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>53816</v>
+        <v>53829</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17221</v>
+        <v>17225</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>57</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20889,18 +20899,18 @@
         </is>
       </c>
       <c r="D357" s="3" t="n">
-        <v>387</v>
+        <v>154</v>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F357" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
@@ -20924,17 +20934,17 @@
         <v>406</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>4730</v>
+        <v>4731</v>
       </c>
       <c r="N357" s="3" t="n">
-        <v>363</v>
+        <v>335</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20963,7 @@
         </is>
       </c>
       <c r="D358" s="3" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
@@ -20964,7 +20974,7 @@
         <v>1</v>
       </c>
       <c r="G358" s="3" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
@@ -20998,7 +21008,7 @@
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21038,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>153.7596</v>
+        <v>153.797848</v>
       </c>
     </row>
     <row r="2">
@@ -21039,7 +21049,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 12 Sep 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 13 Sep 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21061,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4226</v>
+        <v>4227</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3636</v>
+        <v>3637</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3206</v>
+        <v>3885</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1574536</v>
+        <v>1574894</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>96253</v>
+        <v>96275</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23618</v>
+        <v>23623</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23618</v>
+        <v>23623</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>23618</v>
+        <v>23623</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>47236</v>
+        <v>47247</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42512</v>
+        <v>42522</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42552</v>
+        <v>42561</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42512</v>
+        <v>42522</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>42542</v>
+        <v>42552</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85025</v>
+        <v>85044</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -916,20 +916,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>125963</v>
+        <v>125991</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>141708</v>
+        <v>141740</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>251926</v>
+        <v>251983</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>354271</v>
+        <v>354351</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>354271</v>
+        <v>354351</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>708541</v>
+        <v>708702</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1002,18 +1002,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6630</v>
+        <v>6055</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6024</v>
+        <v>6026</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6786</v>
+        <v>6788</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1574536</v>
+        <v>1574894</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8660</v>
+        <v>8662</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>116</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8236</v>
+        <v>8915</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8686</v>
+        <v>8674</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1098,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>7290</v>
+        <v>8864</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>149540</v>
+        <v>149574</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17320</v>
+        <v>17324</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13856</v>
+        <v>13859</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13897</v>
+        <v>13900</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1162,20 +1162,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13856</v>
+        <v>13859</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42275</v>
+        <v>42284</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34640</v>
+        <v>34648</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1216,20 +1216,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>21807</v>
+        <v>21812</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39363</v>
+        <v>39372</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22044</v>
+        <v>22049</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1270,20 +1270,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>93557</v>
+        <v>93579</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>93557</v>
+        <v>93579</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22044</v>
+        <v>22049</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1324,20 +1324,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>236180</v>
+        <v>236234</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1574536</v>
+        <v>1574894</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1378,20 +1378,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>29154</v>
+        <v>29161</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>63786</v>
+        <v>63801</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5353</v>
+        <v>5355</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22439</v>
+        <v>22444</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>63786</v>
+        <v>63801</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5353</v>
+        <v>5355</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
         <v>787</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1574536</v>
+        <v>1574894</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1575</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1563,17 +1563,17 @@
         <v>1575</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>226747</v>
+        <v>226799</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>117</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1614,20 +1614,20 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>267671</v>
+        <v>267732</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1668,20 +1668,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5668</v>
+        <v>5670</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22044</v>
+        <v>22049</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11337</v>
+        <v>11339</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1722,20 +1722,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11022</v>
+        <v>11024</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36797</v>
+        <v>36805</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22044</v>
+        <v>22049</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1776,20 +1776,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21256</v>
+        <v>21261</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>138984</v>
+        <v>139016</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42512</v>
+        <v>42522</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39363</v>
+        <v>39372</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39363</v>
+        <v>39372</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1840,20 +1840,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39363</v>
+        <v>39372</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>320160</v>
+        <v>320233</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>78727</v>
+        <v>78745</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
         <v>1351</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>315</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>1154</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>315</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2026,17 +2026,17 @@
         <v>1260</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1178</v>
+        <v>1165</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1570354</v>
+        <v>1570711</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1575</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2119,18 +2119,18 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2237</v>
+        <v>2430</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>24</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2054</v>
+        <v>2103</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2151,20 +2151,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2332</v>
+        <v>2425</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1574536</v>
+        <v>1574894</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O28" s="2" t="n">
         <v>84</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2215,20 +2215,20 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>16964</v>
+        <v>16968</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
         <v>630</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1574536</v>
+        <v>1574894</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1260</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2336,17 +2336,17 @@
         <v>2362</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11486</v>
+        <v>11489</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -2397,20 +2397,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1453</v>
+        <v>1441</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>629814</v>
+        <v>629957</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1638</v>
+        <v>1586</v>
       </c>
       <c r="O32" s="2" t="n">
         <v>193</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2461,20 +2461,20 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12755</v>
+        <v>12758</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O33" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2493,18 +2493,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3371</v>
+        <v>3310</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3679</v>
+        <v>3653</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2525,20 +2525,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3149</v>
+        <v>3490</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21047</v>
+        <v>21052</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2589,20 +2589,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30434</v>
+        <v>30441</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
         <v>787</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6252</v>
+        <v>6254</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1575</v>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2712,17 +2712,17 @@
         <v>1575</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4138</v>
+        <v>4139</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O37" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
         <v>5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2769,20 +2769,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>314907</v>
+        <v>314979</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2833,20 +2833,20 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>144144</v>
+        <v>144177</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>50</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2887,20 +2887,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>3897</v>
+        <v>3898</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17321</v>
+        <v>17325</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2951,20 +2951,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15064</v>
+        <v>15067</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3574</v>
+        <v>3575</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>7</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3011,20 +3011,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>3932</v>
+        <v>3933</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>5980</v>
+        <v>5981</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>6</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6498</v>
+        <v>6500</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3071,20 +3071,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>7709</v>
+        <v>6320</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8849</v>
+        <v>8851</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>6577</v>
+        <v>6578</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3103,18 +3103,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9942</v>
+        <v>10336</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>39</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10632</v>
+        <v>10675</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3131,20 +3131,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>10206</v>
+        <v>10717</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>13711</v>
+        <v>13714</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10579</v>
+        <v>10659</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3188,17 +3188,17 @@
         <v>1575</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8680</v>
+        <v>8682</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>45</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3249,20 +3249,20 @@
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
         <v>772</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>5848</v>
+        <v>5849</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>787</v>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1575</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3411,20 +3411,20 @@
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
         <v>1973</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>4128</v>
+        <v>4129</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>787</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
         <v>2488</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4344</v>
+        <v>4345</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1575</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>6613</v>
+        <v>6615</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>3</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>6771</v>
+        <v>6772</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3571,20 +3571,20 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6511</v>
+        <v>6512</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -3638,17 +3638,17 @@
         <v>787</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4801</v>
+        <v>4802</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>857</v>
+        <v>787</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
         <v>2</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>1652</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11244</v>
+        <v>11246</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1575</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>3</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3763,20 +3763,20 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>7873</v>
+        <v>3206</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30456</v>
+        <v>30463</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3795,18 +3795,18 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>8783</v>
+        <v>8454</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>7290</v>
+        <v>7458</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3826,21 +3826,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L56" s="3" t="n">
-        <v>8452</v>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>8452</v>
-      </c>
+      <c r="L56" s="3" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="3" t="n">
-        <v>9660</v>
-      </c>
-      <c r="O56" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>9481</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3859,18 +3853,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10009</v>
+        <v>9062</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>44</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>10455</v>
+        <v>10437</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3891,20 +3885,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>10203</v>
+        <v>9210</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30496</v>
+        <v>30503</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3923,18 +3917,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>4002</v>
+        <v>4155</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>28</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3955,20 +3949,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>4154</v>
+        <v>4156</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10279</v>
+        <v>10281</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4195</v>
+        <v>4259</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3981,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -3998,7 +3992,7 @@
         <v>3</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4022,17 +4016,17 @@
         <v>2430</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>3144</v>
+        <v>1575</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4076,17 +4070,17 @@
         <v>1102</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4133,14 +4127,14 @@
         <v>3447</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4177,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9762</v>
+        <v>9764</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4229,20 +4223,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4279,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4333,12 +4327,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42512</v>
+        <v>42522</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4379,20 +4373,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50385</v>
+        <v>50397</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4433,20 +4427,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22044</v>
+        <v>22049</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4483,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22044</v>
+        <v>22049</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4552,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4602,17 +4596,17 @@
         <v>630</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>5015</v>
+        <v>5016</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O70" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4653,20 +4647,20 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4177</v>
+        <v>4178</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>5007</v>
+        <v>5008</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4679,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -4696,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4717,20 +4711,20 @@
         </is>
       </c>
       <c r="L72" s="3" t="n">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1476981</v>
+        <v>1477316</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11337</v>
+        <v>11339</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4771,20 +4765,20 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4731</v>
+        <v>4733</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7443</v>
+        <v>7445</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4825,20 +4819,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8660</v>
+        <v>8662</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20861</v>
+        <v>20866</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17320</v>
+        <v>17324</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4879,20 +4873,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17320</v>
+        <v>17324</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>26928</v>
+        <v>26934</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4940,7 @@
         <v>299</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6345</v>
+        <v>6347</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>315</v>
@@ -4956,7 +4950,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4997,20 +4991,20 @@
         </is>
       </c>
       <c r="L77" s="3" t="n">
-        <v>1181</v>
+        <v>584</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5163</v>
+        <v>5164</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>630</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5062,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5109,20 +5103,20 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5668</v>
+        <v>5670</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5668</v>
+        <v>5670</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5159,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5211,20 +5205,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23029</v>
+        <v>23034</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23029</v>
+        <v>23034</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10077</v>
+        <v>10079</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5267,12 +5261,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20154</v>
+        <v>20159</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5293,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>157</v>
@@ -5322,7 +5316,7 @@
         <v>157</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1574379</v>
+        <v>1574736</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>787</v>
@@ -5332,7 +5326,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5349,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
@@ -5382,7 +5376,7 @@
         <v>724</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34419</v>
+        <v>34427</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1575</v>
@@ -5392,7 +5386,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5429,20 +5423,20 @@
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="3" t="n">
-        <v>1993</v>
+        <v>630</v>
       </c>
       <c r="M85" s="3" t="n">
         <v>3140</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O85" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5482,17 +5476,17 @@
         <v>1260</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5531,12 +5525,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10077</v>
+        <v>10079</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5575,12 +5569,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14171</v>
+        <v>14174</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5613,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17320</v>
+        <v>17324</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5668,7 @@
         <v>498</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>85573</v>
+        <v>85592</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>787</v>
@@ -5684,7 +5678,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5718,7 @@
         <v>787</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5234</v>
+        <v>5235</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1575</v>
@@ -5734,7 +5728,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5771,20 +5765,20 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5820,15 +5814,21 @@
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="3" t="inlineStr"/>
-      <c r="M93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="n">
+        <v>2824</v>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>2824</v>
+      </c>
       <c r="N93" s="3" t="n">
-        <v>6298</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr"/>
+        <v>6300</v>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10077</v>
+        <v>10079</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5911,12 +5911,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14171</v>
+        <v>14174</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -5955,12 +5955,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17320</v>
+        <v>17324</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6004,17 +6004,17 @@
         <v>1592</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="O97" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6058,17 +6058,17 @@
         <v>2047</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6109,20 +6109,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>4697</v>
+        <v>4698</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5153</v>
+        <v>5155</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9762</v>
+        <v>9764</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6163,20 +6163,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6219,12 +6219,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6265,20 +6265,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>17888</v>
+        <v>17892</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>17888</v>
+        <v>17892</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42512</v>
+        <v>42522</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6321,12 +6321,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50385</v>
+        <v>50397</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6373,14 +6373,14 @@
         <v>2677</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="O104" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6471,12 +6471,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9762</v>
+        <v>9764</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6567,12 +6567,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6615,12 +6615,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42512</v>
+        <v>42522</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6663,12 +6663,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50385</v>
+        <v>50397</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6711,12 +6711,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>78727</v>
+        <v>78745</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>86599</v>
+        <v>86619</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>86599</v>
+        <v>86619</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6767,20 +6767,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>86599</v>
+        <v>86619</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>96667</v>
+        <v>96689</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>110218</v>
+        <v>110243</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>110218</v>
+        <v>110243</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>110218</v>
+        <v>110243</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>141708</v>
+        <v>141740</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6875,20 +6875,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>125963</v>
+        <v>125991</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>125963</v>
+        <v>125991</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6929,20 +6929,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>188944</v>
+        <v>188987</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -6983,20 +6983,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>212562</v>
+        <v>212611</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>251926</v>
+        <v>251983</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>251926</v>
+        <v>251983</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7037,20 +7037,20 @@
         </is>
       </c>
       <c r="L117" s="3" t="n">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O117" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7091,20 +7091,20 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3776</v>
+        <v>3777</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>5823</v>
+        <v>5824</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7193,20 +7193,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14171</v>
+        <v>14174</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14171</v>
+        <v>14174</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7249,12 +7249,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22673</v>
+        <v>22678</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7295,20 +7295,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7349,20 +7349,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>40878</v>
+        <v>40887</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7406,17 +7406,17 @@
         <v>1252</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O124" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7457,20 +7457,20 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5654</v>
+        <v>5655</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>5808</v>
+        <v>5810</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6430</v>
+        <v>6432</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7565,20 +7565,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11829</v>
+        <v>11832</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14171</v>
+        <v>14174</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7621,12 +7621,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22673</v>
+        <v>22678</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7669,12 +7669,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       <c r="L130" s="3" t="inlineStr"/>
       <c r="M130" s="3" t="inlineStr"/>
       <c r="N130" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7763,20 +7763,20 @@
         </is>
       </c>
       <c r="L131" s="3" t="n">
-        <v>4900</v>
+        <v>4901</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>4900</v>
+        <v>4901</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O131" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7817,20 +7817,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7871,20 +7871,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15832</v>
+        <v>15836</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7927,12 +7927,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28342</v>
+        <v>28348</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -7973,20 +7973,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21256</v>
+        <v>21261</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21256</v>
+        <v>21261</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47236</v>
+        <v>47247</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8027,20 +8027,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28342</v>
+        <v>28348</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28342</v>
+        <v>28348</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>70854</v>
+        <v>70870</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8081,20 +8081,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -8121,10 +8121,10 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6334</v>
+        <v>6307</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8145,20 +8145,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12686</v>
+        <v>12689</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O138" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8266,17 +8266,17 @@
         <v>578</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5141</v>
+        <v>5142</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>624</v>
+        <v>315</v>
       </c>
       <c r="O140" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
         <v>1575</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>13424</v>
+        <v>13428</v>
       </c>
       <c r="N142" s="3" t="n">
         <v>315</v>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8428,17 +8428,17 @@
         <v>2063</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O143" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8489,20 +8489,20 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10688</v>
+        <v>10690</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="O144" s="2" t="n">
         <v>50</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8545,12 +8545,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8591,20 +8591,20 @@
         </is>
       </c>
       <c r="L146" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53248</v>
+        <v>53260</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8647,12 +8647,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -8703,20 +8703,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17254</v>
+        <v>17258</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8783,18 +8783,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>16133</v>
+        <v>15873</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16655</v>
+        <v>16690</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8815,20 +8815,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15745</v>
+        <v>16075</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39363</v>
+        <v>39372</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>16</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8879,20 +8879,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>62931</v>
+        <v>62945</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75578</v>
+        <v>75595</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8933,20 +8933,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>102345</v>
+        <v>102368</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>102345</v>
+        <v>102368</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>204690</v>
+        <v>204736</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8990,7 @@
         <v>157</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10301</v>
+        <v>10303</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>315</v>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
         <v>787</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15427</v>
+        <v>15431</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1575</v>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9157,14 +9157,14 @@
         <v>3225</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O156" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -9211,20 +9211,20 @@
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
         <v>787</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1574536</v>
+        <v>1574894</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1575</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9322,17 +9322,17 @@
         <v>1575</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19094</v>
+        <v>19099</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O159" s="2" t="n">
         <v>38</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>1</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -9383,20 +9383,20 @@
         </is>
       </c>
       <c r="L160" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6586</v>
+        <v>6588</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O160" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
         <v>3</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -9504,17 +9504,17 @@
         <v>1786</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30042</v>
+        <v>30049</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1575</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -9565,20 +9565,20 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3122</v>
+        <v>2912</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3831</v>
+        <v>3832</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9597,18 +9597,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3884</v>
+        <v>3906</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
         <v>52</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>4066</v>
+        <v>4061</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9629,20 +9629,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3888</v>
+        <v>3687</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>10234</v>
+        <v>10237</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
         </is>
       </c>
       <c r="L165" s="3" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>4889</v>
+        <v>4890</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="L166" s="3" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="M166" s="3" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="N166" s="3" t="n">
         <v>630</v>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1263</v>
+        <v>1248</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -9811,20 +9811,20 @@
         </is>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1427</v>
+        <v>1573</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9677</v>
+        <v>9679</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1260</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
         <v>1575</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5369</v>
+        <v>5370</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>315</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9919,10 +9919,10 @@
         </is>
       </c>
       <c r="L169" s="3" t="n">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>315</v>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9973,20 +9973,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94472</v>
+        <v>94494</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94472</v>
+        <v>94494</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>125963</v>
+        <v>125991</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10029,12 +10029,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42512</v>
+        <v>42522</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10071,20 +10071,20 @@
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O172" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10121,20 +10121,20 @@
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="3" t="n">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10173,12 +10173,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10215,20 +10215,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14141</v>
+        <v>14144</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14171</v>
+        <v>14174</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11337</v>
+        <v>11339</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11337</v>
+        <v>11339</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22673</v>
+        <v>22678</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10315,20 +10315,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>15824</v>
+        <v>15828</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10365,20 +10365,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19052</v>
+        <v>19056</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="O178" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10421,12 +10421,12 @@
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10467,20 +10467,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10523,12 +10523,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10569,20 +10569,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10625,12 +10625,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28342</v>
+        <v>28348</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10671,20 +10671,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21256</v>
+        <v>21261</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21256</v>
+        <v>21261</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42512</v>
+        <v>42522</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10725,20 +10725,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28342</v>
+        <v>28348</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28342</v>
+        <v>28348</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56683</v>
+        <v>56696</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10782,17 +10782,17 @@
         <v>157</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
         <v>157</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>315</v>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
         <v>157</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102442</v>
+        <v>102466</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>315</v>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
         <v>157</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29041</v>
+        <v>29047</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>315</v>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11056,17 +11056,17 @@
         <v>157</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>155459</v>
+        <v>155494</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11120,7 +11120,7 @@
         <v>157</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>315</v>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
         <v>157</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>315</v>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
         <v>157</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>315</v>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>157</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>315</v>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11408,7 +11408,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11449,20 +11449,20 @@
         </is>
       </c>
       <c r="L198" s="3" t="n">
-        <v>1258</v>
+        <v>953</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11503,20 +11503,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20504</v>
+        <v>20508</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20504</v>
+        <v>20508</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -11567,20 +11567,20 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11621,20 +11621,20 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10727</v>
+        <v>10730</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7558</v>
+        <v>7559</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11675,20 +11675,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10304</v>
+        <v>10306</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10077</v>
+        <v>10079</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11729,20 +11729,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8188</v>
+        <v>8189</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>274867</v>
+        <v>274929</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>13856</v>
+        <v>13859</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11783,20 +11783,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15558</v>
+        <v>15562</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>15969</v>
+        <v>15973</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>20154</v>
+        <v>20159</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>1</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>20154</v>
+        <v>20159</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -11847,20 +11847,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20154</v>
+        <v>20159</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>48573</v>
+        <v>48584</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11903,12 +11903,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22673</v>
+        <v>22678</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12080,17 +12080,17 @@
         <v>1776</v>
       </c>
       <c r="M209" s="3" t="n">
-        <v>2988</v>
+        <v>2989</v>
       </c>
       <c r="N209" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O209" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12144,17 +12144,17 @@
         <v>2047</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4451</v>
+        <v>4452</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12195,20 +12195,20 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12249,20 +12249,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14171</v>
+        <v>14174</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12305,12 +12305,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22673</v>
+        <v>22678</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12351,20 +12351,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12408,17 +12408,17 @@
         <v>1102</v>
       </c>
       <c r="M215" s="3" t="n">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="N215" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O215" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12462,17 +12462,17 @@
         <v>2047</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11823</v>
+        <v>11826</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="O216" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12513,20 +12513,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15503</v>
+        <v>15506</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>37301</v>
+        <v>37309</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12545,7 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>1</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -12577,20 +12577,20 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12631,20 +12631,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7085</v>
+        <v>7087</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14171</v>
+        <v>14174</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12687,12 +12687,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12733,20 +12733,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
         <v>787</v>
       </c>
       <c r="M222" s="3" t="n">
-        <v>2828</v>
+        <v>2829</v>
       </c>
       <c r="N222" s="3" t="n">
         <v>1575</v>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -12854,17 +12854,17 @@
         <v>1575</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>4029</v>
+        <v>4030</v>
       </c>
       <c r="N223" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O223" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>1</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -12915,20 +12915,20 @@
         </is>
       </c>
       <c r="L224" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="L225" s="3" t="n">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>7674</v>
+        <v>7676</v>
       </c>
       <c r="N225" s="3" t="n">
         <v>1575</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13043,20 +13043,20 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="M226" s="3" t="n">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="N226" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O226" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>2</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -13107,20 +13107,20 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13164,7 @@
         <v>157</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>315</v>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13218,17 +13218,17 @@
         <v>157</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13272,17 +13272,17 @@
         <v>157</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13326,7 @@
         <v>787</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1575</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13366,7 +13366,7 @@
         <v>3</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -13390,17 +13390,17 @@
         <v>1575</v>
       </c>
       <c r="M232" s="3" t="n">
-        <v>3881</v>
+        <v>3882</v>
       </c>
       <c r="N232" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O232" s="2" t="n">
         <v>60</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13441,20 +13441,20 @@
         </is>
       </c>
       <c r="L233" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7174</v>
+        <v>7175</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>35</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13518,7 +13518,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>1</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -13569,20 +13569,20 @@
         </is>
       </c>
       <c r="L235" s="3" t="n">
-        <v>3919</v>
+        <v>3920</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>4243</v>
+        <v>4244</v>
       </c>
       <c r="N235" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O235" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13623,20 +13623,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6493</v>
+        <v>6495</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13679,12 +13679,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>7263</v>
+        <v>7265</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>1</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>7263</v>
+        <v>7265</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -13735,20 +13735,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>10976</v>
+        <v>10979</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13815,7 +13815,7 @@
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>10430</v>
+        <v>10432</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>1</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>10430</v>
+        <v>10432</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -13849,12 +13849,12 @@
       <c r="L240" s="3" t="inlineStr"/>
       <c r="M240" s="3" t="inlineStr"/>
       <c r="N240" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13873,7 +13873,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>8</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>18384</v>
+        <v>18388</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -13905,20 +13905,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>21776</v>
+        <v>21759</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30505</v>
+        <v>30512</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>1</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -13969,20 +13969,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>41806</v>
+        <v>41815</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58340</v>
+        <v>58353</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75578</v>
+        <v>75595</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14001,18 +14001,18 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>18757</v>
+        <v>17481</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>20110</v>
+        <v>20380</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14029,20 +14029,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>19438</v>
+        <v>21770</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31490721</v>
+        <v>31497874</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14085,12 +14085,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14134,7 @@
         <v>945</v>
       </c>
       <c r="M245" s="3" t="n">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="N245" s="3" t="n">
         <v>315</v>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14163,18 +14163,18 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>2455</v>
+        <v>2332</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F246" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2308</v>
+        <v>2316</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14195,20 +14195,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2332</v>
+        <v>2380</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>2955</v>
+        <v>2928</v>
       </c>
       <c r="O246" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14227,7 @@
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>1</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -14259,20 +14259,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15462</v>
+        <v>15465</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23215</v>
+        <v>23220</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17635</v>
+        <v>17639</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14291,7 +14291,7 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>2</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -14325,12 +14325,12 @@
       <c r="L248" s="3" t="inlineStr"/>
       <c r="M248" s="3" t="inlineStr"/>
       <c r="N248" s="3" t="n">
-        <v>17635</v>
+        <v>17639</v>
       </c>
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>3</v>
       </c>
       <c r="G249" s="3" t="n">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>787</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9244</v>
+        <v>9246</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1575</v>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14484,17 +14484,17 @@
         <v>157</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>96820</v>
+        <v>96842</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14535,20 +14535,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50171</v>
+        <v>50182</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50171</v>
+        <v>50182</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14589,20 +14589,20 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>8754</v>
+        <v>8475</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>8754</v>
+        <v>8475</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>7558</v>
+        <v>7559</v>
       </c>
       <c r="O253" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>7827</v>
+        <v>7829</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>1</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>7827</v>
+        <v>7829</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -14655,12 +14655,12 @@
       <c r="L254" s="3" t="inlineStr"/>
       <c r="M254" s="3" t="inlineStr"/>
       <c r="N254" s="3" t="n">
-        <v>10077</v>
+        <v>10079</v>
       </c>
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14806,7 +14806,7 @@
         <v>290</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>315</v>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14839,14 +14839,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -14876,11 +14876,11 @@
         <v>630</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
@@ -14931,10 +14931,10 @@
         </is>
       </c>
       <c r="L259" s="3" t="n">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21292</v>
+        <v>21297</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1575</v>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>2</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -14995,20 +14995,20 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3656</v>
+        <v>3657</v>
       </c>
       <c r="N260" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O260" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="F261" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -15059,20 +15059,20 @@
         </is>
       </c>
       <c r="L261" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>6985</v>
+        <v>6986</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>11</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15123,20 +15123,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15163,7 +15163,7 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G263" s="3" t="n">
         <v>787</v>
@@ -15190,7 +15190,7 @@
         <v>787</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10515</v>
+        <v>10517</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1575</v>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15257,14 +15257,14 @@
         <v>1606</v>
       </c>
       <c r="N264" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O264" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15307,12 +15307,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>1</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15363,20 +15363,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9595</v>
+        <v>9597</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15395,7 +15395,7 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -15403,10 +15403,10 @@
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>2860</v>
+        <v>2889</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15430,17 +15430,17 @@
         <v>2622</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19365</v>
+        <v>19370</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8910</v>
+        <v>8912</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>2</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>9249</v>
+        <v>9251</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15491,20 +15491,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>9718</v>
+        <v>9720</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14183</v>
+        <v>14187</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>13856</v>
+        <v>13859</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15547,12 +15547,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15595,12 +15595,12 @@
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15619,7 +15619,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>22826</v>
+        <v>22831</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>2</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>21490</v>
+        <v>21495</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15651,20 +15651,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>22828</v>
+        <v>22833</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>22829</v>
+        <v>22834</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15708,17 +15708,17 @@
         <v>157</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O272" s="2" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15762,17 +15762,17 @@
         <v>157</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>20853</v>
+        <v>20858</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O273" s="2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15791,7 +15791,7 @@
         </is>
       </c>
       <c r="D274" s="3" t="n">
-        <v>16644</v>
+        <v>16648</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>1</v>
       </c>
       <c r="G274" s="3" t="n">
-        <v>16644</v>
+        <v>16648</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -15826,17 +15826,17 @@
         <v>157</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31595</v>
+        <v>31602</v>
       </c>
       <c r="N274" s="3" t="n">
-        <v>18309</v>
+        <v>18313</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15890,17 +15890,17 @@
         <v>157</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15824</v>
+        <v>15828</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O275" s="2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15930,7 @@
         <v>2</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>157</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>156980</v>
+        <v>157015</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>315</v>
@@ -15964,7 +15964,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16033,7 @@
         </is>
       </c>
       <c r="D278" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>3</v>
       </c>
       <c r="G278" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -16065,20 +16065,20 @@
         </is>
       </c>
       <c r="L278" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>6846</v>
+        <v>6848</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="D279" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>1</v>
       </c>
       <c r="G279" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -16129,20 +16129,20 @@
         </is>
       </c>
       <c r="L279" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9852</v>
+        <v>9854</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7558</v>
+        <v>7559</v>
       </c>
       <c r="O279" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16183,20 +16183,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8569</v>
+        <v>8571</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10077</v>
+        <v>10079</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16239,12 +16239,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>13856</v>
+        <v>13859</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16287,12 +16287,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16335,12 +16335,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16381,20 +16381,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>20154</v>
+        <v>20159</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33572</v>
+        <v>33580</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16413,18 +16413,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>8564</v>
+        <v>8745</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>8572</v>
+        <v>8629</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16445,20 +16445,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>8743</v>
+        <v>9134</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>9306</v>
+        <v>9377</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16512,7 +16512,7 @@
         <v>157</v>
       </c>
       <c r="M286" s="3" t="n">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="N286" s="3" t="n">
         <v>315</v>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16541,7 +16541,7 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5342</v>
+        <v>5344</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>14</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5561</v>
+        <v>5562</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16568,15 +16568,21 @@
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
-      <c r="L287" s="3" t="inlineStr"/>
-      <c r="M287" s="3" t="inlineStr"/>
+      <c r="L287" s="3" t="n">
+        <v>5529</v>
+      </c>
+      <c r="M287" s="3" t="n">
+        <v>7015</v>
+      </c>
       <c r="N287" s="3" t="n">
-        <v>5860</v>
-      </c>
-      <c r="O287" s="2" t="inlineStr"/>
+        <v>5862</v>
+      </c>
+      <c r="O287" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16595,18 +16601,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6608</v>
+        <v>6804</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
         <v>27</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>7427</v>
+        <v>7381</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16623,20 +16629,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7677</v>
+        <v>7578</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8745</v>
+        <v>8249</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7640</v>
+        <v>7487</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16655,7 +16661,7 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>13604</v>
+        <v>13607</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
@@ -16663,10 +16669,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>10373</v>
+        <v>10299</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16683,20 +16689,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>10593</v>
+        <v>10596</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>10593</v>
+        <v>10596</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>11565</v>
+        <v>11957</v>
       </c>
       <c r="O289" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16737,10 +16743,10 @@
         </is>
       </c>
       <c r="L290" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="M290" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="N290" s="3" t="n">
         <v>1575</v>
@@ -16750,7 +16756,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16769,7 +16775,7 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
@@ -16801,20 +16807,20 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="M291" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="N291" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O291" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16839,7 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -16841,10 +16847,10 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4049</v>
+        <v>4092</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16865,20 +16871,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>5150</v>
+        <v>5151</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5668</v>
+        <v>5670</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O292" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16942,7 +16948,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -16961,18 +16967,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>11544</v>
+        <v>6804</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7583</v>
+        <v>7554</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -16993,20 +16999,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>6802</v>
+        <v>5843</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>28153</v>
+        <v>28159</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>8532</v>
+        <v>9064</v>
       </c>
       <c r="O294" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17047,20 +17053,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51177</v>
+        <v>51189</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>695537</v>
+        <v>695695</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39363</v>
+        <v>39372</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17079,7 +17085,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17090,7 +17096,7 @@
         <v>8</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17111,20 +17117,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68459</v>
+        <v>68475</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39363</v>
+        <v>39372</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17149,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>62981</v>
+        <v>62996</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17154,7 +17160,7 @@
         <v>6</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>62981</v>
+        <v>62996</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17175,20 +17181,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>62981</v>
+        <v>62996</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>125963</v>
+        <v>125991</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>78727</v>
+        <v>78745</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17229,20 +17235,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>125963</v>
+        <v>125991</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>126227</v>
+        <v>126256</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>157454</v>
+        <v>157489</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17261,7 +17267,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>251926</v>
+        <v>251983</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17272,7 +17278,7 @@
         <v>1</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>251926</v>
+        <v>251983</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17293,20 +17299,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>251926</v>
+        <v>251983</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>251927</v>
+        <v>251985</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>314907</v>
+        <v>314979</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17325,7 +17331,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>440870</v>
+        <v>440970</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17336,7 +17342,7 @@
         <v>3</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>440870</v>
+        <v>440970</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17357,20 +17363,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>440870</v>
+        <v>440970</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>856248</v>
+        <v>856443</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>629814</v>
+        <v>629957</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17389,18 +17395,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>2878</v>
+        <v>1217</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2665</v>
+        <v>2644</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17421,20 +17427,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>2430</v>
+        <v>2276</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2595</v>
+        <v>2523</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17461,10 +17467,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1494</v>
+        <v>1466</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17485,20 +17491,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>2332</v>
+        <v>1361</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2204</v>
+        <v>2235</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17517,18 +17523,18 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>3867</v>
+        <v>3870</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F303" s="2" t="n">
         <v>24</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4158</v>
+        <v>4143</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17549,20 +17555,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>3869</v>
+        <v>4041</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15638</v>
+        <v>15642</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4525</v>
+        <v>4459</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17585,14 +17591,14 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F304" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1351</v>
+        <v>1309</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17616,17 +17622,17 @@
         <v>1102</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17680,7 +17686,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17709,7 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F306" s="2" t="n">
@@ -17734,17 +17740,17 @@
         <v>157</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>19891</v>
+        <v>19890</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17785,10 +17791,10 @@
         </is>
       </c>
       <c r="L307" s="3" t="n">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>315</v>
@@ -17798,7 +17804,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17821,14 +17827,14 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G308" s="3" t="n">
-        <v>2362</v>
+        <v>2317</v>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
@@ -17852,17 +17858,17 @@
         <v>2047</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1259629</v>
+        <v>1259915</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17881,7 +17887,7 @@
         </is>
       </c>
       <c r="D309" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
@@ -17892,7 +17898,7 @@
         <v>1</v>
       </c>
       <c r="G309" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
@@ -17913,20 +17919,20 @@
         </is>
       </c>
       <c r="L309" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>31837</v>
+        <v>31844</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O309" s="2" t="n">
         <v>123</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17980,17 +17986,17 @@
         <v>1575</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>5999</v>
+        <v>6000</v>
       </c>
       <c r="N310" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O310" s="2" t="n">
         <v>67</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18009,7 +18015,7 @@
         </is>
       </c>
       <c r="D311" s="3" t="n">
-        <v>4821</v>
+        <v>4822</v>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
@@ -18020,7 +18026,7 @@
         <v>1</v>
       </c>
       <c r="G311" s="3" t="n">
-        <v>4821</v>
+        <v>4822</v>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
@@ -18041,20 +18047,20 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>5139</v>
+        <v>5140</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>6008</v>
+        <v>6010</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18097,12 +18103,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18127,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18132,7 +18138,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18153,20 +18159,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26033</v>
+        <v>26039</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O313" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18207,20 +18213,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15404</v>
+        <v>15407</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15404</v>
+        <v>15407</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18245,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18247,10 +18253,10 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18271,20 +18277,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1574536</v>
+        <v>1574894</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O315" s="2" t="n">
         <v>112</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18303,7 +18309,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18314,7 +18320,7 @@
         <v>2</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18335,20 +18341,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>37789</v>
+        <v>37797</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75578</v>
+        <v>75595</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18373,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>102345</v>
+        <v>102368</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18378,7 +18384,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>102345</v>
+        <v>102368</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18399,20 +18405,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>102345</v>
+        <v>102368</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>102345</v>
+        <v>102368</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>204690</v>
+        <v>204736</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18466,7 +18472,7 @@
         <v>855</v>
       </c>
       <c r="M318" s="3" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="N318" s="3" t="n">
         <v>1016</v>
@@ -18476,7 +18482,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18495,7 +18501,7 @@
         </is>
       </c>
       <c r="D319" s="3" t="n">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
@@ -18506,7 +18512,7 @@
         <v>1</v>
       </c>
       <c r="G319" s="3" t="n">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
@@ -18527,20 +18533,20 @@
         </is>
       </c>
       <c r="L319" s="3" t="n">
-        <v>1360</v>
+        <v>1387</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15638</v>
+        <v>15642</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O319" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18559,18 +18565,18 @@
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>2159</v>
+        <v>1945</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>1662</v>
+        <v>1744</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18591,20 +18597,20 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>1943</v>
+        <v>1167</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9783</v>
+        <v>9785</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18640,7 @@
         <v>9</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18655,10 +18661,10 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3023</v>
+        <v>2888</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>5856</v>
+        <v>5857</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>315</v>
@@ -18668,7 +18674,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18687,18 +18693,18 @@
         </is>
       </c>
       <c r="D322" s="3" t="n">
-        <v>932</v>
+        <v>425</v>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F322" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G322" s="3" t="n">
-        <v>656</v>
+        <v>598</v>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
@@ -18719,20 +18725,20 @@
         </is>
       </c>
       <c r="L322" s="3" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M322" s="3" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="N322" s="3" t="n">
-        <v>315</v>
+        <v>468</v>
       </c>
       <c r="O322" s="2" t="n">
-        <v>577</v>
+        <v>560</v>
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18751,7 +18757,7 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -18762,7 +18768,7 @@
         <v>4</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18786,17 +18792,17 @@
         <v>2430</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="O323" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18837,10 +18843,10 @@
         </is>
       </c>
       <c r="L324" s="3" t="n">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5568</v>
+        <v>5569</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>315</v>
@@ -18850,7 +18856,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18869,7 +18875,7 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -18901,20 +18907,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15638</v>
+        <v>15642</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18933,7 +18939,7 @@
         </is>
       </c>
       <c r="D326" s="3" t="n">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
@@ -18944,7 +18950,7 @@
         <v>3</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -18968,7 +18974,7 @@
         <v>1649</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N326" s="3" t="n">
         <v>2348</v>
@@ -18978,7 +18984,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -18997,7 +19003,7 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
@@ -19005,10 +19011,10 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>2165</v>
+        <v>1867</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19029,20 +19035,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>1102</v>
+        <v>1674</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O327" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19061,18 +19067,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>22352</v>
+        <v>20455</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
         <v>28</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>22776</v>
+        <v>22603</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19093,20 +19099,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>21977</v>
+        <v>20789</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>32453</v>
+        <v>32460</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>23887</v>
+        <v>23033</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19125,7 +19131,7 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>6972</v>
+        <v>6974</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
@@ -19133,10 +19139,10 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7215</v>
+        <v>7200</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19157,20 +19163,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7243</v>
+        <v>7237</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9724</v>
+        <v>9727</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7814</v>
+        <v>7739</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19189,18 +19195,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>6404</v>
+        <v>6298</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5984</v>
+        <v>6011</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19221,20 +19227,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6297</v>
+        <v>6208</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8616</v>
+        <v>8618</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6407</v>
+        <v>6528</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19275,10 +19281,10 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="M331" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="N331" s="3" t="n">
         <v>315</v>
@@ -19288,7 +19294,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19311,14 +19317,14 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>994</v>
+        <v>1035</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19339,20 +19345,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1129</v>
+        <v>1246</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19379,10 +19385,10 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>845</v>
+        <v>908</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19416,7 +19422,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19435,18 +19441,18 @@
         </is>
       </c>
       <c r="D334" s="3" t="n">
-        <v>422</v>
+        <v>578</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19470,17 +19476,17 @@
         <v>422</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9378</v>
+        <v>9380</v>
       </c>
       <c r="N334" s="3" t="n">
-        <v>315</v>
+        <v>635</v>
       </c>
       <c r="O334" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19534,17 +19540,17 @@
         <v>1102</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="O335" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19563,18 +19569,18 @@
         </is>
       </c>
       <c r="D336" s="3" t="n">
-        <v>868</v>
+        <v>387</v>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>368</v>
+        <v>415</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19595,20 +19601,20 @@
         </is>
       </c>
       <c r="L336" s="3" t="n">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="M336" s="3" t="n">
         <v>2885</v>
       </c>
       <c r="N336" s="3" t="n">
-        <v>315</v>
+        <v>425</v>
       </c>
       <c r="O336" s="2" t="n">
         <v>66</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19662,17 +19668,17 @@
         <v>157</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15416</v>
+        <v>15420</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>315</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19742,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19790,7 +19796,7 @@
         <v>592</v>
       </c>
       <c r="M339" s="3" t="n">
-        <v>4689</v>
+        <v>4690</v>
       </c>
       <c r="N339" s="3" t="n">
         <v>652</v>
@@ -19800,7 +19806,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19819,7 +19825,7 @@
         </is>
       </c>
       <c r="D340" s="3" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
@@ -19851,10 +19857,10 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M340" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="N340" s="3" t="n">
         <v>315</v>
@@ -19864,7 +19870,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19883,18 +19889,18 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19921,14 +19927,14 @@
         <v>2422</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>986</v>
+        <v>954</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19946,13 +19952,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D342" s="3" t="inlineStr"/>
-      <c r="E342" s="2" t="inlineStr"/>
-      <c r="F342" s="2" t="inlineStr"/>
-      <c r="G342" s="3" t="inlineStr"/>
+      <c r="D342" s="3" t="n">
+        <v>509</v>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G342" s="3" t="n">
+        <v>509</v>
+      </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I342" s="2" t="n">
@@ -19975,14 +19991,14 @@
         <v>1414</v>
       </c>
       <c r="N342" s="3" t="n">
-        <v>315</v>
+        <v>559</v>
       </c>
       <c r="O342" s="2" t="n">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20005,14 +20021,14 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
@@ -20033,7 +20049,7 @@
         </is>
       </c>
       <c r="L343" s="3" t="n">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="M343" s="3" t="n">
         <v>2422</v>
@@ -20042,11 +20058,11 @@
         <v>315</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20065,18 +20081,18 @@
         </is>
       </c>
       <c r="D344" s="3" t="n">
-        <v>1943</v>
+        <v>2388</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1882</v>
+        <v>1933</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20097,20 +20113,20 @@
         </is>
       </c>
       <c r="L344" s="3" t="n">
-        <v>2789</v>
+        <v>2232</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57433</v>
+        <v>57446</v>
       </c>
       <c r="N344" s="3" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O344" s="2" t="n">
         <v>33</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20137,10 +20153,10 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>2302</v>
+        <v>2313</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20164,17 +20180,17 @@
         <v>2047</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>75455</v>
+        <v>75472</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="O345" s="2" t="n">
         <v>78</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20193,7 +20209,7 @@
         </is>
       </c>
       <c r="D346" s="3" t="n">
-        <v>3968</v>
+        <v>3969</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
@@ -20204,7 +20220,7 @@
         <v>2</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>4632</v>
+        <v>4633</v>
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
@@ -20227,12 +20243,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20251,7 +20267,7 @@
         </is>
       </c>
       <c r="D347" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
@@ -20259,10 +20275,10 @@
         </is>
       </c>
       <c r="F347" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
@@ -20283,20 +20299,20 @@
         </is>
       </c>
       <c r="L347" s="3" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>7901</v>
+        <v>7903</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="O347" s="2" t="n">
         <v>62</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20331,7 @@
         </is>
       </c>
       <c r="D348" s="3" t="n">
-        <v>8051</v>
+        <v>8052</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
@@ -20326,7 +20342,7 @@
         <v>1</v>
       </c>
       <c r="G348" s="3" t="n">
-        <v>8051</v>
+        <v>8052</v>
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
@@ -20347,20 +20363,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12596</v>
+        <v>12599</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20379,7 +20395,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20390,7 +20406,7 @@
         <v>1</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20411,20 +20427,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9447</v>
+        <v>9449</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19523</v>
+        <v>19527</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>18894</v>
+        <v>18899</v>
       </c>
       <c r="O349" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20467,12 +20483,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25193</v>
+        <v>25198</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20491,18 +20507,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>15745</v>
+        <v>15889</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>18076</v>
+        <v>18031</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20523,20 +20539,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>15745</v>
+        <v>15749</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31491</v>
+        <v>31498</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20555,18 +20571,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>47137</v>
+        <v>37797</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>44932</v>
+        <v>44227</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20586,21 +20602,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L352" s="3" t="n">
-        <v>44898</v>
-      </c>
-      <c r="M352" s="3" t="n">
-        <v>44898</v>
-      </c>
+      <c r="L352" s="3" t="inlineStr"/>
+      <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="3" t="n">
-        <v>75578</v>
-      </c>
-      <c r="O352" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>75595</v>
+      </c>
+      <c r="O352" s="2" t="inlineStr"/>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20643,12 +20653,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>204690</v>
+        <v>204736</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20702,7 +20712,7 @@
         <v>835</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="N354" s="3" t="n">
         <v>672</v>
@@ -20712,7 +20722,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20753,20 +20763,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>18855</v>
+        <v>18859</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17635</v>
+        <v>17639</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20807,20 +20817,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55109</v>
+        <v>55121</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17635</v>
+        <v>17639</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>61</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20847,10 +20857,10 @@
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
@@ -20871,20 +20881,20 @@
         </is>
       </c>
       <c r="L357" s="3" t="n">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>4843</v>
+        <v>4844</v>
       </c>
       <c r="N357" s="3" t="n">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20958,7 @@
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -20978,7 +20988,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>157.453603</v>
+        <v>157.489371</v>
       </c>
     </row>
     <row r="2">
@@ -20989,7 +20999,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sun, 27 Sep 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Mon, 28 Sep 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21001,7 +21011,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -609,7 +609,7 @@
         <v>4471</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1578151</v>
+        <v>1578204</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6313</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>6313</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>96474</v>
+        <v>96477</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>31</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23672</v>
+        <v>23673</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23672</v>
+        <v>23673</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>47345</v>
+        <v>47346</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -830,18 +830,18 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42610</v>
+        <v>42611</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42649</v>
+        <v>42644</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42610</v>
+        <v>42611</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>42640</v>
+        <v>42641</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85220</v>
+        <v>85223</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -916,20 +916,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>126252</v>
+        <v>126256</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>142034</v>
+        <v>142038</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>252504</v>
+        <v>252513</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>355084</v>
+        <v>355096</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>355084</v>
+        <v>355096</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>710168</v>
+        <v>710192</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1002,18 +1002,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5757</v>
+        <v>6330</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6015</v>
+        <v>6023</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1037,17 +1037,17 @@
         <v>6527</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1578151</v>
+        <v>1578204</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8680</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>9234</v>
+        <v>8330</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8725</v>
+        <v>8713</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1098,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>7959</v>
+        <v>7766</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>149883</v>
+        <v>149888</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>17360</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1134,14 +1134,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13934</v>
+        <v>13936</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1165,17 +1165,17 @@
         <v>13888</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42372</v>
+        <v>42373</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34719</v>
+        <v>34720</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1216,20 +1216,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>24646</v>
+        <v>19306</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39454</v>
+        <v>39455</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22094</v>
+        <v>22095</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1270,20 +1270,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>93772</v>
+        <v>93775</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>93772</v>
+        <v>93775</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22094</v>
+        <v>22095</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>236723</v>
+        <v>236731</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1578151</v>
+        <v>1578204</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>15782</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>29221</v>
+        <v>29222</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>63932</v>
+        <v>63935</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5366</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22490</v>
+        <v>22491</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>63932</v>
+        <v>63935</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5366</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
         <v>789</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1578151</v>
+        <v>1578204</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1578</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         <v>1578</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>227268</v>
+        <v>227276</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3156</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
         <v>3156</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>268286</v>
+        <v>268295</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6313</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22094</v>
+        <v>22095</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>11363</v>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1725,17 +1725,17 @@
         <v>11047</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36881</v>
+        <v>36883</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22094</v>
+        <v>22095</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1776,20 +1776,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21305</v>
+        <v>21306</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>139303</v>
+        <v>139308</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42610</v>
+        <v>42611</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39454</v>
+        <v>39455</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39454</v>
+        <v>39455</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1840,20 +1840,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39454</v>
+        <v>39455</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>320895</v>
+        <v>320906</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>78908</v>
+        <v>78910</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>15782</v>
@@ -1914,11 +1914,11 @@
         <v>1427</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1535</v>
+        <v>1160</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>1070</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1573960</v>
+        <v>1574012</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1578</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1965</v>
+        <v>1945</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2151,20 +2151,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2430</v>
+        <v>1578</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1578151</v>
+        <v>1578204</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3156</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
         <v>3156</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17003</v>
+        <v>17004</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6313</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
         <v>631</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1578151</v>
+        <v>1578204</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1263</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
         <v>11513</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="O31" s="2" t="n">
         <v>59</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1256</v>
+        <v>1334</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1444</v>
+        <v>1310</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>631260</v>
+        <v>631281</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1578</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3156</v>
+        <v>3160</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3650</v>
+        <v>3648</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3166</v>
+        <v>3194</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21095</v>
+        <v>21096</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>6313</v>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2602,17 +2602,17 @@
         <v>6313</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30504</v>
+        <v>30505</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2668,11 +2668,11 @@
         <v>1578</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
         <v>1578</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4147</v>
+        <v>4148</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>3156</v>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2779,10 +2779,10 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>315630</v>
+        <v>315641</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6313</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
         <v>2473</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>144475</v>
+        <v>144480</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3156</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
         <v>3904</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17361</v>
+        <v>17362</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>6313</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2974,17 +2974,17 @@
         <v>6313</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15098</v>
+        <v>15099</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3582</v>
+        <v>3583</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>3870</v>
+        <v>3871</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>6112</v>
@@ -3040,11 +3040,11 @@
         <v>2209</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
         <v>9</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6772</v>
+        <v>6773</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>8869</v>
+        <v>8870</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8869</v>
+        <v>8870</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>8019</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3123,18 +3123,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>10968</v>
+        <v>10531</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10881</v>
+        <v>10813</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3151,20 +3151,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>10533</v>
+        <v>10435</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>13743</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>11505</v>
+        <v>11718</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
         <v>1578</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8700</v>
+        <v>8701</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3156</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3272,17 +3272,17 @@
         <v>3156</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>6313</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
         <v>960</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1578</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="M51" s="3" t="n">
         <v>4354</v>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>4764</v>
+        <v>4765</v>
       </c>
       <c r="M52" s="3" t="n">
         <v>7102</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="L54" s="3" t="n">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="M54" s="3" t="n">
         <v>11270</v>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3796,17 +3796,17 @@
         <v>3156</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30526</v>
+        <v>30527</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>3472</v>
+        <v>3156</v>
       </c>
       <c r="O55" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3863,14 +3863,14 @@
         <v>6794</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>9317</v>
+        <v>9318</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>10324</v>
+        <v>10250</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3921,20 +3921,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9704</v>
+        <v>9610</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30566</v>
+        <v>30567</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3953,18 +3953,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3868</v>
+        <v>3377</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3848</v>
+        <v>3833</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3985,20 +3985,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3590</v>
+        <v>4094</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10302</v>
+        <v>10303</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4517</v>
+        <v>4338</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
         <v>2561</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>2678</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4315,12 +4315,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4363,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42610</v>
+        <v>42611</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4415,14 +4415,14 @@
         <v>18938</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50501</v>
+        <v>50503</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4466,17 +4466,17 @@
         <v>8838</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22094</v>
+        <v>22095</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4519,12 +4519,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22094</v>
+        <v>22095</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
         <v>631</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>5026</v>
+        <v>5027</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>3156</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4740,17 +4740,17 @@
         <v>2525</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1480372</v>
+        <v>1480421</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>11363</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="M73" s="3" t="n">
         <v>7460</v>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
         <v>8680</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20909</v>
+        <v>20910</v>
       </c>
       <c r="N74" s="3" t="n">
         <v>17360</v>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4905,14 +4905,14 @@
         <v>26990</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="L77" s="3" t="n">
-        <v>1184</v>
+        <v>631</v>
       </c>
       <c r="M77" s="3" t="n">
         <v>5175</v>
@@ -5016,11 +5016,11 @@
         <v>631</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>2525</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5180,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5221,20 +5221,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23082</v>
+        <v>23083</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23082</v>
+        <v>23083</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10100</v>
+        <v>10101</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20200</v>
+        <v>20201</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5332,17 +5332,17 @@
         <v>158</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1577993</v>
+        <v>1578046</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>789</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5392,17 +5392,17 @@
         <v>726</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34498</v>
+        <v>34500</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1578</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10100</v>
+        <v>10101</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5585,12 +5585,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14203</v>
+        <v>14204</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5681,20 +5681,20 @@
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="3" t="n">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>85769</v>
+        <v>85772</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>789</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5781,10 +5781,10 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>3156</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10100</v>
+        <v>10101</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14203</v>
+        <v>14204</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
         <v>1596</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="N97" s="3" t="n">
         <v>2841</v>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6235,12 +6235,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6281,20 +6281,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>17929</v>
+        <v>17930</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>17929</v>
+        <v>17930</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42610</v>
+        <v>42611</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50501</v>
+        <v>50503</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6583,12 +6583,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6631,12 +6631,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42610</v>
+        <v>42611</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6679,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50501</v>
+        <v>50503</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6727,12 +6727,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>78908</v>
+        <v>78910</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>86798</v>
+        <v>86801</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>86798</v>
+        <v>86801</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6783,20 +6783,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>86798</v>
+        <v>86801</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>96889</v>
+        <v>96892</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>110471</v>
+        <v>110474</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6837,20 +6837,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>110471</v>
+        <v>110474</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>110471</v>
+        <v>110474</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>142034</v>
+        <v>142038</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6891,20 +6891,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>126252</v>
+        <v>126256</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>126252</v>
+        <v>126256</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6945,20 +6945,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>189378</v>
+        <v>189384</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6999,20 +6999,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>213050</v>
+        <v>213057</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>252504</v>
+        <v>252513</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>252504</v>
+        <v>252513</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
         <v>1682</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="N117" s="3" t="n">
         <v>2209</v>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7107,20 +7107,20 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>5836</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7212,17 +7212,17 @@
         <v>7102</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14203</v>
+        <v>14204</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14203</v>
+        <v>14204</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7265,12 +7265,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22725</v>
+        <v>22726</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7317,14 +7317,14 @@
         <v>15782</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7368,17 +7368,17 @@
         <v>18938</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>40972</v>
+        <v>40973</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7479,14 +7479,14 @@
         <v>5667</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7587,14 +7587,14 @@
         <v>11857</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14203</v>
+        <v>14204</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22725</v>
+        <v>22726</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7685,12 +7685,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7839,14 +7839,14 @@
         <v>6313</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
         <v>9469</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15868</v>
+        <v>15869</v>
       </c>
       <c r="N133" s="3" t="n">
         <v>18938</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7943,12 +7943,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28407</v>
+        <v>28408</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7989,20 +7989,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21305</v>
+        <v>21306</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21305</v>
+        <v>21306</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47345</v>
+        <v>47346</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8043,20 +8043,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28407</v>
+        <v>28408</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28407</v>
+        <v>28408</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71017</v>
+        <v>71019</v>
       </c>
       <c r="O136" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8103,14 +8103,14 @@
         <v>18938</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6321</v>
+        <v>6313</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8164,17 +8164,17 @@
         <v>6313</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12715</v>
+        <v>12716</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O138" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8192,13 +8192,23 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr"/>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="3" t="inlineStr"/>
+      <c r="D139" s="3" t="n">
+        <v>1051</v>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>1051</v>
+      </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
@@ -8215,20 +8225,20 @@
         </is>
       </c>
       <c r="L139" s="3" t="n">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="M139" s="3" t="n">
         <v>1821</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>316</v>
+        <v>1155</v>
       </c>
       <c r="O139" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8247,18 +8257,18 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8279,20 +8289,20 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>579</v>
+        <v>672</v>
       </c>
       <c r="M140" s="3" t="n">
         <v>5153</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>316</v>
+        <v>636</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8356,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8400,7 @@
         <v>1578</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>13455</v>
+        <v>13456</v>
       </c>
       <c r="N142" s="3" t="n">
         <v>316</v>
@@ -8400,7 +8410,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8464,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8508,17 +8518,17 @@
         <v>2052</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10712</v>
+        <v>10713</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="O144" s="2" t="n">
         <v>51</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8561,12 +8571,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8620,7 @@
         <v>4419</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53370</v>
+        <v>53372</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>6313</v>
@@ -8620,7 +8630,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8663,12 +8673,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8732,7 @@
         <v>9469</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17293</v>
+        <v>17294</v>
       </c>
       <c r="N148" s="3" t="n">
         <v>18938</v>
@@ -8732,7 +8742,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8775,12 +8785,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8803,14 +8813,14 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16779</v>
+        <v>16752</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8834,17 +8844,17 @@
         <v>15782</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39454</v>
+        <v>39455</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8863,18 +8873,18 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
         <v>16</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8895,20 +8905,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>63076</v>
+        <v>378611</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75751</v>
+        <v>75754</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -8949,20 +8959,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>102580</v>
+        <v>102583</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>102580</v>
+        <v>102583</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>205160</v>
+        <v>205166</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9016,17 +9026,17 @@
         <v>158</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10324</v>
+        <v>10325</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9080,7 +9090,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9140,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9200,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9260,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9294,17 +9304,17 @@
         <v>789</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1578151</v>
+        <v>1578204</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1578</v>
       </c>
       <c r="O158" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9358,7 @@
         <v>1578</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19138</v>
+        <v>19139</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3156</v>
@@ -9358,7 +9368,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9422,7 @@
         <v>3156</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6601</v>
+        <v>6602</v>
       </c>
       <c r="N160" s="3" t="n">
         <v>6313</v>
@@ -9422,7 +9432,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9440,13 +9450,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr"/>
-      <c r="E161" s="2" t="inlineStr"/>
-      <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="3" t="inlineStr"/>
+      <c r="D161" s="3" t="n">
+        <v>1578</v>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>1578</v>
+      </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
@@ -9469,14 +9489,14 @@
         <v>1578</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>316</v>
+        <v>1736</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9530,17 +9550,17 @@
         <v>1884</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30111</v>
+        <v>30112</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1968</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9611,7 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>2918</v>
+        <v>2718</v>
       </c>
       <c r="M163" s="3" t="n">
         <v>3840</v>
@@ -9604,7 +9624,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9623,18 +9643,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3526</v>
+        <v>3276</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3937</v>
+        <v>3899</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9655,7 +9675,7 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3590</v>
+        <v>3395</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>10258</v>
@@ -9668,7 +9688,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9752,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9806,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9840,17 +9860,17 @@
         <v>1577</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9699</v>
+        <v>9700</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>1510</v>
+        <v>1263</v>
       </c>
       <c r="O167" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9914,7 @@
         <v>1578</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5381</v>
+        <v>5382</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>316</v>
@@ -9904,7 +9924,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9978,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9999,20 +10019,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94689</v>
+        <v>94692</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94689</v>
+        <v>94692</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>126252</v>
+        <v>126256</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10055,12 +10075,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42610</v>
+        <v>42611</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10130,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10150,17 +10170,17 @@
         <v>2699</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10224,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10244,17 +10264,17 @@
         <v>7102</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14173</v>
+        <v>14174</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14203</v>
+        <v>14204</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10297,14 +10317,14 @@
         <v>11363</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22725</v>
+        <v>22726</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10344,17 +10364,17 @@
         <v>15782</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>15860</v>
+        <v>15861</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10397,14 +10417,14 @@
         <v>19096</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10472,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10526,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10569,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10628,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10651,12 +10671,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28407</v>
+        <v>28408</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10697,20 +10717,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21305</v>
+        <v>21306</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21305</v>
+        <v>21306</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42610</v>
+        <v>42611</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10751,20 +10771,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28407</v>
+        <v>28408</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28407</v>
+        <v>28408</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56813</v>
+        <v>56815</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10828,7 @@
         <v>158</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>316</v>
@@ -10818,7 +10838,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10882,7 @@
         <v>158</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>316</v>
@@ -10872,7 +10892,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10936,7 @@
         <v>158</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102678</v>
+        <v>102681</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>316</v>
@@ -10926,7 +10946,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10994,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11048,7 @@
         <v>158</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29107</v>
+        <v>29108</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>316</v>
@@ -11038,7 +11058,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11102,7 @@
         <v>158</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>155816</v>
+        <v>155821</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>316</v>
@@ -11092,7 +11112,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11166,7 @@
         <v>158</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>316</v>
@@ -11156,7 +11176,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11224,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11268,7 @@
         <v>158</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>316</v>
@@ -11258,7 +11278,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11332,7 @@
         <v>158</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>316</v>
@@ -11322,7 +11342,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11396,7 @@
         <v>158</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>316</v>
@@ -11386,7 +11406,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11454,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11452,13 +11472,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D198" s="3" t="inlineStr"/>
-      <c r="E198" s="2" t="inlineStr"/>
-      <c r="F198" s="2" t="inlineStr"/>
-      <c r="G198" s="3" t="inlineStr"/>
+      <c r="D198" s="3" t="n">
+        <v>855</v>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>855</v>
+      </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I198" s="2" t="n">
@@ -11475,20 +11505,20 @@
         </is>
       </c>
       <c r="L198" s="3" t="n">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="M198" s="3" t="n">
         <v>15782</v>
       </c>
       <c r="N198" s="3" t="n">
-        <v>316</v>
+        <v>941</v>
       </c>
       <c r="O198" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11535,14 +11565,14 @@
         <v>20551</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11596,7 +11626,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11680,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11694,17 +11724,17 @@
         <v>6313</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10327</v>
+        <v>10328</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10100</v>
+        <v>10101</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11745,10 +11775,10 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8206</v>
+        <v>8207</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>275498</v>
+        <v>275507</v>
       </c>
       <c r="N203" s="3" t="n">
         <v>13888</v>
@@ -11758,7 +11788,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11842,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11861,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>20200</v>
+        <v>20201</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -11842,7 +11872,7 @@
         <v>1</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>20200</v>
+        <v>20201</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -11863,20 +11893,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20200</v>
+        <v>37541</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>48684</v>
+        <v>48686</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="O205" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11949,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22725</v>
+        <v>22726</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11984,11 +12014,11 @@
         <v>316</v>
       </c>
       <c r="O207" s="2" t="n">
-        <v>678</v>
+        <v>638</v>
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12082,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12123,7 @@
         </is>
       </c>
       <c r="L209" s="3" t="n">
-        <v>1780</v>
+        <v>1775</v>
       </c>
       <c r="M209" s="3" t="n">
         <v>2995</v>
@@ -12102,11 +12132,11 @@
         <v>2209</v>
       </c>
       <c r="O209" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12190,7 @@
         <v>2052</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4461</v>
+        <v>4462</v>
       </c>
       <c r="N210" s="3" t="n">
         <v>4103</v>
@@ -12170,7 +12200,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12211,7 +12241,7 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="M211" s="3" t="n">
         <v>7891</v>
@@ -12224,7 +12254,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12271,14 +12301,14 @@
         <v>7102</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14203</v>
+        <v>14204</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12321,12 +12351,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22725</v>
+        <v>22726</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12373,14 +12403,14 @@
         <v>15782</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12454,7 @@
         <v>1105</v>
       </c>
       <c r="M215" s="3" t="n">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="N215" s="3" t="n">
         <v>2209</v>
@@ -12434,7 +12464,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12508,7 @@
         <v>2052</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11850</v>
+        <v>11851</v>
       </c>
       <c r="N216" s="3" t="n">
         <v>4103</v>
@@ -12488,7 +12518,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12529,20 +12559,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15538</v>
+        <v>15539</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>29281</v>
+        <v>29282</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12561,7 +12591,7 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
@@ -12572,7 +12602,7 @@
         <v>1</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -12596,7 +12626,7 @@
         <v>4853</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>4865</v>
+        <v>4866</v>
       </c>
       <c r="N218" s="3" t="n">
         <v>7891</v>
@@ -12606,7 +12636,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12653,14 +12683,14 @@
         <v>7102</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14203</v>
+        <v>14204</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12703,12 +12733,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12755,14 +12785,14 @@
         <v>18938</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12846,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12900,7 @@
         <v>1578</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>4038</v>
+        <v>4039</v>
       </c>
       <c r="N223" s="3" t="n">
         <v>3156</v>
@@ -12880,7 +12910,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12974,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13038,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13092,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13126,7 +13156,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13200,7 @@
         <v>158</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>316</v>
@@ -13180,7 +13210,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13254,7 @@
         <v>158</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>316</v>
@@ -13234,7 +13264,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13308,7 @@
         <v>158</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>316</v>
@@ -13288,7 +13318,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13362,17 @@
         <v>789</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1578</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13436,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13460,7 +13490,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13524,7 +13554,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13588,7 +13618,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13629,20 +13659,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6508</v>
+        <v>6509</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13685,12 +13715,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13744,7 +13774,7 @@
         <v>8838</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11001</v>
+        <v>11002</v>
       </c>
       <c r="N238" s="3" t="n">
         <v>6313</v>
@@ -13754,7 +13784,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13797,12 +13827,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13890,7 @@
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13911,20 +13941,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>19435</v>
+        <v>19436</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30575</v>
+        <v>30576</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -13943,7 +13973,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>41901</v>
+        <v>41903</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -13954,7 +13984,7 @@
         <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>39889</v>
+        <v>39890</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -13975,20 +14005,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>58474</v>
+        <v>58476</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58474</v>
+        <v>58476</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75751</v>
+        <v>75754</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14037,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>21862</v>
+        <v>21863</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14035,20 +14065,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>20383</v>
+        <v>20283</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31563022</v>
+        <v>31564070</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14091,12 +14121,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14180,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14199,7 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
@@ -14214,7 +14244,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14255,20 +14285,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15497</v>
+        <v>15498</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23268</v>
+        <v>23269</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17675</v>
+        <v>17676</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14321,12 +14351,12 @@
       <c r="L248" s="3" t="inlineStr"/>
       <c r="M248" s="3" t="inlineStr"/>
       <c r="N248" s="3" t="n">
-        <v>17675</v>
+        <v>17676</v>
       </c>
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14406,7 @@
         <v>789</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9265</v>
+        <v>9266</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1578</v>
@@ -14386,7 +14416,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14466,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14510,7 @@
         <v>158</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97042</v>
+        <v>97045</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>316</v>
@@ -14490,7 +14520,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14531,10 +14561,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50286</v>
+        <v>50288</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50286</v>
+        <v>50288</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6313</v>
@@ -14544,7 +14574,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14628,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14651,12 +14681,12 @@
       <c r="L254" s="3" t="inlineStr"/>
       <c r="M254" s="3" t="inlineStr"/>
       <c r="N254" s="3" t="n">
-        <v>10100</v>
+        <v>10101</v>
       </c>
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14740,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14764,7 +14794,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14818,7 +14848,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14841,14 +14871,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -14878,11 +14908,11 @@
         <v>631</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -14901,18 +14931,18 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>1215</v>
+        <v>789</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>1002</v>
+        <v>931</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -14936,7 +14966,7 @@
         <v>1215</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21341</v>
+        <v>21342</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1578</v>
@@ -14946,7 +14976,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15030,7 @@
         <v>2620</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3664</v>
+        <v>3665</v>
       </c>
       <c r="N260" s="3" t="n">
         <v>3156</v>
@@ -15010,7 +15040,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15104,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15131,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G262" s="3" t="n">
         <v>6313</v>
@@ -15128,17 +15158,17 @@
         <v>6313</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15232,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15296,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15344,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15337,11 +15367,11 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G266" s="3" t="n">
         <v>6313</v>
@@ -15365,20 +15395,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6313</v>
+        <v>9618</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9617</v>
+        <v>9618</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O266" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15472,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15523,7 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8206</v>
+        <v>8207</v>
       </c>
       <c r="M268" s="3" t="n">
         <v>14216</v>
@@ -15506,7 +15536,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15554,7 +15584,7 @@
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15597,12 +15627,12 @@
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15621,7 +15651,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>22878</v>
+        <v>22879</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15632,7 +15662,7 @@
         <v>2</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>21539</v>
+        <v>21540</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15653,20 +15683,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>20200</v>
+        <v>20201</v>
       </c>
       <c r="M271" s="3" t="n">
         <v>22882</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15710,7 +15740,7 @@
         <v>158</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>316</v>
@@ -15720,7 +15750,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15764,7 +15794,7 @@
         <v>158</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>20901</v>
+        <v>20902</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>316</v>
@@ -15774,7 +15804,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15828,7 +15858,7 @@
         <v>158</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31667</v>
+        <v>31668</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>316</v>
@@ -15838,7 +15868,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15922,7 @@
         <v>158</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15860</v>
+        <v>15861</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>316</v>
@@ -15902,7 +15932,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15956,7 +15986,7 @@
         <v>158</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>157340</v>
+        <v>157345</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>316</v>
@@ -15966,7 +15996,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16016,7 +16046,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16110,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16164,7 @@
         <v>5050</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9874</v>
+        <v>9875</v>
       </c>
       <c r="N279" s="3" t="n">
         <v>7575</v>
@@ -16144,7 +16174,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16188,17 +16218,17 @@
         <v>6313</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8588</v>
+        <v>8589</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10100</v>
+        <v>10101</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16276,7 @@
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16324,7 @@
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16367,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16383,20 +16413,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>20200</v>
+        <v>33650</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33649</v>
+        <v>33650</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="O284" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16415,18 +16445,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>7973</v>
+        <v>8653</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>8591</v>
+        <v>8587</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16447,20 +16477,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>8281</v>
+        <v>9154</v>
       </c>
       <c r="M285" s="3" t="n">
         <v>15782</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>9289</v>
+        <v>9365</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16554,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16570,15 +16600,21 @@
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
-      <c r="L287" s="3" t="inlineStr"/>
-      <c r="M287" s="3" t="inlineStr"/>
+      <c r="L287" s="3" t="n">
+        <v>7765</v>
+      </c>
+      <c r="M287" s="3" t="n">
+        <v>7765</v>
+      </c>
       <c r="N287" s="3" t="n">
-        <v>5602</v>
-      </c>
-      <c r="O287" s="2" t="inlineStr"/>
+        <v>5544</v>
+      </c>
+      <c r="O287" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16605,10 +16641,10 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>7323</v>
+        <v>7289</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16625,20 +16661,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7278</v>
+        <v>6794</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>7443</v>
+        <v>7668</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7348</v>
+        <v>7395</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16693,7 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9235</v>
+        <v>9236</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
@@ -16665,10 +16701,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>10331</v>
+        <v>10256</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16684,15 +16720,21 @@
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr"/>
-      <c r="L289" s="3" t="inlineStr"/>
-      <c r="M289" s="3" t="inlineStr"/>
+      <c r="L289" s="3" t="n">
+        <v>11649</v>
+      </c>
+      <c r="M289" s="3" t="n">
+        <v>11649</v>
+      </c>
       <c r="N289" s="3" t="n">
-        <v>11372</v>
-      </c>
-      <c r="O289" s="2" t="inlineStr"/>
+        <v>11373</v>
+      </c>
+      <c r="O289" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16733,7 +16775,7 @@
         </is>
       </c>
       <c r="L290" s="3" t="n">
-        <v>2329</v>
+        <v>2445</v>
       </c>
       <c r="M290" s="3" t="n">
         <v>3156</v>
@@ -16742,11 +16784,11 @@
         <v>1578</v>
       </c>
       <c r="O290" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16852,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16829,18 +16871,18 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>5050</v>
+        <v>4271</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4263</v>
+        <v>4265</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16864,7 +16906,7 @@
         <v>5162</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="N292" s="3" t="n">
         <v>6313</v>
@@ -16874,7 +16916,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16980,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16965,10 +17007,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7566</v>
+        <v>7596</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -16989,20 +17031,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>9706</v>
+        <v>8541</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>21474</v>
+        <v>21475</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>7398</v>
+        <v>7399</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17043,20 +17085,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51295</v>
+        <v>51296</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>697134</v>
+        <v>697157</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39454</v>
+        <v>39455</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17075,7 +17117,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17083,10 +17125,10 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17107,20 +17149,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68616</v>
+        <v>68619</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39454</v>
+        <v>39455</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17139,7 +17181,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63126</v>
+        <v>63128</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17150,7 +17192,7 @@
         <v>5</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63126</v>
+        <v>63128</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17171,20 +17213,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63126</v>
+        <v>63128</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>126252</v>
+        <v>126256</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>78908</v>
+        <v>78910</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17225,20 +17267,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>126252</v>
+        <v>126256</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>126517</v>
+        <v>126521</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>157815</v>
+        <v>157820</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17299,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>252504</v>
+        <v>252513</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17268,7 +17310,7 @@
         <v>2</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>252504</v>
+        <v>252513</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17289,20 +17331,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>252504</v>
+        <v>252513</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>252506</v>
+        <v>252514</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>315630</v>
+        <v>315641</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17321,7 +17363,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>441882</v>
+        <v>441897</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17332,7 +17374,7 @@
         <v>3</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>441882</v>
+        <v>441897</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17353,20 +17395,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>441882</v>
+        <v>441897</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>818282</v>
+        <v>949679</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>631260</v>
+        <v>631281</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17385,18 +17427,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>1875</v>
+        <v>1845</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2638</v>
+        <v>2620</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17423,14 +17465,14 @@
         <v>18938</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2918</v>
+        <v>2898</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17536,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17555,7 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4341</v>
+        <v>4387</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -17524,7 +17566,7 @@
         <v>23</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4162</v>
+        <v>4164</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17545,20 +17587,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4480</v>
+        <v>4555</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15674</v>
+        <v>15675</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4498</v>
+        <v>4593</v>
       </c>
       <c r="O303" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17581,14 +17623,14 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17609,7 +17651,7 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>1105</v>
+        <v>1536</v>
       </c>
       <c r="M304" s="3" t="n">
         <v>18938</v>
@@ -17618,11 +17660,11 @@
         <v>2209</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17718,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17782,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17758,13 +17800,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D307" s="3" t="inlineStr"/>
-      <c r="E307" s="2" t="inlineStr"/>
-      <c r="F307" s="2" t="inlineStr"/>
-      <c r="G307" s="3" t="inlineStr"/>
+      <c r="D307" s="3" t="n">
+        <v>917</v>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G307" s="3" t="n">
+        <v>917</v>
+      </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I307" s="2" t="n">
@@ -17781,20 +17833,20 @@
         </is>
       </c>
       <c r="L307" s="3" t="n">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="M307" s="3" t="n">
         <v>15782</v>
       </c>
       <c r="N307" s="3" t="n">
-        <v>316</v>
+        <v>1008</v>
       </c>
       <c r="O307" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17821,10 +17873,10 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G308" s="3" t="n">
-        <v>2322</v>
+        <v>2367</v>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
@@ -17848,17 +17900,17 @@
         <v>2052</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1262521</v>
+        <v>1262563</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="O308" s="2" t="n">
         <v>231</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17912,7 +17964,7 @@
         <v>4419</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>31910</v>
+        <v>31911</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6313</v>
@@ -17922,7 +17974,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17941,18 +17993,18 @@
         </is>
       </c>
       <c r="D310" s="3" t="n">
-        <v>1578</v>
+        <v>1640</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G310" s="3" t="n">
-        <v>1578</v>
+        <v>1609</v>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
@@ -17973,7 +18025,7 @@
         </is>
       </c>
       <c r="L310" s="3" t="n">
-        <v>1578</v>
+        <v>1888</v>
       </c>
       <c r="M310" s="3" t="n">
         <v>6013</v>
@@ -17982,11 +18034,11 @@
         <v>3156</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18043,14 +18095,14 @@
         <v>6022</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18093,12 +18145,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18204,7 @@
         <v>9469</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26093</v>
+        <v>26094</v>
       </c>
       <c r="N313" s="3" t="n">
         <v>18938</v>
@@ -18162,7 +18214,7 @@
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18203,20 +18255,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15439</v>
+        <v>15440</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15439</v>
+        <v>15440</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18239,11 +18291,11 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G315" s="3" t="n">
         <v>15782</v>
@@ -18270,17 +18322,17 @@
         <v>15782</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1578151</v>
+        <v>1578204</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18299,18 +18351,18 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18331,20 +18383,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>37876</v>
+        <v>37877</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75751</v>
+        <v>75754</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18415,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>102580</v>
+        <v>102583</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18374,7 +18426,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>102580</v>
+        <v>102583</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18395,20 +18447,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>102580</v>
+        <v>102583</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>102580</v>
+        <v>102583</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>205160</v>
+        <v>205166</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18431,14 +18483,14 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>797</v>
+        <v>810</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18468,11 +18520,11 @@
         <v>963</v>
       </c>
       <c r="O318" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18491,18 +18543,18 @@
         </is>
       </c>
       <c r="D319" s="3" t="n">
-        <v>1341</v>
+        <v>1390</v>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F319" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G319" s="3" t="n">
-        <v>1341</v>
+        <v>1366</v>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
@@ -18526,17 +18578,17 @@
         <v>1390</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15674</v>
+        <v>15675</v>
       </c>
       <c r="N319" s="3" t="n">
-        <v>316</v>
+        <v>1529</v>
       </c>
       <c r="O319" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18593,14 +18645,14 @@
         <v>9805</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2303</v>
+        <v>2282</v>
       </c>
       <c r="O320" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18619,18 +18671,18 @@
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>3281</v>
+        <v>2842</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F321" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3152</v>
+        <v>3172</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18657,14 +18709,14 @@
         <v>5869</v>
       </c>
       <c r="N321" s="3" t="n">
-        <v>3608</v>
+        <v>3368</v>
       </c>
       <c r="O321" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18683,18 +18735,18 @@
         </is>
       </c>
       <c r="D322" s="3" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F322" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G322" s="3" t="n">
-        <v>570</v>
+        <v>534</v>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
@@ -18715,7 +18767,7 @@
         </is>
       </c>
       <c r="L322" s="3" t="n">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="M322" s="3" t="n">
         <v>1034</v>
@@ -18724,11 +18776,11 @@
         <v>469</v>
       </c>
       <c r="O322" s="2" t="n">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18779,7 +18831,7 @@
         </is>
       </c>
       <c r="L323" s="3" t="n">
-        <v>2232</v>
+        <v>1649</v>
       </c>
       <c r="M323" s="3" t="n">
         <v>18938</v>
@@ -18792,7 +18844,7 @@
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18846,7 +18898,7 @@
         <v>316</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5580</v>
+        <v>5581</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>316</v>
@@ -18856,7 +18908,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18875,18 +18927,18 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>2628</v>
+        <v>3267</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2699</v>
+        <v>2725</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18907,20 +18959,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>3224</v>
+        <v>2863</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15674</v>
+        <v>15675</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2948</v>
+        <v>3131</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -18971,7 +19023,7 @@
         </is>
       </c>
       <c r="L326" s="3" t="n">
-        <v>2131</v>
+        <v>2014</v>
       </c>
       <c r="M326" s="3" t="n">
         <v>15782</v>
@@ -18980,11 +19032,11 @@
         <v>2209</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19048,7 +19100,7 @@
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19119,7 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>24297</v>
+        <v>24298</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
@@ -19099,10 +19151,10 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>24296</v>
+        <v>24290</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>32527</v>
+        <v>32528</v>
       </c>
       <c r="N328" s="3" t="n">
         <v>22863</v>
@@ -19112,7 +19164,7 @@
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19131,18 +19183,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>6791</v>
+        <v>6018</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7137</v>
+        <v>7102</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19163,20 +19215,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>6892</v>
+        <v>6212</v>
       </c>
       <c r="M329" s="3" t="n">
         <v>9747</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7409</v>
+        <v>7324</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19195,7 +19247,7 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -19227,20 +19279,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5716</v>
+        <v>4851</v>
       </c>
       <c r="M330" s="3" t="n">
         <v>8636</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6197</v>
+        <v>6111</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19258,13 +19310,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D331" s="3" t="inlineStr"/>
-      <c r="E331" s="2" t="inlineStr"/>
-      <c r="F331" s="2" t="inlineStr"/>
-      <c r="G331" s="3" t="inlineStr"/>
+      <c r="D331" s="3" t="n">
+        <v>1117</v>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G331" s="3" t="n">
+        <v>1117</v>
+      </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I331" s="2" t="n">
@@ -19287,14 +19349,14 @@
         <v>3156</v>
       </c>
       <c r="N331" s="3" t="n">
-        <v>316</v>
+        <v>1228</v>
       </c>
       <c r="O331" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19313,18 +19375,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1107</v>
+        <v>1151</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19351,14 +19413,14 @@
         <v>15782</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1605</v>
+        <v>1673</v>
       </c>
       <c r="O332" s="2" t="n">
         <v>176</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19385,10 +19447,10 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>799</v>
+        <v>858</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19422,7 +19484,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19441,18 +19503,18 @@
         </is>
       </c>
       <c r="D334" s="3" t="n">
-        <v>423</v>
+        <v>521</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19476,17 +19538,17 @@
         <v>521</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9399</v>
+        <v>9400</v>
       </c>
       <c r="N334" s="3" t="n">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="O334" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19537,7 +19599,7 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>2725</v>
+        <v>2426</v>
       </c>
       <c r="M335" s="3" t="n">
         <v>15782</v>
@@ -19546,11 +19608,11 @@
         <v>2209</v>
       </c>
       <c r="O335" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19569,7 +19631,7 @@
         </is>
       </c>
       <c r="D336" s="3" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
@@ -19577,10 +19639,10 @@
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19601,20 +19663,20 @@
         </is>
       </c>
       <c r="L336" s="3" t="n">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="M336" s="3" t="n">
         <v>2891</v>
       </c>
       <c r="N336" s="3" t="n">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19674,11 +19736,11 @@
         <v>316</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19705,10 +19767,10 @@
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G338" s="3" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
@@ -19742,7 +19804,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19823,7 @@
         </is>
       </c>
       <c r="D339" s="3" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
@@ -19772,7 +19834,7 @@
         <v>16</v>
       </c>
       <c r="G339" s="3" t="n">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
@@ -19793,20 +19855,20 @@
         </is>
       </c>
       <c r="L339" s="3" t="n">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="M339" s="3" t="n">
         <v>4700</v>
       </c>
       <c r="N339" s="3" t="n">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="O339" s="2" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19825,18 +19887,18 @@
         </is>
       </c>
       <c r="D340" s="3" t="n">
-        <v>971</v>
+        <v>1038</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F340" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G340" s="3" t="n">
-        <v>883</v>
+        <v>831</v>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
@@ -19863,14 +19925,14 @@
         <v>3156</v>
       </c>
       <c r="N340" s="3" t="n">
-        <v>1067</v>
+        <v>1105</v>
       </c>
       <c r="O340" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19893,14 +19955,14 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>850</v>
+        <v>867</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19921,20 +19983,20 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>955</v>
+        <v>1531</v>
       </c>
       <c r="M341" s="3" t="n">
         <v>2427</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>1064</v>
+        <v>1095</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19998,7 +20060,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20025,10 +20087,10 @@
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
@@ -20062,7 +20124,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20081,7 +20143,7 @@
         </is>
       </c>
       <c r="D344" s="3" t="n">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
@@ -20116,7 +20178,7 @@
         <v>2235</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57565</v>
+        <v>57567</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3156</v>
@@ -20126,7 +20188,7 @@
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20153,10 +20215,10 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>2340</v>
+        <v>2352</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20180,17 +20242,17 @@
         <v>2052</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>75628</v>
+        <v>75631</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="O345" s="2" t="n">
         <v>85</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20243,12 +20305,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20312,7 +20374,7 @@
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20369,14 +20431,14 @@
         <v>9469</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12625</v>
+        <v>12626</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20430,7 +20492,7 @@
         <v>9469</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19567</v>
+        <v>19568</v>
       </c>
       <c r="N349" s="3" t="n">
         <v>18938</v>
@@ -20440,7 +20502,7 @@
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20483,12 +20545,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25250</v>
+        <v>25251</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20507,18 +20569,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>16695</v>
+        <v>17367</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17894</v>
+        <v>17561</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20539,20 +20601,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>16017</v>
+        <v>15782</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31563</v>
+        <v>31564</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20571,18 +20633,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>37876</v>
+        <v>41152</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>44135</v>
+        <v>43635</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20603,20 +20665,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>41150</v>
+        <v>41062</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>44165</v>
+        <v>44166</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>75751</v>
+        <v>75754</v>
       </c>
       <c r="O352" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20657,20 +20719,20 @@
         </is>
       </c>
       <c r="L353" s="3" t="n">
-        <v>116485</v>
+        <v>116489</v>
       </c>
       <c r="M353" s="3" t="n">
-        <v>116485</v>
+        <v>116489</v>
       </c>
       <c r="N353" s="3" t="n">
-        <v>205160</v>
+        <v>205166</v>
       </c>
       <c r="O353" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20727,14 +20789,14 @@
         <v>1416</v>
       </c>
       <c r="N354" s="3" t="n">
-        <v>781</v>
+        <v>316</v>
       </c>
       <c r="O354" s="2" t="n">
         <v>320</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20778,17 +20840,17 @@
         <v>8838</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>18898</v>
+        <v>18899</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17675</v>
+        <v>17676</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20832,17 +20894,17 @@
         <v>8838</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55235</v>
+        <v>55237</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17675</v>
+        <v>17676</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>67</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20861,18 +20923,18 @@
         </is>
       </c>
       <c r="D357" s="3" t="n">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
@@ -20893,20 +20955,20 @@
         </is>
       </c>
       <c r="L357" s="3" t="n">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>4854</v>
+        <v>4855</v>
       </c>
       <c r="N357" s="3" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -20963,14 +21025,14 @@
         <v>767</v>
       </c>
       <c r="N358" s="3" t="n">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O358" s="2" t="n">
         <v>804</v>
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21062,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>157.81511</v>
+        <v>157.820352</v>
       </c>
     </row>
     <row r="2">
@@ -21011,7 +21073,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 03 Oct 2026 00:02:32 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 04 Oct 2026 00:02:32 +0000)</t>
         </is>
       </c>
     </row>
@@ -21023,7 +21085,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3638</v>
+        <v>3607</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>3166</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1582858</v>
+        <v>1582873</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6331</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         <v>6331</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>96762</v>
+        <v>96763</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>12663</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>25326</v>
+        <v>23743</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>25326</v>
@@ -807,11 +807,11 @@
         <v>47486</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -830,18 +830,18 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42765</v>
+        <v>42766</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85474</v>
+        <v>85475</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -916,20 +916,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>126629</v>
+        <v>126630</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>142457</v>
+        <v>142459</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>253257</v>
+        <v>253260</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>356143</v>
+        <v>356146</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>356143</v>
+        <v>356146</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>712286</v>
+        <v>712293</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1002,18 +1002,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6309</v>
+        <v>6648</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>39</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6136</v>
+        <v>6159</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5823</v>
+        <v>7087</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1582858</v>
+        <v>1582873</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8706</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8334</v>
+        <v>8085</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8714</v>
+        <v>8675</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1098,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8145</v>
+        <v>8125</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>150330</v>
+        <v>150332</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17411</v>
+        <v>17412</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14119</v>
+        <v>14134</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1162,20 +1162,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>16525</v>
+        <v>15048</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42498</v>
+        <v>42499</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>34823</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
         <v>39570</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39571</v>
+        <v>39572</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>22160</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>94052</v>
+        <v>94053</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>94052</v>
+        <v>94053</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>22160</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>237429</v>
+        <v>237431</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1582858</v>
+        <v>1582873</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>15829</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
         <v>29308</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64123</v>
+        <v>64124</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5382</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22557</v>
+        <v>22558</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64123</v>
+        <v>64124</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5382</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
         <v>791</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1582858</v>
+        <v>1582873</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1583</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         <v>1583</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>227946</v>
+        <v>227948</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3166</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
         <v>3166</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>269086</v>
+        <v>269088</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6331</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
         <v>11080</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36991</v>
+        <v>36992</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>22160</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1779,17 +1779,17 @@
         <v>21369</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>139719</v>
+        <v>139720</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39571</v>
+        <v>39572</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39571</v>
+        <v>39572</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1840,20 +1840,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39571</v>
+        <v>39572</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>321852</v>
+        <v>321855</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>79143</v>
+        <v>79144</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2032,11 +2032,11 @@
         <v>2533</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2055,18 +2055,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1075</v>
+        <v>1265</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>989</v>
+        <v>1011</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2087,20 +2087,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1578654</v>
+        <v>1578669</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1583</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1961</v>
+        <v>1978</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2154,17 +2154,17 @@
         <v>1583</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1582858</v>
+        <v>1582873</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3166</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2224,11 +2224,11 @@
         <v>6331</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
         <v>633</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1582858</v>
+        <v>1582873</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1266</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>2374</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
         <v>1314</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>633143</v>
+        <v>633149</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1583</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2356</v>
+        <v>2334</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2503,18 +2503,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3476</v>
+        <v>3204</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>51</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3572</v>
+        <v>3573</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3592</v>
+        <v>3495</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>21158</v>
@@ -2544,11 +2544,11 @@
         <v>6331</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6331</v>
@@ -2608,11 +2608,11 @@
         <v>12663</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
         <v>3166</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>316572</v>
+        <v>316575</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6331</v>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
         <v>1583</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>144906</v>
+        <v>144907</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3166</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>3747</v>
+        <v>3166</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>17413</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>6331</v>
@@ -2970,11 +2970,11 @@
         <v>12663</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>8896</v>
+        <v>7572</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>8896</v>
@@ -3090,11 +3090,11 @@
         <v>3957</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3113,18 +3113,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9459</v>
+        <v>9223</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10393</v>
+        <v>10308</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3141,20 +3141,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9689</v>
+        <v>9679</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>13784</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10550</v>
+        <v>10387</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3172,13 +3172,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="n">
+        <v>1583</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>1583</v>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -3204,11 +3214,11 @@
         <v>3166</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3268,11 +3278,11 @@
         <v>6331</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3336,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3400,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3454,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3504,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3564,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3624,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3688,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3742,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3796,7 @@
         <v>3166</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30617</v>
+        <v>30618</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3166</v>
@@ -3796,7 +3806,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3815,18 +3825,18 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>8497</v>
+        <v>5825</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>8642</v>
+        <v>7983</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3846,21 +3856,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L56" s="3" t="n">
-        <v>5825</v>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>5825</v>
-      </c>
+      <c r="L56" s="3" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="3" t="n">
-        <v>6331</v>
-      </c>
-      <c r="O56" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>6407</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3879,18 +3883,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>8981</v>
+        <v>9804</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9974</v>
+        <v>9970</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3911,7 +3915,7 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>8741</v>
+        <v>9708</v>
       </c>
       <c r="M57" s="3" t="n">
         <v>30657</v>
@@ -3924,7 +3928,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3943,18 +3947,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3861</v>
+        <v>2912</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3830</v>
+        <v>3814</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3975,20 +3979,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3397</v>
+        <v>3202</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>10333</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3914</v>
+        <v>3889</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4042,17 +4046,17 @@
         <v>2566</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11317</v>
+        <v>11318</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4110,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4164,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4212,7 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4266,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4314,7 @@
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4353,12 +4357,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4405,14 +4409,14 @@
         <v>18994</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50651</v>
+        <v>50652</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4470,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4518,7 @@
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4582,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4636,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4680,7 @@
         <v>4199</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>5033</v>
+        <v>5034</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>6331</v>
@@ -4686,7 +4690,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4734,7 @@
         <v>2533</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1484787</v>
+        <v>1484801</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>11397</v>
@@ -4740,7 +4744,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4798,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4841,14 +4845,14 @@
         <v>20971</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17411</v>
+        <v>17412</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4893,7 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17411</v>
+        <v>17412</v>
       </c>
       <c r="M75" s="3" t="n">
         <v>27070</v>
@@ -4902,7 +4906,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4970,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5024,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5082,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5136,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5184,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5238,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5286,7 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5332,17 +5336,17 @@
         <v>158</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1582700</v>
+        <v>1582714</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>791</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5396,7 @@
         <v>388</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34601</v>
+        <v>34602</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1583</v>
@@ -5402,7 +5406,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5466,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5526,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5570,7 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5614,7 @@
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5649,12 +5653,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17411</v>
+        <v>17412</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5708,7 @@
         <v>495</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>86025</v>
+        <v>86026</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>791</v>
@@ -5714,7 +5718,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5768,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5818,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5868,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5912,7 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5956,7 @@
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -5991,12 +5995,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17411</v>
+        <v>17412</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6054,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6108,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6162,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6216,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6264,7 @@
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6307,14 +6311,14 @@
         <v>17983</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6357,12 +6361,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50651</v>
+        <v>50652</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6420,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6468,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6516,7 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6564,7 @@
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6612,7 @@
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6655,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6699,12 +6703,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50651</v>
+        <v>50652</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6751,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>79143</v>
+        <v>79144</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6775,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>87057</v>
+        <v>87058</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6786,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>87057</v>
+        <v>87058</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6803,20 +6807,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>87057</v>
+        <v>87058</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>97178</v>
+        <v>97179</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>110800</v>
+        <v>110801</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6839,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>110800</v>
+        <v>110801</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -6846,7 +6850,7 @@
         <v>1</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>110800</v>
+        <v>110801</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6867,20 +6871,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>110800</v>
+        <v>110801</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>110800</v>
+        <v>110801</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>142457</v>
+        <v>142459</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6921,20 +6925,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>126629</v>
+        <v>126630</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>126629</v>
+        <v>126630</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -6975,20 +6979,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>189943</v>
+        <v>189945</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7029,20 +7033,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>213686</v>
+        <v>213688</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>253257</v>
+        <v>253260</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>253257</v>
+        <v>253260</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7100,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7154,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7202,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7256,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7304,7 @@
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7358,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7402,7 @@
         <v>18994</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>41094</v>
+        <v>41095</v>
       </c>
       <c r="N123" s="3" t="n">
         <v>37989</v>
@@ -7408,7 +7412,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7466,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7520,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7574,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7628,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7676,7 @@
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7724,7 @@
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7772,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7826,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7880,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7934,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7973,12 +7977,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28491</v>
+        <v>28492</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8032,7 +8036,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8073,10 +8077,10 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28491</v>
+        <v>28492</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28491</v>
+        <v>28492</v>
       </c>
       <c r="N136" s="3" t="n">
         <v>71229</v>
@@ -8086,7 +8090,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8144,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8208,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8261,14 +8265,14 @@
         <v>1827</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>1159</v>
+        <v>317</v>
       </c>
       <c r="O139" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8325,14 +8329,14 @@
         <v>5168</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>690</v>
+        <v>741</v>
       </c>
       <c r="O140" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8363,7 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" s="3" t="n">
         <v>1583</v>
@@ -8392,11 +8396,11 @@
         <v>1741</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8444,7 @@
         <v>1583</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>13495</v>
+        <v>13496</v>
       </c>
       <c r="N142" s="3" t="n">
         <v>317</v>
@@ -8450,7 +8454,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8508,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8531,10 +8535,10 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2099</v>
+        <v>2113</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8558,7 +8562,7 @@
         <v>2145</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10744</v>
+        <v>10745</v>
       </c>
       <c r="N144" s="3" t="n">
         <v>3957</v>
@@ -8568,7 +8572,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8620,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8664,7 @@
         <v>4432</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53529</v>
+        <v>53530</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>6331</v>
@@ -8670,7 +8674,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8722,7 @@
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8776,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8824,7 @@
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8847,10 +8851,10 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16889</v>
+        <v>16888</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8874,17 +8878,17 @@
         <v>15829</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39571</v>
+        <v>39572</v>
       </c>
       <c r="N150" s="3" t="n">
         <v>31657</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8915,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>37989</v>
@@ -8941,14 +8945,14 @@
         <v>63264</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75977</v>
+        <v>75978</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8989,20 +8993,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>102886</v>
+        <v>102887</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>102886</v>
+        <v>102887</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>205772</v>
+        <v>205773</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9070,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9134,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9184,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9236,11 +9240,11 @@
         <v>3166</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9304,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9348,7 @@
         <v>791</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1582858</v>
+        <v>1582873</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1583</v>
@@ -9354,7 +9358,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9404,11 +9408,11 @@
         <v>3166</v>
       </c>
       <c r="O159" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9466,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9519,14 +9523,14 @@
         <v>1583</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>1741</v>
+        <v>317</v>
       </c>
       <c r="O161" s="2" t="n">
         <v>321</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9594,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9658,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9673,18 +9677,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3278</v>
+        <v>3300</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3858</v>
+        <v>3850</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9705,7 +9709,7 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>10289</v>
@@ -9714,11 +9718,11 @@
         <v>6331</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9786,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9840,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9904,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9958,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9999,7 @@
         </is>
       </c>
       <c r="L169" s="3" t="n">
-        <v>1455</v>
+        <v>1067</v>
       </c>
       <c r="M169" s="3" t="n">
         <v>15829</v>
@@ -10008,7 +10012,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10049,20 +10053,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94971</v>
+        <v>94972</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94971</v>
+        <v>94972</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>126629</v>
+        <v>126630</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10105,12 +10109,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10160,7 +10164,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10204,7 @@
         <v>2707</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="N173" s="3" t="n">
         <v>3957</v>
@@ -10210,7 +10214,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10258,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10308,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10358,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10408,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10458,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10506,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10560,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10608,7 @@
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10662,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10701,12 +10705,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28491</v>
+        <v>28492</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10753,14 +10757,14 @@
         <v>21369</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10801,20 +10805,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28491</v>
+        <v>28492</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28491</v>
+        <v>28492</v>
       </c>
       <c r="N185" s="3" t="n">
         <v>56983</v>
       </c>
       <c r="O185" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10862,7 @@
         <v>158</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>317</v>
@@ -10868,7 +10872,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10912,7 +10916,7 @@
         <v>158</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>317</v>
@@ -10922,7 +10926,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10980,7 @@
         <v>158</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102984</v>
+        <v>102985</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>317</v>
@@ -10986,7 +10990,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11038,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11082,7 @@
         <v>158</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29194</v>
+        <v>29195</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>317</v>
@@ -11088,7 +11092,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11136,7 @@
         <v>158</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>156280</v>
+        <v>156282</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>317</v>
@@ -11142,7 +11146,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11200,7 @@
         <v>158</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>317</v>
@@ -11206,7 +11210,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11258,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11302,7 @@
         <v>158</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>317</v>
@@ -11308,7 +11312,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11356,7 @@
         <v>158</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>317</v>
@@ -11362,7 +11366,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11381,18 +11385,18 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1494</v>
+        <v>21317</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>1494</v>
+        <v>11405</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -11416,17 +11420,17 @@
         <v>158</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N196" s="3" t="n">
-        <v>317</v>
+        <v>23447</v>
       </c>
       <c r="O196" s="2" t="n">
         <v>562</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11478,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11531,14 +11535,14 @@
         <v>15829</v>
       </c>
       <c r="N198" s="3" t="n">
-        <v>943</v>
+        <v>317</v>
       </c>
       <c r="O198" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11596,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11660,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11714,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11768,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11812,7 @@
         <v>8231</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>276320</v>
+        <v>276322</v>
       </c>
       <c r="N203" s="3" t="n">
         <v>13929</v>
@@ -11818,7 +11822,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11872,7 +11876,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11940,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11988,7 @@
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12035,7 +12039,7 @@
         </is>
       </c>
       <c r="L207" s="3" t="n">
-        <v>679</v>
+        <v>582</v>
       </c>
       <c r="M207" s="3" t="n">
         <v>1583</v>
@@ -12048,7 +12052,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12116,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12170,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12234,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12288,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12342,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12390,7 @@
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12444,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12498,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12552,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12592,7 +12596,7 @@
         <v>15585</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>29368</v>
+        <v>29369</v>
       </c>
       <c r="N217" s="3" t="n">
         <v>25326</v>
@@ -12602,7 +12606,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12670,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12720,7 +12724,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12772,7 @@
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12822,7 +12826,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12840,13 +12844,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D222" s="3" t="inlineStr"/>
-      <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="3" t="inlineStr"/>
+      <c r="D222" s="3" t="n">
+        <v>791</v>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="3" t="n">
+        <v>791</v>
+      </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I222" s="2" t="n">
@@ -12863,7 +12877,7 @@
         </is>
       </c>
       <c r="L222" s="3" t="n">
-        <v>791</v>
+        <v>882</v>
       </c>
       <c r="M222" s="3" t="n">
         <v>2843</v>
@@ -12872,11 +12886,11 @@
         <v>1583</v>
       </c>
       <c r="O222" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12940,7 +12954,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -12994,7 +13008,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13062,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13116,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13180,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13224,7 @@
         <v>158</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>317</v>
@@ -13220,7 +13234,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13264,17 +13278,17 @@
         <v>158</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>317</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13328,17 +13342,17 @@
         <v>158</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N230" s="3" t="n">
-        <v>49214</v>
+        <v>49215</v>
       </c>
       <c r="O230" s="2" t="n">
         <v>1197</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13382,17 +13396,17 @@
         <v>791</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1583</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13470,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13524,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13588,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13638,7 +13652,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13706,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13754,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13808,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13856,7 @@
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13904,7 @@
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13917,10 +13931,10 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>19289</v>
+        <v>19093</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -13944,7 +13958,7 @@
         <v>18447</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30666</v>
+        <v>30667</v>
       </c>
       <c r="N241" s="3" t="n">
         <v>31657</v>
@@ -13954,7 +13968,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13973,7 +13987,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>42026</v>
+        <v>42027</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14008,17 +14022,17 @@
         <v>54854</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58648</v>
+        <v>58649</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75977</v>
+        <v>75978</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14037,18 +14051,18 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>17467</v>
+        <v>19422</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>20013</v>
+        <v>19954</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14065,20 +14079,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>19422</v>
+        <v>19425</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31657158</v>
+        <v>31657453</v>
       </c>
       <c r="N243" s="3" t="n">
         <v>31657</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14140,7 @@
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14180,7 +14194,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14199,18 +14213,18 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>3166</v>
+        <v>3957</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F246" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2431</v>
+        <v>2512</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14231,20 +14245,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="M246" s="3" t="n">
         <v>6331</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>3224</v>
+        <v>3506</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14312,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14370,7 @@
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14420,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14464,7 @@
       <c r="O250" s="2" t="inlineStr"/>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14504,7 +14518,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14545,10 +14559,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50436</v>
+        <v>50437</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50436</v>
+        <v>50437</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6331</v>
@@ -14558,7 +14572,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14599,7 +14613,7 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>6988</v>
+        <v>6300</v>
       </c>
       <c r="M253" s="3" t="n">
         <v>8517</v>
@@ -14612,7 +14626,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14684,7 @@
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14738,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14778,7 +14792,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14846,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14859,10 +14873,10 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -14886,17 +14900,17 @@
         <v>317</v>
       </c>
       <c r="M258" s="3" t="n">
-        <v>964</v>
+        <v>15824</v>
       </c>
       <c r="N258" s="3" t="n">
         <v>633</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14960,7 +14974,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15028,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15092,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15115,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F262" s="2" t="n">
@@ -15138,11 +15152,11 @@
         <v>12663</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15220,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15274,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15308,7 +15322,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15386,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15432,11 +15446,11 @@
         <v>633</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15504,7 @@
         <v>12752</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14258</v>
+        <v>14259</v>
       </c>
       <c r="N268" s="3" t="n">
         <v>13929</v>
@@ -15500,7 +15514,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15548,7 +15562,7 @@
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15610,7 @@
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15615,18 +15629,18 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>22950</v>
+        <v>28492</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>21604</v>
+        <v>22982</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15654,7 +15668,7 @@
       <c r="O271" s="2" t="inlineStr"/>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15712,7 @@
         <v>158</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>317</v>
@@ -15708,7 +15722,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15766,7 @@
         <v>158</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>20963</v>
+        <v>20964</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>317</v>
@@ -15762,7 +15776,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15795,7 @@
         </is>
       </c>
       <c r="D274" s="3" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
@@ -15792,7 +15806,7 @@
         <v>1</v>
       </c>
       <c r="G274" s="3" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -15826,7 +15840,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15890,7 +15904,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15934,7 +15948,7 @@
         <v>158</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>157809</v>
+        <v>157811</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>317</v>
@@ -15944,7 +15958,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15994,7 +16008,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16072,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16122,7 +16136,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16190,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16224,7 +16238,7 @@
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16286,7 @@
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16334,7 @@
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16388,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16425,20 +16439,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>9765</v>
+        <v>9830</v>
       </c>
       <c r="M285" s="3" t="n">
         <v>15829</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10725</v>
+        <v>11197</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16516,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16521,18 +16535,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5095</v>
+        <v>5342</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5476</v>
+        <v>5458</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16549,20 +16563,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5337</v>
+        <v>5825</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>6311</v>
+        <v>6216</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5789</v>
+        <v>5823</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16581,18 +16595,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>7037</v>
+        <v>6795</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>7198</v>
+        <v>7133</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16609,20 +16623,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>6795</v>
+        <v>6990</v>
       </c>
       <c r="M288" s="3" t="n">
         <v>7766</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7112</v>
+        <v>7148</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16649,10 +16663,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>10302</v>
+        <v>10358</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16682,7 +16696,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16732,11 +16746,11 @@
         <v>1583</v>
       </c>
       <c r="O290" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16800,7 +16814,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16819,18 +16833,18 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>4283</v>
+        <v>5178</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4674</v>
+        <v>4842</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16851,7 +16865,7 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>5178</v>
+        <v>5382</v>
       </c>
       <c r="M292" s="3" t="n">
         <v>5698</v>
@@ -16860,11 +16874,11 @@
         <v>6331</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16928,7 +16942,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -16947,18 +16961,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>8454</v>
+        <v>8264</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7361</v>
+        <v>7396</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -16979,20 +16993,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>8264</v>
+        <v>7754</v>
       </c>
       <c r="M294" s="3" t="n">
         <v>21538</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>8383</v>
+        <v>8454</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17036,17 +17050,17 @@
         <v>51448</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>699213</v>
+        <v>699220</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39571</v>
+        <v>39572</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17087,7 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G296" s="3" t="n">
         <v>31657</v>
@@ -17100,17 +17114,17 @@
         <v>31657</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68821</v>
+        <v>68822</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39571</v>
+        <v>39572</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17129,7 +17143,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63314</v>
+        <v>63315</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17140,7 +17154,7 @@
         <v>4</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63314</v>
+        <v>63315</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17161,20 +17175,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63314</v>
+        <v>63315</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>126629</v>
+        <v>126630</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>79143</v>
+        <v>79144</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17193,7 +17207,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>126629</v>
+        <v>126630</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17204,7 +17218,7 @@
         <v>1</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>126629</v>
+        <v>126630</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17225,20 +17239,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>126629</v>
+        <v>126630</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>126895</v>
+        <v>126896</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>158286</v>
+        <v>158287</v>
       </c>
       <c r="O298" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17271,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>253257</v>
+        <v>253260</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17268,7 +17282,7 @@
         <v>2</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>253257</v>
+        <v>253260</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17289,20 +17303,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>253257</v>
+        <v>253260</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>253259</v>
+        <v>253261</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>316572</v>
+        <v>316575</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17321,7 +17335,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>443200</v>
+        <v>443204</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17332,7 +17346,7 @@
         <v>4</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>443200</v>
+        <v>443204</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17353,20 +17367,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>443200</v>
+        <v>443204</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>952480</v>
+        <v>952489</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>633143</v>
+        <v>633149</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17385,18 +17399,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>3343</v>
+        <v>3378</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2549</v>
+        <v>2478</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17423,14 +17437,14 @@
         <v>18994</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2656</v>
+        <v>2683</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17494,7 +17508,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17521,10 +17535,10 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4286</v>
+        <v>4294</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17545,20 +17559,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4749</v>
+        <v>4747</v>
       </c>
       <c r="M303" s="3" t="n">
         <v>15829</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>5052</v>
+        <v>5064</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17622,7 +17636,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17700,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17746,11 +17760,11 @@
         <v>317</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>19914</v>
+        <v>19944</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17807,14 +17821,14 @@
         <v>15829</v>
       </c>
       <c r="N307" s="3" t="n">
-        <v>1011</v>
+        <v>317</v>
       </c>
       <c r="O307" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17868,7 +17882,7 @@
         <v>2058</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1266286</v>
+        <v>1266298</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>3957</v>
@@ -17878,7 +17892,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17932,7 +17946,7 @@
         <v>4432</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32005</v>
+        <v>32006</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6331</v>
@@ -17942,7 +17956,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -17961,18 +17975,18 @@
         </is>
       </c>
       <c r="D310" s="3" t="n">
-        <v>1645</v>
+        <v>1583</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G310" s="3" t="n">
-        <v>1614</v>
+        <v>1603</v>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
@@ -17993,7 +18007,7 @@
         </is>
       </c>
       <c r="L310" s="3" t="n">
-        <v>1893</v>
+        <v>1583</v>
       </c>
       <c r="M310" s="3" t="n">
         <v>6031</v>
@@ -18002,11 +18016,11 @@
         <v>3166</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18074,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18122,7 @@
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18172,7 +18186,7 @@
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18226,7 +18240,7 @@
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18280,17 +18294,17 @@
         <v>15829</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1582858</v>
+        <v>1582873</v>
       </c>
       <c r="N315" s="3" t="n">
         <v>31657</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18344,17 +18358,17 @@
         <v>37989</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>77669</v>
+        <v>63108</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75977</v>
+        <v>75978</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18373,7 +18387,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>102886</v>
+        <v>102887</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18384,7 +18398,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>102886</v>
+        <v>102887</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18405,20 +18419,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>102886</v>
+        <v>102887</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>102886</v>
+        <v>102887</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>205772</v>
+        <v>205773</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18445,10 +18459,10 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>824</v>
+        <v>793</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18475,14 +18489,14 @@
         <v>2053</v>
       </c>
       <c r="N318" s="3" t="n">
-        <v>750</v>
+        <v>533</v>
       </c>
       <c r="O318" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18501,7 +18515,7 @@
         </is>
       </c>
       <c r="D319" s="3" t="n">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
@@ -18509,10 +18523,10 @@
         </is>
       </c>
       <c r="F319" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G319" s="3" t="n">
-        <v>1378</v>
+        <v>1395</v>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
@@ -18533,7 +18547,7 @@
         </is>
       </c>
       <c r="L319" s="3" t="n">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="M319" s="3" t="n">
         <v>15721</v>
@@ -18546,7 +18560,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18624,7 @@
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18667,14 +18681,14 @@
         <v>5887</v>
       </c>
       <c r="N321" s="3" t="n">
-        <v>3395</v>
+        <v>3656</v>
       </c>
       <c r="O321" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18731,14 +18745,14 @@
         <v>1037</v>
       </c>
       <c r="N322" s="3" t="n">
-        <v>582</v>
+        <v>693</v>
       </c>
       <c r="O322" s="2" t="n">
         <v>509</v>
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18757,18 +18771,18 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>1296</v>
+        <v>1937</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>1745</v>
+        <v>1793</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18798,11 +18812,11 @@
         <v>2216</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18821,18 +18835,18 @@
         </is>
       </c>
       <c r="D324" s="3" t="n">
-        <v>195</v>
+        <v>324</v>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F324" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G324" s="3" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
@@ -18853,20 +18867,20 @@
         </is>
       </c>
       <c r="L324" s="3" t="n">
-        <v>317</v>
+        <v>508</v>
       </c>
       <c r="M324" s="3" t="n">
         <v>5597</v>
       </c>
       <c r="N324" s="3" t="n">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="O324" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18889,14 +18903,14 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
         <v>23</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2817</v>
+        <v>2873</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18917,20 +18931,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>3166</v>
+        <v>3351</v>
       </c>
       <c r="M325" s="3" t="n">
         <v>15721</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>3409</v>
+        <v>3375</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18949,18 +18963,18 @@
         </is>
       </c>
       <c r="D326" s="3" t="n">
-        <v>2151</v>
+        <v>2145</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F326" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2135</v>
+        <v>2042</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -18981,20 +18995,20 @@
         </is>
       </c>
       <c r="L326" s="3" t="n">
-        <v>2145</v>
+        <v>11080</v>
       </c>
       <c r="M326" s="3" t="n">
         <v>15829</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>2287</v>
+        <v>2301</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19059,7 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>1683</v>
+        <v>1508</v>
       </c>
       <c r="M327" s="3" t="n">
         <v>15829</v>
@@ -19054,11 +19068,11 @@
         <v>2466</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19077,18 +19091,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>26230</v>
+        <v>25242</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>23511</v>
+        <v>23663</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19109,20 +19123,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>28048</v>
+        <v>26212</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>30579</v>
+        <v>30580</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>28048</v>
+        <v>28164</v>
       </c>
       <c r="O328" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19141,18 +19155,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7688</v>
+        <v>7451</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
         <v>43</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7264</v>
+        <v>7261</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19173,20 +19187,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7620</v>
+        <v>7281</v>
       </c>
       <c r="M329" s="3" t="n">
         <v>9776</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7959</v>
+        <v>8149</v>
       </c>
       <c r="O329" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19213,10 +19227,10 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5844</v>
+        <v>5841</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19246,11 +19260,11 @@
         <v>6062</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19314,7 +19328,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19341,10 +19355,10 @@
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1207</v>
+        <v>1217</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19365,20 +19379,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="M332" s="3" t="n">
         <v>15829</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1733</v>
+        <v>1727</v>
       </c>
       <c r="O332" s="2" t="n">
         <v>184</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19405,10 +19419,10 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>867</v>
+        <v>931</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19432,17 +19446,17 @@
         <v>236</v>
       </c>
       <c r="M333" s="3" t="n">
-        <v>2900</v>
+        <v>9694</v>
       </c>
       <c r="N333" s="3" t="n">
         <v>317</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19469,10 +19483,10 @@
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19493,7 +19507,7 @@
         </is>
       </c>
       <c r="L334" s="3" t="n">
-        <v>951</v>
+        <v>519</v>
       </c>
       <c r="M334" s="3" t="n">
         <v>9428</v>
@@ -19502,11 +19516,11 @@
         <v>575</v>
       </c>
       <c r="O334" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19570,7 +19584,7 @@
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19597,10 +19611,10 @@
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19624,17 +19638,17 @@
         <v>467</v>
       </c>
       <c r="M336" s="3" t="n">
-        <v>2900</v>
+        <v>9694</v>
       </c>
       <c r="N336" s="3" t="n">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19685,7 +19699,7 @@
         </is>
       </c>
       <c r="L337" s="3" t="n">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="M337" s="3" t="n">
         <v>15498</v>
@@ -19694,11 +19708,11 @@
         <v>317</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19717,18 +19731,18 @@
         </is>
       </c>
       <c r="D338" s="3" t="n">
-        <v>158</v>
+        <v>285</v>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F338" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G338" s="3" t="n">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
@@ -19749,20 +19763,20 @@
         </is>
       </c>
       <c r="L338" s="3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M338" s="3" t="n">
-        <v>980</v>
+        <v>9694</v>
       </c>
       <c r="N338" s="3" t="n">
         <v>317</v>
       </c>
       <c r="O338" s="2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19785,14 +19799,14 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F339" s="2" t="n">
         <v>17</v>
       </c>
       <c r="G339" s="3" t="n">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
@@ -19819,14 +19833,14 @@
         <v>4714</v>
       </c>
       <c r="N339" s="3" t="n">
-        <v>2996</v>
+        <v>2610</v>
       </c>
       <c r="O339" s="2" t="n">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19883,14 +19897,14 @@
         <v>3166</v>
       </c>
       <c r="N340" s="3" t="n">
-        <v>1144</v>
+        <v>317</v>
       </c>
       <c r="O340" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -19941,20 +19955,20 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>1440</v>
+        <v>1266</v>
       </c>
       <c r="M341" s="3" t="n">
         <v>2434</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>1383</v>
+        <v>1448</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20032,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20045,10 +20059,10 @@
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
@@ -20072,17 +20086,17 @@
         <v>385</v>
       </c>
       <c r="M343" s="3" t="n">
-        <v>2434</v>
+        <v>9694</v>
       </c>
       <c r="N343" s="3" t="n">
         <v>435</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20136,7 +20150,7 @@
         <v>2241</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3166</v>
@@ -20146,7 +20160,7 @@
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20165,18 +20179,18 @@
         </is>
       </c>
       <c r="D345" s="3" t="n">
-        <v>2058</v>
+        <v>2140</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F345" s="2" t="n">
         <v>21</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20197,7 +20211,7 @@
         </is>
       </c>
       <c r="L345" s="3" t="n">
-        <v>2058</v>
+        <v>2164</v>
       </c>
       <c r="M345" s="3" t="n">
         <v>75854</v>
@@ -20206,11 +20220,11 @@
         <v>3957</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20282,7 @@
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20328,11 +20342,11 @@
         <v>6331</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20396,7 +20410,7 @@
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20460,7 +20474,7 @@
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20522,7 @@
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20527,18 +20541,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>21842</v>
+        <v>17980</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17668</v>
+        <v>17656</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20559,7 +20573,7 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>21359</v>
+        <v>16505</v>
       </c>
       <c r="M351" s="3" t="n">
         <v>31657</v>
@@ -20568,11 +20582,11 @@
         <v>31657</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20591,18 +20605,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>43807</v>
+        <v>48501</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>42305</v>
+        <v>43080</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20622,21 +20636,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L352" s="3" t="n">
-        <v>48500</v>
-      </c>
-      <c r="M352" s="3" t="n">
-        <v>48500</v>
-      </c>
+      <c r="L352" s="3" t="inlineStr"/>
+      <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="3" t="n">
-        <v>75977</v>
-      </c>
-      <c r="O352" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>75978</v>
+      </c>
+      <c r="O352" s="2" t="inlineStr"/>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20655,7 +20663,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>116832</v>
+        <v>116833</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20666,7 +20674,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>116832</v>
+        <v>116833</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20689,12 +20697,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>205772</v>
+        <v>205773</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20758,7 +20766,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20812,7 +20820,7 @@
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20856,17 +20864,17 @@
         <v>8864</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55400</v>
+        <v>55401</v>
       </c>
       <c r="N356" s="3" t="n">
         <v>17728</v>
       </c>
       <c r="O356" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20893,10 +20901,10 @@
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>956</v>
+        <v>984</v>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
@@ -20923,14 +20931,14 @@
         <v>15829</v>
       </c>
       <c r="N357" s="3" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20989,7 @@
         </is>
       </c>
       <c r="L358" s="3" t="n">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="M358" s="3" t="n">
         <v>769</v>
@@ -20990,11 +20998,11 @@
         <v>402</v>
       </c>
       <c r="O358" s="2" t="n">
-        <v>491</v>
+        <v>774</v>
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -21024,7 +21032,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>158.285788</v>
+        <v>158.287265</v>
       </c>
     </row>
     <row r="2">
@@ -21035,7 +21043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 10 Oct 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 11 Oct 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21047,7 +21055,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -609,17 +609,17 @@
         <v>3166</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1583076</v>
+        <v>1583055</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6332</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>6332</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>96775</v>
+        <v>96774</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>31</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>25329</v>
@@ -747,7 +747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -830,18 +830,18 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42771</v>
+        <v>42767</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85486</v>
+        <v>85485</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -916,20 +916,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>126646</v>
+        <v>126644</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>142477</v>
+        <v>142475</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>253292</v>
+        <v>253289</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>356192</v>
+        <v>356187</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>356192</v>
+        <v>356187</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>712384</v>
+        <v>712375</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6208</v>
+        <v>6219</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6798</v>
+        <v>6663</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1583076</v>
+        <v>1583055</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8707</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8398</v>
+        <v>8675</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8604</v>
+        <v>8558</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1098,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8675</v>
+        <v>6965</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>150351</v>
+        <v>150349</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>17414</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1130,18 +1130,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14064</v>
+        <v>13931</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14168</v>
+        <v>14179</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1162,20 +1162,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13931</v>
+        <v>14075</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42504</v>
+        <v>42503</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34828</v>
+        <v>34827</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
         <v>39575</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39577</v>
+        <v>39576</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>22163</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>94065</v>
+        <v>94064</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>94065</v>
+        <v>94064</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>22163</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>237461</v>
+        <v>237458</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1583076</v>
+        <v>1583055</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>15831</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
         <v>29312</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64132</v>
+        <v>64131</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5382</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>22560</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64132</v>
+        <v>64131</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5382</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
         <v>792</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1583076</v>
+        <v>1583055</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1583</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>1583</v>
@@ -1563,7 +1563,7 @@
         <v>1583</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>227977</v>
+        <v>227974</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3166</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
         <v>3166</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>269123</v>
+        <v>269119</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6332</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11082</v>
+        <v>11081</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>36996</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1776,20 +1776,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21372</v>
+        <v>21371</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>139738</v>
+        <v>139736</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39577</v>
+        <v>39576</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39577</v>
+        <v>39576</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1840,20 +1840,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39577</v>
+        <v>39576</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>321896</v>
+        <v>321892</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>79154</v>
+        <v>79153</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1905,20 +1905,20 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>15831</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1672</v>
+        <v>2007</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>40</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1975,14 +1975,14 @@
         <v>15831</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1597</v>
+        <v>317</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2055,18 +2055,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1265</v>
+        <v>972</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1076</v>
+        <v>1062</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2087,20 +2087,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1259</v>
+        <v>1171</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1578871</v>
+        <v>1578850</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1583</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2123,14 +2123,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1931</v>
+        <v>1914</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2154,17 +2154,17 @@
         <v>1583</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1583076</v>
+        <v>1583055</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3166</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>3173</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
         <v>633</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1583076</v>
+        <v>1583055</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1266</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>2375</v>
@@ -2346,7 +2346,7 @@
         <v>2375</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11549</v>
+        <v>11548</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>4749</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2407,20 +2407,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1257</v>
+        <v>972</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>633230</v>
+        <v>633222</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1583</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2381</v>
+        <v>2407</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2503,18 +2503,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3685</v>
+        <v>3549</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3561</v>
+        <v>3551</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2544,11 +2544,11 @@
         <v>6332</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2571,11 +2571,11 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6332</v>
@@ -2605,14 +2605,14 @@
         <v>30599</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O35" s="2" t="n">
         <v>91</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2690,13 +2690,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="n">
+        <v>1583</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1583</v>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -2709,7 +2719,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="3" t="n">
-        <v>1583</v>
+        <v>2452</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>4160</v>
@@ -2718,11 +2728,11 @@
         <v>3166</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2745,14 +2755,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3184</v>
+        <v>3178</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2772,7 +2782,7 @@
         <v>3166</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>316615</v>
+        <v>316611</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6332</v>
@@ -2782,7 +2792,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2846,7 @@
         <v>1583</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>144926</v>
+        <v>144924</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3166</v>
@@ -2846,7 +2856,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2920,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2933,11 +2943,11 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>6332</v>
@@ -2967,14 +2977,14 @@
         <v>15145</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3001,10 +3011,10 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3369</v>
+        <v>3343</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3021,20 +3031,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>6131</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>4243</v>
+        <v>4920</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3104,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3113,18 +3123,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>8735</v>
+        <v>9243</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3141,20 +3151,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>8729</v>
+        <v>9224</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>13785</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>9980</v>
+        <v>10139</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3228,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3282,7 @@
         <v>3166</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>6332</v>
@@ -3282,7 +3292,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3336,7 @@
         <v>774</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>5880</v>
+        <v>5879</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>792</v>
@@ -3336,7 +3346,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3410,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3464,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3472,13 +3482,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1984</v>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -3491,20 +3511,20 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>1984</v>
+        <v>2188</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>4151</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>792</v>
+        <v>2181</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3584,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3644,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3708,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3762,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3769,10 +3789,10 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>2314</v>
+        <v>3438</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3806,7 +3826,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3890,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3889,18 +3909,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9706</v>
+        <v>9243</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9685</v>
+        <v>9705</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3921,20 +3941,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9706</v>
+        <v>8757</v>
       </c>
       <c r="M57" s="3" t="n">
         <v>30661</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3953,18 +3973,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3689</v>
+        <v>3506</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3753</v>
+        <v>3744</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3991,14 +4011,14 @@
         <v>10334</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3890</v>
+        <v>3847</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4082,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4106,17 +4126,17 @@
         <v>1108</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4190,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4238,7 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4292,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4315,12 +4335,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4383,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4442,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4463,10 +4483,10 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>22163</v>
@@ -4476,7 +4496,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4544,7 @@
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4608,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4662,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4716,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4760,7 @@
         <v>2533</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1484992</v>
+        <v>1484972</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>11398</v>
@@ -4750,7 +4770,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4824,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4878,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4902,17 +4922,17 @@
         <v>17414</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27074</v>
+        <v>27073</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4996,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5050,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5108,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5162,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5210,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5264,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5312,7 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5362,7 @@
         <v>158</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1582917</v>
+        <v>1582897</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>792</v>
@@ -5352,7 +5372,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5375,11 +5395,11 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>317</v>
@@ -5408,11 +5428,11 @@
         <v>1583</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5492,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5552,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5596,7 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5615,12 +5635,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14248</v>
+        <v>14247</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5684,7 @@
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5703,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -5694,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -5711,10 +5731,10 @@
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="3" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>86037</v>
+        <v>86036</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>792</v>
@@ -5724,7 +5744,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5794,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5844,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5894,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5938,7 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5977,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14248</v>
+        <v>14247</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6026,7 @@
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6053,14 +6073,14 @@
         <v>3098</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="O97" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6134,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6198,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6252,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6275,12 +6295,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6327,14 +6347,14 @@
         <v>17985</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6402,7 @@
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6429,14 +6449,14 @@
         <v>2691</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="O104" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6504,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6552,7 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6600,7 @@
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6623,12 +6643,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6671,12 +6691,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6744,7 @@
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6767,12 +6787,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>79154</v>
+        <v>79153</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6811,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>87069</v>
+        <v>87068</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6802,7 +6822,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>87069</v>
+        <v>87068</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6823,20 +6843,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>87069</v>
+        <v>87068</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>97191</v>
+        <v>97190</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>110815</v>
+        <v>110814</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6875,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>110815</v>
+        <v>110814</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -6866,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>110815</v>
+        <v>110814</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6887,20 +6907,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>110815</v>
+        <v>110814</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>110815</v>
+        <v>110814</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>142477</v>
+        <v>142475</v>
       </c>
       <c r="O113" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6941,20 +6961,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>126646</v>
+        <v>126644</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>126646</v>
+        <v>126644</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -6995,20 +7015,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>189969</v>
+        <v>189967</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7049,20 +7069,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>213715</v>
+        <v>213712</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>253292</v>
+        <v>253289</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>253292</v>
+        <v>253289</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7136,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7190,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7238,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7262,17 +7282,17 @@
         <v>7124</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14248</v>
+        <v>14247</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14248</v>
+        <v>14247</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7340,7 @@
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7367,14 +7387,14 @@
         <v>15831</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7418,17 +7438,17 @@
         <v>18997</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>41100</v>
+        <v>41099</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7502,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7556,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7610,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7634,17 +7654,17 @@
         <v>7124</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11894</v>
+        <v>11893</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14248</v>
+        <v>14247</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7712,7 @@
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7735,12 +7755,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7808,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7829,10 +7849,10 @@
         </is>
       </c>
       <c r="L131" s="3" t="n">
-        <v>4927</v>
+        <v>4926</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>4927</v>
+        <v>4926</v>
       </c>
       <c r="N131" s="3" t="n">
         <v>6332</v>
@@ -7842,7 +7862,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7889,14 +7909,14 @@
         <v>6332</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7970,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7998,7 +8018,7 @@
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8039,10 +8059,10 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21372</v>
+        <v>21371</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21372</v>
+        <v>21371</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>47492</v>
@@ -8052,7 +8072,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8099,14 +8119,14 @@
         <v>28495</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71238</v>
+        <v>71237</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8153,14 +8173,14 @@
         <v>18997</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8183,11 +8203,11 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G138" s="3" t="n">
         <v>6332</v>
@@ -8217,14 +8237,14 @@
         <v>12755</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8308,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8339,20 +8359,20 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="M140" s="3" t="n">
         <v>5169</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8436,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8490,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8544,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8551,10 +8571,10 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2113</v>
+        <v>2140</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8588,7 +8608,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8656,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8710,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8733,12 +8753,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8812,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8860,7 @@
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8863,14 +8883,14 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
         <v>31</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16567</v>
+        <v>16488</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8894,17 +8914,17 @@
         <v>15831</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39577</v>
+        <v>39576</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8943,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8934,7 +8954,7 @@
         <v>15</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8955,20 +8975,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="M151" s="3" t="n">
         <v>63272</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75988</v>
+        <v>75987</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9009,20 +9029,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>102900</v>
+        <v>102899</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>102900</v>
+        <v>102899</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>205800</v>
+        <v>205797</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9106,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9170,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9220,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9280,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9340,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9384,7 @@
         <v>792</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1583076</v>
+        <v>1583055</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1583</v>
@@ -9374,7 +9394,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9448,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9502,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9566,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9617,7 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>2311</v>
+        <v>2237</v>
       </c>
       <c r="M162" s="3" t="n">
         <v>30205</v>
@@ -9606,11 +9626,11 @@
         <v>1583</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9694,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9693,18 +9713,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3492</v>
+        <v>3996</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3789</v>
+        <v>3793</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9745,7 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3480</v>
+        <v>4184</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>10290</v>
@@ -9734,11 +9754,11 @@
         <v>6332</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9795,14 +9815,14 @@
         <v>4915</v>
       </c>
       <c r="N165" s="3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O165" s="2" t="n">
         <v>30</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9876,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9875,18 +9895,18 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>633</v>
+        <v>966</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>972</v>
+        <v>849</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -9907,20 +9927,20 @@
         </is>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1260</v>
+        <v>1567</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1266</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9994,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10028,7 +10048,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10069,20 +10089,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94985</v>
+        <v>94983</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94985</v>
+        <v>94983</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>126646</v>
+        <v>126644</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10125,12 +10145,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10200,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10250,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10294,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10314,17 +10334,17 @@
         <v>7124</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14218</v>
+        <v>14217</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14248</v>
+        <v>14247</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10374,7 +10394,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10417,14 +10437,14 @@
         <v>15910</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10467,14 +10487,14 @@
         <v>19155</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10542,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10596,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10619,12 +10639,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10698,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10746,7 @@
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10767,20 +10787,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21372</v>
+        <v>21371</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21372</v>
+        <v>21371</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42743</v>
+        <v>42742</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10827,14 +10847,14 @@
         <v>28495</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56991</v>
+        <v>56990</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10878,7 +10898,7 @@
         <v>158</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>317</v>
@@ -10888,7 +10908,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10952,7 @@
         <v>158</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>317</v>
@@ -10942,7 +10962,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -10996,17 +11016,17 @@
         <v>158</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102998</v>
+        <v>102997</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>317</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11054,7 +11074,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11128,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11172,7 @@
         <v>158</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>156302</v>
+        <v>156300</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>317</v>
@@ -11162,7 +11182,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11209,7 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>158</v>
@@ -11216,7 +11236,7 @@
         <v>158</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>317</v>
@@ -11226,7 +11246,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11294,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11338,7 @@
         <v>158</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>317</v>
@@ -11328,7 +11348,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11372,17 +11392,17 @@
         <v>158</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>317</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11409,10 +11429,10 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>11407</v>
+        <v>21319</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -11436,7 +11456,7 @@
         <v>158</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>23450</v>
@@ -11446,7 +11466,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11514,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11578,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11605,14 +11625,14 @@
         <v>20615</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11696,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11730,7 +11750,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11804,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11848,7 @@
         <v>8232</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>276358</v>
+        <v>276354</v>
       </c>
       <c r="N203" s="3" t="n">
         <v>13931</v>
@@ -11838,7 +11858,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11902,7 @@
         <v>15642</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16056</v>
+        <v>16055</v>
       </c>
       <c r="N204" s="3" t="n">
         <v>18997</v>
@@ -11892,7 +11912,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11939,14 +11959,14 @@
         <v>48836</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -11994,7 +12014,7 @@
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12058,7 +12078,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12132,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12186,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12250,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12304,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12331,14 +12351,14 @@
         <v>7124</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14248</v>
+        <v>14247</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12406,7 @@
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12433,14 +12453,14 @@
         <v>15831</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12514,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12568,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12622,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12686,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12713,14 +12733,14 @@
         <v>7124</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14248</v>
+        <v>14247</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12763,12 +12783,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12815,14 +12835,14 @@
         <v>18997</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12906,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12970,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -12994,7 +13014,7 @@
         <v>3166</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7205</v>
+        <v>7204</v>
       </c>
       <c r="N224" s="3" t="n">
         <v>6332</v>
@@ -13004,7 +13024,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13078,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13112,7 +13132,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13196,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13240,7 @@
         <v>158</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>317</v>
@@ -13230,7 +13250,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13274,17 +13294,17 @@
         <v>158</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>317</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13338,17 +13358,17 @@
         <v>158</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>317</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13392,17 +13412,17 @@
         <v>792</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1583</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13466,7 +13486,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13520,7 +13540,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13604,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13638,7 +13658,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13712,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13760,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13804,7 @@
         <v>8865</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11036</v>
+        <v>11035</v>
       </c>
       <c r="N238" s="3" t="n">
         <v>6332</v>
@@ -13794,7 +13814,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13837,12 +13857,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13910,7 @@
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -13941,20 +13961,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>22138</v>
+        <v>22137</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30671</v>
+        <v>30670</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14005,20 +14025,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>52835</v>
+        <v>52834</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58656</v>
+        <v>58655</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75988</v>
+        <v>75987</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14048,7 +14068,7 @@
         <v>10</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>19993</v>
+        <v>19992</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14065,20 +14085,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>19257</v>
+        <v>18688</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31661515</v>
+        <v>31661099</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14146,7 @@
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14180,7 +14200,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14199,18 +14219,18 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>3958</v>
+        <v>3687</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2669</v>
+        <v>2733</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14231,20 +14251,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>3687</v>
+        <v>3689</v>
       </c>
       <c r="M246" s="3" t="n">
         <v>15831</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>3507</v>
+        <v>3962</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14318,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14376,7 @@
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14426,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14456,7 +14476,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14520,7 @@
         <v>158</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97345</v>
+        <v>97344</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>317</v>
@@ -14510,7 +14530,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14561,10 +14581,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50443</v>
+        <v>50442</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50443</v>
+        <v>50442</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6332</v>
@@ -14574,7 +14594,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14625,10 +14645,10 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>8519</v>
+        <v>8518</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>8519</v>
+        <v>8518</v>
       </c>
       <c r="N253" s="3" t="n">
         <v>7599</v>
@@ -14638,7 +14658,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14716,7 @@
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14750,7 +14770,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14824,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14878,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14877,11 +14897,11 @@
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>385</v>
+        <v>317</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
@@ -14918,11 +14938,11 @@
         <v>633</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -14982,11 +15002,11 @@
         <v>1583</v>
       </c>
       <c r="O259" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15060,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15094,7 +15114,7 @@
         <v>3166</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7023</v>
+        <v>7022</v>
       </c>
       <c r="N261" s="3" t="n">
         <v>6332</v>
@@ -15104,7 +15124,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15131,7 +15151,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G262" s="3" t="n">
         <v>6332</v>
@@ -15158,17 +15178,17 @@
         <v>6332</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15228,11 +15248,11 @@
         <v>1583</v>
       </c>
       <c r="O263" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15286,7 +15306,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15354,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15391,14 +15411,14 @@
         <v>9647</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15417,18 +15437,18 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>317</v>
+        <v>2428</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>1755</v>
+        <v>1969</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15449,20 +15469,20 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>1939</v>
+        <v>3324</v>
       </c>
       <c r="M267" s="3" t="n">
         <v>19470</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>633</v>
+        <v>1716</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15526,7 +15546,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15594,7 @@
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15622,7 +15642,7 @@
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15649,10 +15669,10 @@
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>22985</v>
+        <v>23665</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15679,14 +15699,14 @@
         <v>28495</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15750,7 @@
         <v>158</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>317</v>
@@ -15740,7 +15760,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15814,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15813,7 +15833,7 @@
         </is>
       </c>
       <c r="D274" s="3" t="n">
-        <v>16735</v>
+        <v>16734</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
@@ -15824,7 +15844,7 @@
         <v>1</v>
       </c>
       <c r="G274" s="3" t="n">
-        <v>16735</v>
+        <v>16734</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -15858,7 +15878,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15918,11 +15938,11 @@
         <v>317</v>
       </c>
       <c r="O275" s="2" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -15966,17 +15986,17 @@
         <v>158</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>157831</v>
+        <v>157829</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>317</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16026,7 +16046,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16086,11 +16106,11 @@
         <v>6332</v>
       </c>
       <c r="O278" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16144,7 +16164,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16198,7 +16218,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16266,7 @@
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16314,7 @@
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16362,7 @@
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16389,14 +16409,14 @@
         <v>33754</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16415,7 +16435,7 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>10634</v>
+        <v>10633</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -16423,10 +16443,10 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9062</v>
+        <v>9060</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16453,14 +16473,14 @@
         <v>15831</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>11506</v>
+        <v>11704</v>
       </c>
       <c r="O285" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16544,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16571,20 +16591,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5636</v>
+        <v>5634</v>
       </c>
       <c r="M287" s="3" t="n">
         <v>6217</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5785</v>
+        <v>5784</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16603,18 +16623,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6111</v>
+        <v>5838</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
         <v>26</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6900</v>
+        <v>6780</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16631,20 +16651,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>6109</v>
+        <v>6096</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>7767</v>
+        <v>7766</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>6988</v>
+        <v>6970</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16667,14 +16687,14 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>10557</v>
+        <v>10551</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16691,20 +16711,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>10483</v>
+        <v>11597</v>
       </c>
       <c r="M289" s="3" t="n">
         <v>11685</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>11564</v>
+        <v>11531</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16778,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16777,18 +16797,18 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>2726</v>
+        <v>2153</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F291" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>2639</v>
+        <v>2545</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -16809,7 +16829,7 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>2153</v>
+        <v>2620</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5066</v>
@@ -16818,11 +16838,11 @@
         <v>3166</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16849,10 +16869,10 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4843</v>
+        <v>4731</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16873,7 +16893,7 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>5382</v>
+        <v>3891</v>
       </c>
       <c r="M292" s="3" t="n">
         <v>5699</v>
@@ -16882,11 +16902,11 @@
         <v>6332</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16970,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -16969,18 +16989,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>8716</v>
+        <v>8727</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
         <v>26</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7224</v>
+        <v>7369</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17001,20 +17021,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>8720</v>
+        <v>8099</v>
       </c>
       <c r="M294" s="3" t="n">
         <v>21541</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>8082</v>
+        <v>8099</v>
       </c>
       <c r="O294" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17055,20 +17075,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51455</v>
+        <v>51454</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>699309</v>
+        <v>699300</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39577</v>
+        <v>39576</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17087,7 +17107,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17098,7 +17118,7 @@
         <v>5</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17119,20 +17139,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68831</v>
+        <v>68830</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39577</v>
+        <v>39576</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17151,7 +17171,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63323</v>
+        <v>63322</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17159,10 +17179,10 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63323</v>
+        <v>63322</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17183,20 +17203,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63323</v>
+        <v>63322</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>126646</v>
+        <v>126644</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>79154</v>
+        <v>79153</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17215,7 +17235,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>126646</v>
+        <v>126644</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17226,7 +17246,7 @@
         <v>1</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>126646</v>
+        <v>126644</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17247,20 +17267,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>126646</v>
+        <v>126644</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>126649</v>
+        <v>126648</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>158308</v>
+        <v>158305</v>
       </c>
       <c r="O298" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17279,18 +17299,18 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>253292</v>
+        <v>253289</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>253292</v>
+        <v>253289</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17311,20 +17331,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>253292</v>
+        <v>253289</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>253294</v>
+        <v>253290</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>316615</v>
+        <v>316611</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17363,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>443261</v>
+        <v>443255</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17354,7 +17374,7 @@
         <v>2</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>443261</v>
+        <v>443255</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17375,20 +17395,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>443261</v>
+        <v>443255</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>952611</v>
+        <v>952599</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>633230</v>
+        <v>633222</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17407,18 +17427,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>2132</v>
+        <v>2036</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
         <v>44</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2412</v>
+        <v>2424</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17439,20 +17459,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>2036</v>
+        <v>2142</v>
       </c>
       <c r="M301" s="3" t="n">
         <v>18997</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2468</v>
+        <v>2533</v>
       </c>
       <c r="O301" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17479,10 +17499,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1860</v>
+        <v>1796</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17503,20 +17523,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1162</v>
+        <v>1108</v>
       </c>
       <c r="M302" s="3" t="n">
         <v>4801</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2216</v>
+        <v>2243</v>
       </c>
       <c r="O302" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17555,7 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4748</v>
+        <v>4749</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -17546,7 +17566,7 @@
         <v>23</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4375</v>
+        <v>4383</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17573,14 +17593,14 @@
         <v>15831</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>5112</v>
+        <v>5121</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17664,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17708,7 +17728,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17792,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17836,7 +17856,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17863,10 +17883,10 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G308" s="3" t="n">
-        <v>2295</v>
+        <v>2058</v>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
@@ -17890,17 +17910,17 @@
         <v>2058</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1266461</v>
+        <v>1266444</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>3958</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17974,7 @@
         <v>4433</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32010</v>
+        <v>32009</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6332</v>
@@ -17964,7 +17984,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18018,7 +18038,7 @@
         <v>1893</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="N310" s="3" t="n">
         <v>3166</v>
@@ -18028,7 +18048,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18082,7 +18102,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18125,12 +18145,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18184,17 +18204,17 @@
         <v>9498</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26175</v>
+        <v>26174</v>
       </c>
       <c r="N313" s="3" t="n">
         <v>18997</v>
       </c>
       <c r="O313" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18248,7 +18268,7 @@
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18271,11 +18291,11 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G315" s="3" t="n">
         <v>15831</v>
@@ -18302,17 +18322,17 @@
         <v>15831</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1583076</v>
+        <v>1583055</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18331,18 +18351,18 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18363,20 +18383,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>37994</v>
+        <v>37993</v>
       </c>
       <c r="M316" s="3" t="n">
         <v>37995</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75988</v>
+        <v>75987</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18395,7 +18415,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>102900</v>
+        <v>102899</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18406,7 +18426,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>102900</v>
+        <v>102899</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18427,20 +18447,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>102900</v>
+        <v>102899</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>102900</v>
+        <v>102899</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>205800</v>
+        <v>205797</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18511,7 @@
         </is>
       </c>
       <c r="L318" s="3" t="n">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="M318" s="3" t="n">
         <v>2053</v>
@@ -18500,11 +18520,11 @@
         <v>317</v>
       </c>
       <c r="O318" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18568,7 +18588,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18619,7 +18639,7 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>2311</v>
+        <v>1108</v>
       </c>
       <c r="M320" s="3" t="n">
         <v>9836</v>
@@ -18632,7 +18652,7 @@
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18655,14 +18675,14 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3223</v>
+        <v>3240</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18683,20 +18703,20 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3324</v>
+        <v>3320</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>5887</v>
+        <v>8276</v>
       </c>
       <c r="N321" s="3" t="n">
-        <v>317</v>
+        <v>3657</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18780,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18820,11 +18840,11 @@
         <v>2645</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18888,7 +18908,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -18907,18 +18927,18 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>2802</v>
+        <v>3158</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2858</v>
+        <v>2870</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18939,20 +18959,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>3166</v>
+        <v>3158</v>
       </c>
       <c r="M325" s="3" t="n">
         <v>15723</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>3351</v>
+        <v>3380</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19023,7 @@
         </is>
       </c>
       <c r="L326" s="3" t="n">
-        <v>11082</v>
+        <v>11081</v>
       </c>
       <c r="M326" s="3" t="n">
         <v>15831</v>
@@ -19016,7 +19036,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19066,7 @@
         <v>4</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19080,7 +19100,7 @@
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19099,18 +19119,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>27229</v>
+        <v>27070</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>23943</v>
+        <v>23969</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19131,20 +19151,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>27071</v>
+        <v>26413</v>
       </c>
       <c r="M328" s="3" t="n">
         <v>30583</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>28165</v>
+        <v>28289</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19163,18 +19183,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>8118</v>
+        <v>7993</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7273</v>
+        <v>7282</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19195,20 +19215,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7976</v>
+        <v>8173</v>
       </c>
       <c r="M329" s="3" t="n">
         <v>9777</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8273</v>
+        <v>8351</v>
       </c>
       <c r="O329" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19227,18 +19247,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>6218</v>
+        <v>5911</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5826</v>
+        <v>5811</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19259,20 +19279,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5911</v>
+        <v>5830</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8663</v>
+        <v>8662</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6757</v>
+        <v>6690</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19336,7 +19356,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19355,18 +19375,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>1529</v>
+        <v>1537</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19387,20 +19407,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="M332" s="3" t="n">
         <v>15831</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19427,10 +19447,10 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>946</v>
+        <v>1027</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19464,7 +19484,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19515,7 +19535,7 @@
         </is>
       </c>
       <c r="L334" s="3" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M334" s="3" t="n">
         <v>9429</v>
@@ -19528,7 +19548,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19547,18 +19567,18 @@
         </is>
       </c>
       <c r="D335" s="3" t="n">
-        <v>2433</v>
+        <v>1108</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1689</v>
+        <v>1592</v>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
@@ -19592,7 +19612,7 @@
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19643,7 +19663,7 @@
         </is>
       </c>
       <c r="L336" s="3" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M336" s="3" t="n">
         <v>2900</v>
@@ -19656,7 +19676,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19707,7 +19727,7 @@
         </is>
       </c>
       <c r="L337" s="3" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M337" s="3" t="n">
         <v>15500</v>
@@ -19716,11 +19736,11 @@
         <v>317</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19804,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19868,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19912,7 +19932,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -19939,10 +19959,10 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>1025</v>
+        <v>1046</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19966,17 +19986,17 @@
         <v>1266</v>
       </c>
       <c r="M341" s="3" t="n">
-        <v>2435</v>
+        <v>15831</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>784</v>
+        <v>317</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20040,7 +20060,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20097,14 +20117,14 @@
         <v>2435</v>
       </c>
       <c r="N343" s="3" t="n">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="O343" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20123,18 +20143,18 @@
         </is>
       </c>
       <c r="D344" s="3" t="n">
-        <v>2400</v>
+        <v>2238</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>2022</v>
+        <v>2060</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20155,7 +20175,7 @@
         </is>
       </c>
       <c r="L344" s="3" t="n">
-        <v>2238</v>
+        <v>2242</v>
       </c>
       <c r="M344" s="3" t="n">
         <v>57744</v>
@@ -20164,11 +20184,11 @@
         <v>3166</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20187,7 +20207,7 @@
         </is>
       </c>
       <c r="D345" s="3" t="n">
-        <v>19659</v>
+        <v>19658</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
@@ -20195,10 +20215,10 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>2908</v>
+        <v>2950</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20219,20 +20239,20 @@
         </is>
       </c>
       <c r="L345" s="3" t="n">
-        <v>2242</v>
+        <v>2338</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>75864</v>
+        <v>75863</v>
       </c>
       <c r="N345" s="3" t="n">
         <v>4048</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20300,7 @@
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20344,7 +20364,7 @@
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20401,14 +20421,14 @@
         <v>9498</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12665</v>
+        <v>12664</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20462,7 +20482,7 @@
         <v>9498</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19629</v>
+        <v>19628</v>
       </c>
       <c r="N349" s="3" t="n">
         <v>18997</v>
@@ -20472,7 +20492,7 @@
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20520,7 +20540,7 @@
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20539,18 +20559,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>17860</v>
+        <v>20999</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
         <v>57</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17383</v>
+        <v>17312</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20571,20 +20591,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>16972</v>
+        <v>21625</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31662</v>
+        <v>31661</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20603,18 +20623,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>48507</v>
+        <v>48495</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>43086</v>
+        <v>43686</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20635,20 +20655,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>48496</v>
+        <v>48657</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>48496</v>
+        <v>48657</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>75988</v>
+        <v>75987</v>
       </c>
       <c r="O352" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20687,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>116848</v>
+        <v>116847</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20678,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>116848</v>
+        <v>116847</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20701,12 +20721,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>205800</v>
+        <v>205797</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20757,7 +20777,7 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="M354" s="3" t="n">
         <v>1420</v>
@@ -20766,11 +20786,11 @@
         <v>317</v>
       </c>
       <c r="O354" s="2" t="n">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20824,7 +20844,7 @@
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20888,7 @@
         <v>8865</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55408</v>
+        <v>55407</v>
       </c>
       <c r="N356" s="3" t="n">
         <v>17730</v>
@@ -20878,7 +20898,7 @@
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20905,10 +20925,10 @@
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
@@ -20942,7 +20962,7 @@
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -20993,7 +21013,7 @@
         </is>
       </c>
       <c r="L358" s="3" t="n">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="M358" s="3" t="n">
         <v>769</v>
@@ -21006,7 +21026,7 @@
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21056,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>158.307574</v>
+        <v>158.305497</v>
       </c>
     </row>
     <row r="2">
@@ -21047,7 +21067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Wed, 14 Oct 2026 00:02:32 +0000)</t>
+          <t>open.er-api.com (取得日時: Thu, 15 Oct 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21059,7 +21079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -578,14 +578,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3559</v>
+        <v>3523</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -609,17 +609,17 @@
         <v>3160</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1579943</v>
+        <v>1580012</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6320</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         <v>6320</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>96584</v>
+        <v>96588</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>12640</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -740,14 +740,14 @@
         <v>12640</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25279</v>
+        <v>25280</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23699</v>
+        <v>23700</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23699</v>
+        <v>23700</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>23699</v>
+        <v>23700</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>23699</v>
+        <v>23700</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>47398</v>
+        <v>47400</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42686</v>
+        <v>42688</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85317</v>
+        <v>85321</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -916,20 +916,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>126395</v>
+        <v>126401</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>142195</v>
+        <v>142201</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>252791</v>
+        <v>252802</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>355487</v>
+        <v>355503</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>355487</v>
+        <v>355503</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>710975</v>
+        <v>711005</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1002,18 +1002,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6644</v>
+        <v>6211</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6262</v>
+        <v>6266</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5803</v>
+        <v>6205</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1579943</v>
+        <v>1580012</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8690</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8677</v>
+        <v>8559</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8523</v>
+        <v>8527</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1098,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8250</v>
+        <v>8715</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>150054</v>
+        <v>150060</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17379</v>
+        <v>17380</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14545</v>
+        <v>14546</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1165,17 +1165,17 @@
         <v>13904</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42420</v>
+        <v>42422</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34759</v>
+        <v>34760</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1216,20 +1216,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>17256</v>
+        <v>17257</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39499</v>
+        <v>39500</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22119</v>
+        <v>22120</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1270,20 +1270,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>93879</v>
+        <v>93883</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>93879</v>
+        <v>93883</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22119</v>
+        <v>22120</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1324,20 +1324,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>236992</v>
+        <v>237002</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1579943</v>
+        <v>1580012</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>29254</v>
+        <v>29255</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64005</v>
+        <v>64008</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5372</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22516</v>
+        <v>22517</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64005</v>
+        <v>64008</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5372</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
         <v>790</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1579943</v>
+        <v>1580012</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1580</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
         <v>1580</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>227526</v>
+        <v>227536</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3160</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
         <v>3160</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>268590</v>
+        <v>268602</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6320</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
         <v>5688</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22119</v>
+        <v>22120</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>11376</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1715,17 +1715,17 @@
         <v>11060</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36923</v>
+        <v>36925</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22119</v>
+        <v>22120</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1766,20 +1766,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21329</v>
+        <v>21330</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>139462</v>
+        <v>139468</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39499</v>
+        <v>39500</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39499</v>
+        <v>39500</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1830,20 +1830,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39499</v>
+        <v>39500</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>321259</v>
+        <v>321273</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>78997</v>
+        <v>79001</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
         <v>1817</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>2003</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         <v>1450</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>316</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2022,11 +2022,11 @@
         <v>2528</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2045,18 +2045,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1264</v>
+        <v>1248</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1575747</v>
+        <v>1575815</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1580</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2109,18 +2109,18 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1580</v>
+        <v>2951</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1893</v>
+        <v>1925</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2144,17 +2144,17 @@
         <v>1580</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1579943</v>
+        <v>1580012</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3160</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2177,14 +2177,14 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2208,17 +2208,17 @@
         <v>3160</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17022</v>
+        <v>17023</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6320</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2241,11 +2241,11 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>632</v>
@@ -2272,17 +2272,17 @@
         <v>632</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1579943</v>
+        <v>1580012</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1264</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2342,11 +2342,11 @@
         <v>4740</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2400,17 +2400,17 @@
         <v>961</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>631977</v>
+        <v>632005</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1580</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2464,17 +2464,17 @@
         <v>1934</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12799</v>
+        <v>12800</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3160</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3539</v>
+        <v>3528</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2525,20 +2525,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3737</v>
+        <v>3862</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21119</v>
+        <v>21120</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>6320</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
         <v>6320</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30539</v>
+        <v>30540</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>12640</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2625,11 +2625,11 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>790</v>
@@ -2658,11 +2658,11 @@
         <v>1580</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2772,17 +2772,17 @@
         <v>3160</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>315989</v>
+        <v>316002</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6320</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
         <v>1580</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>144639</v>
+        <v>144645</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3160</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2897,20 +2897,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>3160</v>
+        <v>4459</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17381</v>
+        <v>17382</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>6320</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2933,11 +2933,11 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>6320</v>
@@ -2964,17 +2964,17 @@
         <v>6320</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15115</v>
+        <v>15116</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>12640</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2993,18 +2993,18 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>2427</v>
+        <v>3871</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3127</v>
+        <v>3276</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3021,20 +3021,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>3871</v>
+        <v>3876</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>6119</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>3790</v>
+        <v>3945</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6619</v>
+        <v>6771</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3081,20 +3081,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>8879</v>
+        <v>8880</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8879</v>
+        <v>8880</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>6550</v>
+        <v>6551</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3113,18 +3113,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>8687</v>
+        <v>9610</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>42</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9936</v>
+        <v>9832</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3141,20 +3141,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9221</v>
+        <v>9608</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>13758</v>
+        <v>13759</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10047</v>
+        <v>10134</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3208,17 +3208,17 @@
         <v>1580</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8710</v>
+        <v>8711</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3160</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3278,11 +3278,11 @@
         <v>6320</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3355,18 +3355,18 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>779</v>
+        <v>1025</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>779</v>
+        <v>902</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1025</v>
+        <v>1896</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>2616</v>
@@ -3396,11 +3396,11 @@
         <v>1580</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3592,23 +3592,13 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D52" s="3" t="n">
-        <v>6636</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>6636</v>
-      </c>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -3634,7 +3624,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3688,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3742,7 @@
         <v>1896</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11282</v>
+        <v>11283</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1822</v>
@@ -3762,7 +3752,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3806,7 @@
         <v>3160</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30561</v>
+        <v>30562</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3160</v>
@@ -3826,7 +3816,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3883,14 +3873,14 @@
         <v>8219</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>6396</v>
+        <v>6320</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3909,18 +3899,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10677</v>
+        <v>10483</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9717</v>
+        <v>9684</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3941,20 +3931,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>11064</v>
+        <v>10387</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30600</v>
+        <v>30602</v>
       </c>
       <c r="N57" s="3" t="n">
         <v>12640</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3973,18 +3963,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3692</v>
+        <v>3105</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3730</v>
+        <v>3705</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4005,20 +3995,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3781</v>
+        <v>3863</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>10314</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3830</v>
+        <v>3869</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4072,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4126,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4177,10 +4167,10 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>5056</v>
@@ -4190,7 +4180,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4228,7 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4279,20 +4269,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>7118</v>
+        <v>17837</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4325,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4373,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4429,20 +4419,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50558</v>
+        <v>50560</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4486,17 +4476,17 @@
         <v>8848</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22119</v>
+        <v>22120</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4529,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22119</v>
+        <v>22120</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4604,11 +4594,11 @@
         <v>1580</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4658,11 +4648,11 @@
         <v>3160</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4706,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4750,7 @@
         <v>2528</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1482053</v>
+        <v>1482117</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>11376</v>
@@ -4770,7 +4760,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4804,7 @@
         <v>4748</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7468</v>
+        <v>7469</v>
       </c>
       <c r="N73" s="3" t="n">
         <v>9480</v>
@@ -4824,7 +4814,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4868,17 +4858,17 @@
         <v>8690</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20933</v>
+        <v>20934</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17379</v>
+        <v>17380</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4919,20 +4909,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17379</v>
+        <v>17380</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27020</v>
+        <v>27021</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4986,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5040,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5098,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5152,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5200,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5251,10 +5241,10 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23108</v>
+        <v>23109</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23108</v>
+        <v>23109</v>
       </c>
       <c r="N81" s="3" t="n">
         <v>10112</v>
@@ -5264,7 +5254,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5297,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20223</v>
+        <v>20224</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5321,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -5339,10 +5329,10 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5359,20 +5349,20 @@
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="3" t="n">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1579785</v>
+        <v>1579854</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>790</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5412,7 @@
         <v>351</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34538</v>
+        <v>34539</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1580</v>
@@ -5432,7 +5422,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5472,7 @@
         <v>2000</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>3160</v>
@@ -5492,7 +5482,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5542,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5586,7 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5635,12 +5625,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14219</v>
+        <v>14220</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5669,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17379</v>
+        <v>17380</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5707,11 +5697,11 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>495</v>
@@ -5731,20 +5721,20 @@
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="3" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>85867</v>
+        <v>85870</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>790</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5784,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5834,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5884,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5928,7 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -5977,12 +5967,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14219</v>
+        <v>14220</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6011,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17379</v>
+        <v>17380</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6070,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6098,13 +6088,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="3" t="inlineStr"/>
+      <c r="D98" s="3" t="n">
+        <v>2054</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>2054</v>
+      </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="L98" s="3" t="n">
-        <v>2054</v>
+        <v>3465</v>
       </c>
       <c r="M98" s="3" t="n">
         <v>3465</v>
@@ -6130,11 +6130,11 @@
         <v>5056</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6245,14 +6245,14 @@
         <v>7110</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6341,20 +6341,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>17950</v>
+        <v>17951</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>17950</v>
+        <v>17951</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6397,12 +6397,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50558</v>
+        <v>50560</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6595,12 +6595,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6643,12 +6643,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6739,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50558</v>
+        <v>50560</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6787,12 +6787,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>78997</v>
+        <v>79001</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6843,20 +6843,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>96999</v>
+        <v>97003</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>110596</v>
+        <v>110601</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>110596</v>
+        <v>110601</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>110596</v>
+        <v>110601</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6907,20 +6907,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>110596</v>
+        <v>110601</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>110596</v>
+        <v>110601</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>142195</v>
+        <v>142201</v>
       </c>
       <c r="O113" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6961,20 +6961,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>126395</v>
+        <v>126401</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>126395</v>
+        <v>126401</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7015,20 +7015,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>189593</v>
+        <v>189601</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>213292</v>
+        <v>213302</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>213292</v>
+        <v>213302</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -7079,20 +7079,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>213292</v>
+        <v>213302</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>252791</v>
+        <v>252802</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>252791</v>
+        <v>252802</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7292,17 +7292,17 @@
         <v>7110</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14219</v>
+        <v>14220</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14219</v>
+        <v>14220</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7345,12 +7345,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22751</v>
+        <v>22752</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7391,20 +7391,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7445,20 +7445,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>41018</v>
+        <v>41020</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7476,13 +7476,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr"/>
-      <c r="E124" s="2" t="inlineStr"/>
-      <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="3" t="inlineStr"/>
+      <c r="D124" s="3" t="n">
+        <v>1256</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>1256</v>
+      </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
@@ -7499,7 +7509,7 @@
         </is>
       </c>
       <c r="L124" s="3" t="n">
-        <v>1256</v>
+        <v>1923</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>1923</v>
@@ -7508,11 +7518,11 @@
         <v>2212</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7576,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7620,7 @@
         <v>5734</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6452</v>
+        <v>6453</v>
       </c>
       <c r="N126" s="3" t="n">
         <v>7900</v>
@@ -7620,7 +7630,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7664,17 +7674,17 @@
         <v>7110</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11870</v>
+        <v>11871</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14219</v>
+        <v>14220</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7727,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22751</v>
+        <v>22752</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7765,12 +7775,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7828,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7882,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7936,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -7970,17 +7980,17 @@
         <v>9480</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15886</v>
+        <v>15887</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8023,12 +8033,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8069,20 +8079,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21329</v>
+        <v>21330</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21329</v>
+        <v>21330</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47398</v>
+        <v>47400</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8123,20 +8133,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71097</v>
+        <v>71101</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8177,20 +8187,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8264,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8328,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8345,10 +8355,10 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>595</v>
+        <v>656</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8378,11 +8388,11 @@
         <v>801</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8439,14 +8449,14 @@
         <v>1580</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>1738</v>
+        <v>316</v>
       </c>
       <c r="O141" s="2" t="n">
         <v>237</v>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8510,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8564,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8573,18 +8583,18 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>2155</v>
+        <v>2141</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8605,7 +8615,7 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>2141</v>
+        <v>3316</v>
       </c>
       <c r="M144" s="3" t="n">
         <v>10725</v>
@@ -8614,11 +8624,11 @@
         <v>3950</v>
       </c>
       <c r="O144" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8676,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8720,7 @@
         <v>4424</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53431</v>
+        <v>53433</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>6320</v>
@@ -8720,7 +8730,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8778,7 @@
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8812,17 +8822,17 @@
         <v>9480</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17313</v>
+        <v>17314</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8865,12 +8875,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25279</v>
+        <v>25280</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8889,18 +8899,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16132</v>
+        <v>16087</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8921,20 +8931,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39499</v>
+        <v>39500</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -8953,18 +8963,18 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8985,20 +8995,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>63147</v>
+        <v>63150</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75837</v>
+        <v>75841</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9039,20 +9049,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>102696</v>
+        <v>102701</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>102696</v>
+        <v>102701</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>205393</v>
+        <v>205402</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9126,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9190,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9198,13 +9208,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr"/>
-      <c r="E155" s="2" t="inlineStr"/>
-      <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="3" t="inlineStr"/>
+      <c r="D155" s="3" t="n">
+        <v>790</v>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>790</v>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
@@ -9220,17 +9240,17 @@
         <v>790</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15480</v>
+        <v>15481</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1580</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9310,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9360,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9404,7 @@
         <v>790</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1579943</v>
+        <v>1580012</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1580</v>
@@ -9394,7 +9414,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9438,17 +9458,17 @@
         <v>1580</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19160</v>
+        <v>19161</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3160</v>
       </c>
       <c r="O159" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9522,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9525,11 +9545,11 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G161" s="3" t="n">
         <v>1580</v>
@@ -9559,14 +9579,14 @@
         <v>1580</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>316</v>
+        <v>1738</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9640,7 @@
         <v>1845</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30145</v>
+        <v>30147</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1580</v>
@@ -9630,7 +9650,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9669,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>3624</v>
+        <v>3625</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -9681,7 +9701,7 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>2109</v>
+        <v>3628</v>
       </c>
       <c r="M163" s="3" t="n">
         <v>3844</v>
@@ -9690,11 +9710,11 @@
         <v>3160</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9713,18 +9733,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>4072</v>
+        <v>3974</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3788</v>
+        <v>3793</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9745,7 +9765,7 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>4070</v>
+        <v>3882</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>10270</v>
@@ -9754,11 +9774,11 @@
         <v>6320</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9777,18 +9797,18 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -9809,7 +9829,7 @@
         </is>
       </c>
       <c r="L165" s="3" t="n">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="M165" s="3" t="n">
         <v>4906</v>
@@ -9818,11 +9838,11 @@
         <v>316</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9896,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9950,7 @@
         <v>1564</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9710</v>
+        <v>9711</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1264</v>
@@ -9940,7 +9960,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10014,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10058,7 @@
         <v>329</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>316</v>
@@ -10048,7 +10068,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10087,7 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>94797</v>
+        <v>94801</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>94797</v>
+        <v>94801</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -10099,20 +10119,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94797</v>
+        <v>94801</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94797</v>
+        <v>94801</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>126395</v>
+        <v>126401</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10155,12 +10175,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10230,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10280,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10324,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10344,17 +10364,17 @@
         <v>7110</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14189</v>
+        <v>14190</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14219</v>
+        <v>14220</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10397,14 +10417,14 @@
         <v>11376</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22751</v>
+        <v>22752</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10441,20 +10461,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>15878</v>
+        <v>15879</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10491,20 +10511,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19117</v>
+        <v>19118</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10572,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10626,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10674,7 @@
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10701,14 +10721,14 @@
         <v>9480</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10751,12 +10771,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10797,20 +10817,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21329</v>
+        <v>21330</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21329</v>
+        <v>21330</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42658</v>
+        <v>42660</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10851,20 +10871,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56878</v>
+        <v>56880</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10928,7 @@
         <v>158</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>316</v>
@@ -10918,7 +10938,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10982,7 @@
         <v>158</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>316</v>
@@ -10972,7 +10992,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -10995,11 +11015,11 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>158</v>
@@ -11026,17 +11046,17 @@
         <v>158</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11104,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11148,7 @@
         <v>158</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29140</v>
+        <v>29142</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>316</v>
@@ -11138,7 +11158,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11202,7 @@
         <v>158</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>155993</v>
+        <v>155999</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>316</v>
@@ -11192,7 +11212,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11266,7 @@
         <v>158</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>316</v>
@@ -11256,7 +11276,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11324,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11322,13 +11342,23 @@
           <t>チップ / チップ</t>
         </is>
       </c>
-      <c r="D194" s="3" t="inlineStr"/>
-      <c r="E194" s="2" t="inlineStr"/>
-      <c r="F194" s="2" t="inlineStr"/>
-      <c r="G194" s="3" t="inlineStr"/>
+      <c r="D194" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>158</v>
+      </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I194" s="2" t="n">
@@ -11348,17 +11378,17 @@
         <v>158</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11432,7 @@
         <v>158</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>316</v>
@@ -11412,7 +11442,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11461,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>21277</v>
+        <v>21278</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11472,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>21277</v>
+        <v>21278</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -11466,17 +11496,17 @@
         <v>158</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N196" s="3" t="n">
-        <v>23404</v>
+        <v>23405</v>
       </c>
       <c r="O196" s="2" t="n">
         <v>563</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11554,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11608,7 @@
         <v>877</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>316</v>
@@ -11588,7 +11618,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11629,20 +11659,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20574</v>
+        <v>20575</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20574</v>
+        <v>20575</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11726,7 @@
         <v>4424</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6299</v>
+        <v>6300</v>
       </c>
       <c r="N200" s="3" t="n">
         <v>6320</v>
@@ -11706,7 +11736,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11780,7 @@
         <v>5056</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10764</v>
+        <v>10765</v>
       </c>
       <c r="N201" s="3" t="n">
         <v>7584</v>
@@ -11760,7 +11790,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11834,7 @@
         <v>6320</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10339</v>
+        <v>10340</v>
       </c>
       <c r="N202" s="3" t="n">
         <v>10112</v>
@@ -11814,7 +11844,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11888,7 @@
         <v>8216</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>275811</v>
+        <v>275823</v>
       </c>
       <c r="N203" s="3" t="n">
         <v>13904</v>
@@ -11868,7 +11898,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11909,20 +11939,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15611</v>
+        <v>15612</v>
       </c>
       <c r="M204" s="3" t="n">
         <v>16024</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -11963,20 +11993,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20223</v>
+        <v>20224</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>48740</v>
+        <v>48742</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12019,12 +12049,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22751</v>
+        <v>22752</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12105,7 @@
         </is>
       </c>
       <c r="L207" s="3" t="n">
-        <v>629</v>
+        <v>532</v>
       </c>
       <c r="M207" s="3" t="n">
         <v>1580</v>
@@ -12084,11 +12114,11 @@
         <v>316</v>
       </c>
       <c r="O207" s="2" t="n">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12172,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12213,7 @@
         </is>
       </c>
       <c r="L209" s="3" t="n">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="M209" s="3" t="n">
         <v>2999</v>
@@ -12196,7 +12226,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12260,7 +12290,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12344,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12361,14 +12391,14 @@
         <v>7110</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14219</v>
+        <v>14220</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12411,12 +12441,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22751</v>
+        <v>22752</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12457,20 +12487,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12524,7 +12554,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12608,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12622,17 +12652,17 @@
         <v>13904</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>29314</v>
+        <v>29316</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25279</v>
+        <v>25280</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12673,7 +12703,7 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>4858</v>
+        <v>4859</v>
       </c>
       <c r="M218" s="3" t="n">
         <v>4871</v>
@@ -12686,7 +12716,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12733,14 +12763,14 @@
         <v>7110</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14219</v>
+        <v>14220</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12783,12 +12813,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12829,20 +12859,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12902,11 +12932,11 @@
         <v>1580</v>
       </c>
       <c r="O222" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -12966,11 +12996,11 @@
         <v>3160</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13044,7 @@
         <v>3160</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7190</v>
+        <v>7191</v>
       </c>
       <c r="N224" s="3" t="n">
         <v>6320</v>
@@ -13024,7 +13054,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13078,7 +13108,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13162,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13226,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13240,7 +13270,7 @@
         <v>158</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>316</v>
@@ -13250,7 +13280,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13324,7 @@
         <v>158</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>316</v>
@@ -13304,7 +13334,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13353,7 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>44659</v>
+        <v>44661</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -13334,7 +13364,7 @@
         <v>1</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>44659</v>
+        <v>44661</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -13358,7 +13388,7 @@
         <v>158</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>316</v>
@@ -13368,7 +13398,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13442,7 @@
         <v>790</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1580</v>
@@ -13422,7 +13452,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13482,11 +13512,11 @@
         <v>3160</v>
       </c>
       <c r="O232" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13560,7 @@
         <v>3160</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7198</v>
+        <v>7199</v>
       </c>
       <c r="N233" s="3" t="n">
         <v>6320</v>
@@ -13540,7 +13570,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13604,7 +13634,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13678,7 @@
         <v>3888</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>3932</v>
+        <v>3933</v>
       </c>
       <c r="N235" s="3" t="n">
         <v>3160</v>
@@ -13658,7 +13688,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13712,7 +13742,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13760,7 +13790,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13844,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13862,7 +13892,7 @@
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13905,12 +13935,12 @@
       <c r="L240" s="3" t="inlineStr"/>
       <c r="M240" s="3" t="inlineStr"/>
       <c r="N240" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13959,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -13940,7 +13970,7 @@
         <v>10</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>18667</v>
+        <v>18668</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -13961,20 +13991,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>22094</v>
+        <v>22095</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30610</v>
+        <v>30611</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O241" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -13993,7 +14023,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>41949</v>
+        <v>41951</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14004,7 +14034,7 @@
         <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>39934</v>
+        <v>39936</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14025,20 +14055,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>53369</v>
+        <v>53371</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58540</v>
+        <v>58543</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75837</v>
+        <v>75841</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14057,7 +14087,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14068,7 +14098,7 @@
         <v>11</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>19575</v>
+        <v>19576</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14085,20 +14115,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>18628</v>
+        <v>18443</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31598869</v>
+        <v>31600233</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14141,12 +14171,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25279</v>
+        <v>25280</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14230,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14251,20 +14281,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>3430</v>
+        <v>3427</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>4195</v>
+        <v>4046</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14305,20 +14335,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15515</v>
+        <v>15516</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23295</v>
+        <v>23296</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17695</v>
+        <v>17696</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14361,12 +14391,12 @@
       <c r="L248" s="3" t="inlineStr"/>
       <c r="M248" s="3" t="inlineStr"/>
       <c r="N248" s="3" t="n">
-        <v>17695</v>
+        <v>17696</v>
       </c>
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14412,11 +14442,11 @@
         <v>1580</v>
       </c>
       <c r="O249" s="2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14466,7 +14496,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14540,7 @@
         <v>158</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97152</v>
+        <v>97156</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>316</v>
@@ -14520,7 +14550,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14571,10 +14601,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50343</v>
+        <v>50345</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50343</v>
+        <v>50345</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6320</v>
@@ -14584,7 +14614,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14665,7 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>8502</v>
+        <v>5491</v>
       </c>
       <c r="M253" s="3" t="n">
         <v>8502</v>
@@ -14644,11 +14674,11 @@
         <v>7584</v>
       </c>
       <c r="O253" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14742,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14766,7 +14796,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14850,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14904,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -14897,14 +14927,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -14934,11 +14964,11 @@
         <v>632</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15032,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15056,7 +15086,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15150,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15180,11 +15210,11 @@
         <v>12640</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15244,11 +15274,11 @@
         <v>1580</v>
       </c>
       <c r="O263" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15289,7 +15319,7 @@
         </is>
       </c>
       <c r="L264" s="3" t="n">
-        <v>1612</v>
+        <v>1580</v>
       </c>
       <c r="M264" s="3" t="n">
         <v>1612</v>
@@ -15298,11 +15328,11 @@
         <v>3160</v>
       </c>
       <c r="O264" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15380,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15401,10 +15431,10 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6784</v>
+        <v>6785</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9628</v>
+        <v>9629</v>
       </c>
       <c r="N266" s="3" t="n">
         <v>12640</v>
@@ -15414,7 +15444,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15444,7 +15474,7 @@
         <v>4</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15468,7 +15498,7 @@
         <v>3318</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19432</v>
+        <v>19433</v>
       </c>
       <c r="N267" s="3" t="n">
         <v>1713</v>
@@ -15478,7 +15508,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15508,7 +15538,7 @@
         <v>2</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8578</v>
+        <v>8579</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15529,10 +15559,10 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>12611</v>
+        <v>12612</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14232</v>
+        <v>14233</v>
       </c>
       <c r="N268" s="3" t="n">
         <v>13904</v>
@@ -15542,7 +15572,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15585,12 +15615,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15633,12 +15663,12 @@
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="3" t="n">
-        <v>25279</v>
+        <v>25280</v>
       </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15657,7 +15687,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15668,7 +15698,7 @@
         <v>4</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>23619</v>
+        <v>23620</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15689,20 +15719,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>28439</v>
+        <v>28440</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15746,7 +15776,7 @@
         <v>158</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>316</v>
@@ -15756,7 +15786,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15800,7 +15830,7 @@
         <v>158</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>20925</v>
+        <v>20926</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>316</v>
@@ -15810,7 +15840,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15864,7 +15894,7 @@
         <v>158</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31703</v>
+        <v>31705</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>316</v>
@@ -15874,7 +15904,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15928,7 +15958,7 @@
         <v>158</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15878</v>
+        <v>15879</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>316</v>
@@ -15938,7 +15968,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -15982,7 +16012,7 @@
         <v>158</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>157519</v>
+        <v>157526</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>316</v>
@@ -15992,7 +16022,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16038,11 +16068,11 @@
         <v>1580</v>
       </c>
       <c r="O277" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16106,7 +16136,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16190,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16244,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16262,7 +16292,7 @@
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16305,12 +16335,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16353,12 +16383,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25279</v>
+        <v>25280</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16399,20 +16429,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>20223</v>
+        <v>20224</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33688</v>
+        <v>33689</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16431,18 +16461,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>10612</v>
+        <v>10622</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9041</v>
+        <v>9132</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16463,20 +16493,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>10630</v>
+        <v>10610</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>11219</v>
+        <v>11313</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16540,7 +16570,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16589,7 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5332</v>
+        <v>5333</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
@@ -16587,20 +16617,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>6204</v>
+        <v>6205</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5862</v>
+        <v>1580</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16619,18 +16649,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6841</v>
+        <v>6017</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6644</v>
+        <v>6605</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16647,20 +16677,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7672</v>
+        <v>6017</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>7751</v>
+        <v>7752</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>6936</v>
+        <v>6990</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16679,18 +16709,18 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>10786</v>
+        <v>11153</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>10558</v>
+        <v>10608</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16713,14 +16743,14 @@
         <v>11662</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>11627</v>
+        <v>11883</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16814,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16803,18 +16833,18 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>1845</v>
+        <v>1923</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>2401</v>
+        <v>2264</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -16835,7 +16865,7 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>1921</v>
+        <v>2615</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5056</v>
@@ -16844,11 +16874,11 @@
         <v>3160</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16867,18 +16897,18 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>5168</v>
+        <v>3884</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4722</v>
+        <v>4442</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16899,7 +16929,7 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>3884</v>
+        <v>5372</v>
       </c>
       <c r="M292" s="3" t="n">
         <v>5688</v>
@@ -16908,11 +16938,11 @@
         <v>6320</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16976,7 +17006,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16995,18 +17025,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>8710</v>
+        <v>7276</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7450</v>
+        <v>7473</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17027,20 +17057,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>7280</v>
+        <v>7183</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>21498</v>
+        <v>21499</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>7789</v>
+        <v>7612</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17081,20 +17111,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51353</v>
+        <v>51355</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>697926</v>
+        <v>697956</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39499</v>
+        <v>39500</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17113,18 +17143,18 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F296" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17145,20 +17175,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68694</v>
+        <v>68697</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39499</v>
+        <v>39500</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17177,18 +17207,18 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63198</v>
+        <v>63200</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63198</v>
+        <v>63200</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17209,20 +17239,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63198</v>
+        <v>63200</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>126395</v>
+        <v>126401</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>78997</v>
+        <v>79001</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17241,7 +17271,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>126395</v>
+        <v>126401</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17252,7 +17282,7 @@
         <v>1</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>126395</v>
+        <v>126401</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17273,20 +17303,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>126395</v>
+        <v>126401</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>126399</v>
+        <v>126404</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>157994</v>
+        <v>158001</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17305,7 +17335,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>252791</v>
+        <v>252802</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17316,7 +17346,7 @@
         <v>2</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>252791</v>
+        <v>252802</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17337,20 +17367,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>252791</v>
+        <v>252802</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>252793</v>
+        <v>252803</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>315989</v>
+        <v>316002</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17399,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>442384</v>
+        <v>442403</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17380,7 +17410,7 @@
         <v>2</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>442384</v>
+        <v>442403</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17401,20 +17431,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>442384</v>
+        <v>442403</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>950726</v>
+        <v>950767</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>631977</v>
+        <v>632005</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17433,18 +17463,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>3700</v>
+        <v>3331</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2367</v>
+        <v>2389</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17465,20 +17495,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>3106</v>
+        <v>3201</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2637</v>
+        <v>2860</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17497,18 +17527,18 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>2492</v>
+        <v>2231</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1856</v>
+        <v>1887</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17529,20 +17559,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>2405</v>
+        <v>2231</v>
       </c>
       <c r="M302" s="3" t="n">
         <v>4792</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2234</v>
+        <v>2278</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17565,14 +17595,14 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4362</v>
+        <v>4379</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17596,7 +17626,7 @@
         <v>4738</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N303" s="3" t="n">
         <v>5212</v>
@@ -17606,7 +17636,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17625,7 +17655,7 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>3779</v>
+        <v>2173</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -17633,10 +17663,10 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1649</v>
+        <v>1707</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17657,20 +17687,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>1457</v>
+        <v>4817</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>3662</v>
+        <v>3154</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17764,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17757,11 +17787,11 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G306" s="3" t="n">
         <v>158</v>
@@ -17788,17 +17818,17 @@
         <v>158</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>20168</v>
+        <v>20216</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17882,7 @@
         <v>920</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>316</v>
@@ -17862,7 +17892,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17946,7 @@
         <v>2054</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1263955</v>
+        <v>1264009</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>3950</v>
@@ -17926,7 +17956,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -17980,7 +18010,7 @@
         <v>4424</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>31946</v>
+        <v>31948</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6320</v>
@@ -17990,7 +18020,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18050,7 @@
         <v>3</v>
       </c>
       <c r="G310" s="3" t="n">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
@@ -18054,7 +18084,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18138,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18186,7 @@
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18210,17 +18240,17 @@
         <v>9480</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26123</v>
+        <v>26124</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O313" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18267,14 +18297,14 @@
         <v>15457</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25279</v>
+        <v>25280</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18293,18 +18323,18 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18325,20 +18355,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1579943</v>
+        <v>1580012</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O315" s="2" t="n">
         <v>105</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18387,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18365,10 +18395,10 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18389,20 +18419,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>37919</v>
+        <v>37920</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75837</v>
+        <v>75841</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18421,7 +18451,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>102696</v>
+        <v>102701</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18432,7 +18462,7 @@
         <v>2</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>102696</v>
+        <v>102701</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18453,20 +18483,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>102696</v>
+        <v>102701</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>102696</v>
+        <v>102701</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>205393</v>
+        <v>205402</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18485,18 +18515,18 @@
         </is>
       </c>
       <c r="D318" s="3" t="n">
-        <v>485</v>
+        <v>736</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>792</v>
+        <v>805</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18517,20 +18547,20 @@
         </is>
       </c>
       <c r="L318" s="3" t="n">
-        <v>863</v>
+        <v>736</v>
       </c>
       <c r="M318" s="3" t="n">
         <v>2049</v>
       </c>
       <c r="N318" s="3" t="n">
-        <v>316</v>
+        <v>913</v>
       </c>
       <c r="O318" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18584,7 +18614,7 @@
         <v>1392</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15692</v>
+        <v>15693</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>316</v>
@@ -18594,7 +18624,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18613,18 +18643,18 @@
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>3585</v>
+        <v>1106</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>2202</v>
+        <v>2033</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18645,20 +18675,20 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>1106</v>
+        <v>2117</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9816</v>
+        <v>9817</v>
       </c>
       <c r="N320" s="3" t="n">
         <v>2212</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18685,10 +18715,10 @@
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3234</v>
+        <v>3217</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18722,7 +18752,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18803,7 @@
         </is>
       </c>
       <c r="L322" s="3" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M322" s="3" t="n">
         <v>1035</v>
@@ -18786,7 +18816,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18805,18 +18835,18 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>2044</v>
+        <v>4501</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>2065</v>
+        <v>2471</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18840,17 +18870,17 @@
         <v>2953</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>2444</v>
+        <v>2945</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18907,14 +18937,14 @@
         <v>5587</v>
       </c>
       <c r="N324" s="3" t="n">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="O324" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18941,10 +18971,10 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2881</v>
+        <v>2888</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18968,17 +18998,17 @@
         <v>2910</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15692</v>
+        <v>15693</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="O325" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19029,20 +19059,20 @@
         </is>
       </c>
       <c r="L326" s="3" t="n">
-        <v>6794</v>
+        <v>4748</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>2354</v>
+        <v>2212</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19093,10 +19123,10 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N327" s="3" t="n">
         <v>2462</v>
@@ -19106,7 +19136,7 @@
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19125,7 +19155,7 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>27178</v>
+        <v>27179</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
@@ -19133,10 +19163,10 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>24182</v>
+        <v>24242</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19157,20 +19187,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>27278</v>
+        <v>25239</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>30523</v>
+        <v>30524</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>28937</v>
+        <v>28970</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19189,18 +19219,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7424</v>
+        <v>7764</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
         <v>40</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7231</v>
+        <v>7245</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19221,20 +19251,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7764</v>
+        <v>7766</v>
       </c>
       <c r="M329" s="3" t="n">
         <v>9758</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8184</v>
+        <v>8205</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19253,18 +19283,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5241</v>
+        <v>6088</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5764</v>
+        <v>5761</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19285,20 +19315,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5716</v>
+        <v>6228</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8645</v>
+        <v>8646</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6294</v>
+        <v>6331</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19362,7 +19392,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19381,18 +19411,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>1447</v>
+        <v>1490</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
         <v>26</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1331</v>
+        <v>1351</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19413,20 +19443,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1447</v>
+        <v>1556</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19445,18 +19475,18 @@
         </is>
       </c>
       <c r="D333" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G333" s="3" t="n">
         <v>235</v>
-      </c>
-      <c r="E333" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="F333" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G333" s="3" t="n">
-        <v>230</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19480,7 +19510,7 @@
         <v>235</v>
       </c>
       <c r="M333" s="3" t="n">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="N333" s="3" t="n">
         <v>316</v>
@@ -19490,7 +19520,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19574,7 @@
         <v>427</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>574</v>
@@ -19554,7 +19584,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19577,14 +19607,14 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1589</v>
+        <v>1520</v>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
@@ -19605,20 +19635,20 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1106</v>
+        <v>2729</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N335" s="3" t="n">
         <v>2212</v>
       </c>
       <c r="O335" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19648,7 +19678,7 @@
         <v>8</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19672,7 +19702,7 @@
         <v>427</v>
       </c>
       <c r="M336" s="3" t="n">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="N336" s="3" t="n">
         <v>512</v>
@@ -19682,7 +19712,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19766,7 @@
         <v>188</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15469</v>
+        <v>15470</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>316</v>
@@ -19746,7 +19776,7 @@
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19803,14 +19833,14 @@
         <v>978</v>
       </c>
       <c r="N338" s="3" t="n">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="O338" s="2" t="n">
         <v>33</v>
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19904,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19925,7 +19955,7 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>837</v>
+        <v>1038</v>
       </c>
       <c r="M340" s="3" t="n">
         <v>3160</v>
@@ -19934,11 +19964,11 @@
         <v>316</v>
       </c>
       <c r="O340" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19957,18 +19987,18 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>1264</v>
+        <v>1534</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>1077</v>
+        <v>1125</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19989,20 +20019,20 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>1438</v>
+        <v>1534</v>
       </c>
       <c r="M341" s="3" t="n">
         <v>2430</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>1390</v>
+        <v>1553</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20066,7 +20096,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20085,18 +20115,18 @@
         </is>
       </c>
       <c r="D343" s="3" t="n">
-        <v>384</v>
+        <v>471</v>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
@@ -20123,14 +20153,14 @@
         <v>2430</v>
       </c>
       <c r="N343" s="3" t="n">
-        <v>422</v>
+        <v>485</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20157,10 +20187,10 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>2074</v>
+        <v>2129</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20184,17 +20214,17 @@
         <v>2239</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57630</v>
+        <v>57633</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3160</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20221,10 +20251,10 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>3116</v>
+        <v>3183</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20245,20 +20275,20 @@
         </is>
       </c>
       <c r="L345" s="3" t="n">
-        <v>2360</v>
+        <v>2135</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>75714</v>
+        <v>75717</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>4748</v>
+        <v>6227</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20306,7 +20336,7 @@
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20329,11 +20359,11 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F347" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G347" s="3" t="n">
         <v>4424</v>
@@ -20366,11 +20396,11 @@
         <v>6320</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20389,7 +20419,7 @@
         </is>
       </c>
       <c r="D348" s="3" t="n">
-        <v>8078</v>
+        <v>8079</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
@@ -20400,7 +20430,7 @@
         <v>1</v>
       </c>
       <c r="G348" s="3" t="n">
-        <v>8078</v>
+        <v>8079</v>
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
@@ -20434,7 +20464,7 @@
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20457,11 +20487,11 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G349" s="3" t="n">
         <v>9480</v>
@@ -20488,17 +20518,17 @@
         <v>9480</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19590</v>
+        <v>19591</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>18959</v>
+        <v>18960</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20541,12 +20571,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25279</v>
+        <v>25280</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20565,18 +20595,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>20558</v>
+        <v>20867</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17297</v>
+        <v>17402</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20597,20 +20627,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>21095</v>
+        <v>17472</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31599</v>
+        <v>31600</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20629,18 +20659,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>48561</v>
+        <v>47484</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>44096</v>
+        <v>44406</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20660,21 +20690,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L352" s="3" t="n">
-        <v>47482</v>
-      </c>
-      <c r="M352" s="3" t="n">
-        <v>47482</v>
-      </c>
+      <c r="L352" s="3" t="inlineStr"/>
+      <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="3" t="n">
-        <v>75837</v>
-      </c>
-      <c r="O352" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>75841</v>
+      </c>
+      <c r="O352" s="2" t="inlineStr"/>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20693,7 +20717,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>116617</v>
+        <v>116622</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20704,7 +20728,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>116617</v>
+        <v>116622</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20727,12 +20751,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>205393</v>
+        <v>205402</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20783,7 +20807,7 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="M354" s="3" t="n">
         <v>1417</v>
@@ -20796,7 +20820,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20840,17 +20864,17 @@
         <v>8848</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>18920</v>
+        <v>18921</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17695</v>
+        <v>17696</v>
       </c>
       <c r="O355" s="2" t="n">
         <v>86</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20894,17 +20918,17 @@
         <v>8848</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55298</v>
+        <v>55300</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17695</v>
+        <v>17696</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>71</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -20927,14 +20951,14 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
@@ -20958,17 +20982,17 @@
         <v>483</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>15799</v>
+        <v>15800</v>
       </c>
       <c r="N357" s="3" t="n">
         <v>531</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -21025,14 +21049,14 @@
         <v>768</v>
       </c>
       <c r="N358" s="3" t="n">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="O358" s="2" t="n">
         <v>512</v>
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -21062,7 +21086,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>157.994345</v>
+        <v>158.001167</v>
       </c>
     </row>
     <row r="2">
@@ -21073,7 +21097,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 17 Oct 2026 00:02:32 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 18 Oct 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21085,7 +21109,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -578,14 +578,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
         <v>13</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3370</v>
+        <v>3331</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>3137</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1568397</v>
+        <v>1568426</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6274</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         <v>6274</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>95878</v>
+        <v>95879</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>12547</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -740,14 +740,14 @@
         <v>12547</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25094</v>
+        <v>25095</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -770,11 +770,11 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>23526</v>
@@ -797,21 +797,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>23526</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>23526</v>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>47052</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>47053</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -868,14 +862,14 @@
         <v>42347</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>84693</v>
+        <v>84695</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -916,20 +910,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>125472</v>
+        <v>125474</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>141156</v>
+        <v>141158</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>250944</v>
+        <v>250948</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -970,20 +964,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>352889</v>
+        <v>352896</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>352889</v>
+        <v>352896</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>705779</v>
+        <v>705792</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1002,18 +996,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6093</v>
+        <v>6016</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>38</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6157</v>
+        <v>6116</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1034,20 +1028,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5828</v>
+        <v>6015</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1568397</v>
+        <v>1568426</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8626</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1060,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8869</v>
+        <v>9608</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>57</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8467</v>
+        <v>8507</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1092,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8493</v>
+        <v>9026</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>148957</v>
+        <v>148960</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17252</v>
+        <v>17253</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1134,14 +1128,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14055</v>
+        <v>14031</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1165,17 +1159,17 @@
         <v>13802</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>34505</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1213,7 @@
         <v>8783</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39210</v>
+        <v>39211</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>21958</v>
@@ -1229,7 +1223,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1270,10 +1264,10 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>93193</v>
+        <v>93194</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>93193</v>
+        <v>93194</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>21958</v>
@@ -1283,7 +1277,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1324,10 +1318,10 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>188208</v>
+        <v>188211</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1568397</v>
+        <v>1568426</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>15684</v>
@@ -1337,7 +1331,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1378,10 +1372,10 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>33998</v>
+        <v>33999</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>63537</v>
+        <v>63538</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5333</v>
@@ -1391,7 +1385,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1426,10 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22351</v>
+        <v>22352</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>63537</v>
+        <v>63538</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5333</v>
@@ -1445,7 +1439,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1483,7 @@
         <v>784</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1568397</v>
+        <v>1568426</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1568</v>
@@ -1499,7 +1493,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1537,7 @@
         <v>1568</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>225863</v>
+        <v>225867</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3137</v>
@@ -1553,7 +1547,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1591,7 @@
         <v>3137</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>266627</v>
+        <v>266632</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6274</v>
@@ -1607,7 +1601,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1654,14 +1648,14 @@
         <v>21958</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11292</v>
+        <v>11293</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1699,7 @@
         <v>10979</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36653</v>
+        <v>36654</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>21958</v>
@@ -1715,7 +1709,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1756,10 +1750,10 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21173</v>
+        <v>21174</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>138442</v>
+        <v>138445</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>42347</v>
@@ -1769,7 +1763,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1787,23 +1781,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>39210</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>39210</v>
-      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
@@ -1820,20 +1804,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39210</v>
+        <v>39211</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>318912</v>
+        <v>318917</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>78420</v>
+        <v>78421</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1853,18 +1837,18 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1684</v>
+        <v>1910</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1582</v>
+        <v>1665</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1885,20 +1869,20 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1830</v>
+        <v>2037</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>15684</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1852</v>
+        <v>1934</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1912,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1962,7 +1946,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2000,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2054,7 @@
         <v>1263</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1564231</v>
+        <v>1564260</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1568</v>
@@ -2080,7 +2064,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2099,18 +2083,18 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1890</v>
+        <v>1568</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1786</v>
+        <v>1825</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2131,20 +2115,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2793</v>
+        <v>1568</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1568397</v>
+        <v>1568426</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3137</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2155,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>3145</v>
@@ -2208,7 +2192,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2246,7 @@
         <v>627</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1568397</v>
+        <v>1568426</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1255</v>
@@ -2272,7 +2256,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2310,17 @@
         <v>2353</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11441</v>
+        <v>11442</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>4705</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2387,20 +2371,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>954</v>
+        <v>853</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>627359</v>
+        <v>627370</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1568</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2419,18 +2403,18 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1926</v>
+        <v>2619</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1965</v>
+        <v>1998</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2451,7 +2435,7 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2619</v>
+        <v>2480</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>12706</v>
@@ -2464,7 +2448,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2483,18 +2467,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3460</v>
+        <v>3653</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3437</v>
+        <v>3434</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2499,7 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3137</v>
+        <v>3736</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>20965</v>
@@ -2524,11 +2508,11 @@
         <v>6274</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2542,7 @@
         <v>15</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6631</v>
+        <v>6632</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2588,11 +2572,11 @@
         <v>12547</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2636,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2696,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2762,17 +2746,17 @@
         <v>3137</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>313679</v>
+        <v>313685</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6274</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2810,7 @@
         <v>1568</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>143582</v>
+        <v>143585</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3137</v>
@@ -2836,7 +2820,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2871,7 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>3137</v>
+        <v>4426</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>17254</v>
@@ -2896,11 +2880,11 @@
         <v>6274</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2923,11 +2907,11 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>6274</v>
@@ -2960,11 +2944,11 @@
         <v>12547</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3014,17 +2998,17 @@
         <v>3556</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6074</v>
+        <v>6075</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>4227</v>
+        <v>2196</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3027,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6430</v>
+        <v>6431</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3051,10 +3035,10 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6672</v>
+        <v>6816</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3074,17 +3058,17 @@
         <v>6545</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8814</v>
+        <v>8815</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>7073</v>
+        <v>7074</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3107,14 +3091,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9671</v>
+        <v>9649</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3131,20 +3115,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9589</v>
+        <v>9592</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>13658</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10715</v>
+        <v>10625</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3167,11 +3151,11 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>1568</v>
@@ -3204,11 +3188,11 @@
         <v>3137</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3256,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3310,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3361,7 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1371</v>
+        <v>1266</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>2597</v>
@@ -3390,7 +3374,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3428,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3488,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3548,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3598,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3662,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3726,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3780,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3844,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3879,18 +3863,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9984</v>
+        <v>9411</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9419</v>
+        <v>9434</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3911,7 +3895,7 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9221</v>
+        <v>9299</v>
       </c>
       <c r="M57" s="3" t="n">
         <v>30377</v>
@@ -3920,11 +3904,11 @@
         <v>12547</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3943,18 +3927,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3785</v>
+        <v>3863</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3642</v>
+        <v>3640</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3975,20 +3959,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3824</v>
+        <v>3882</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10238</v>
+        <v>10239</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3971</v>
+        <v>4106</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4036,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4090,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4144,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4192,7 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4246,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4289,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4342,7 @@
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4405,14 +4389,14 @@
         <v>18821</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50189</v>
+        <v>50190</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4440,7 @@
         <v>8783</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>21958</v>
@@ -4466,7 +4450,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4498,7 @@
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4552,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4606,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4660,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4720,17 +4704,17 @@
         <v>2509</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1471222</v>
+        <v>1471249</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11292</v>
+        <v>11293</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4777,14 +4761,14 @@
         <v>7414</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4831,14 +4815,14 @@
         <v>20780</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17252</v>
+        <v>17253</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4879,20 +4863,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17252</v>
+        <v>17253</v>
       </c>
       <c r="M75" s="3" t="n">
         <v>26823</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4940,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5010,7 +4994,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5042,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5096,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5144,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5201,10 +5185,10 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>22939</v>
+        <v>22940</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>22939</v>
+        <v>22940</v>
       </c>
       <c r="N81" s="3" t="n">
         <v>10038</v>
@@ -5214,7 +5198,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5257,12 +5241,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20075</v>
+        <v>20076</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5281,18 +5265,18 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5309,20 +5293,20 @@
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1568240</v>
+        <v>1568269</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>784</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5356,7 @@
         <v>348</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34285</v>
+        <v>34286</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1568</v>
@@ -5382,7 +5366,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5426,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5486,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5530,7 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5574,7 @@
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5613,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17252</v>
+        <v>17253</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5653,18 +5637,18 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -5681,20 +5665,20 @@
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="3" t="n">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>85239</v>
+        <v>85241</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>784</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5728,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5778,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5828,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5872,7 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5916,7 @@
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -5971,12 +5955,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17252</v>
+        <v>17253</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6014,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6081,10 +6065,10 @@
         </is>
       </c>
       <c r="L98" s="3" t="n">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="N98" s="3" t="n">
         <v>5019</v>
@@ -6094,7 +6078,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6142,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6196,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6255,12 +6239,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6298,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6357,12 +6341,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50189</v>
+        <v>50190</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6400,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6448,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6496,7 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6544,7 @@
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6603,12 +6587,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6640,7 @@
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6699,12 +6683,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50189</v>
+        <v>50190</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6731,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>78420</v>
+        <v>78421</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6755,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>86262</v>
+        <v>86263</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6766,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>86262</v>
+        <v>86263</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6803,20 +6787,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>86262</v>
+        <v>86263</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>96290</v>
+        <v>96292</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>109788</v>
+        <v>109790</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6819,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>109788</v>
+        <v>109790</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -6846,7 +6830,7 @@
         <v>2</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>109788</v>
+        <v>109790</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6867,20 +6851,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>109788</v>
+        <v>109790</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>109788</v>
+        <v>109790</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>141156</v>
+        <v>141158</v>
       </c>
       <c r="O113" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6921,20 +6905,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>125472</v>
+        <v>125474</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>125472</v>
+        <v>125474</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6975,20 +6959,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>188208</v>
+        <v>188211</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7007,7 +6991,7 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>211734</v>
+        <v>211737</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -7018,7 +7002,7 @@
         <v>2</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>211734</v>
+        <v>211737</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -7039,20 +7023,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>211734</v>
+        <v>211737</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>250944</v>
+        <v>250948</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>250944</v>
+        <v>250948</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7090,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7144,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7192,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7246,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7294,7 @@
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7357,14 +7341,14 @@
         <v>15684</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7402,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7466,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7520,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7574,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7618,7 @@
         <v>7058</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11783</v>
+        <v>11784</v>
       </c>
       <c r="N127" s="3" t="n">
         <v>14116</v>
@@ -7644,7 +7628,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7676,7 @@
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7735,12 +7719,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7772,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7826,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7880,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7937,10 +7921,10 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15770</v>
+        <v>15771</v>
       </c>
       <c r="N133" s="3" t="n">
         <v>18821</v>
@@ -7950,7 +7934,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -7993,12 +7977,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28231</v>
+        <v>28232</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8039,20 +8023,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21173</v>
+        <v>21174</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21173</v>
+        <v>21174</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47052</v>
+        <v>47053</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8093,20 +8077,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28231</v>
+        <v>28232</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28231</v>
+        <v>28232</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>70578</v>
+        <v>70579</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8144,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8183,11 +8167,11 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G138" s="3" t="n">
         <v>6274</v>
@@ -8220,11 +8204,11 @@
         <v>12547</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8272,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8336,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8375,11 +8359,11 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G141" s="3" t="n">
         <v>1568</v>
@@ -8409,14 +8393,14 @@
         <v>1568</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>314</v>
+        <v>1725</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8454,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8508,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8572,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8620,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8664,7 @@
         <v>4392</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53040</v>
+        <v>53041</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>6274</v>
@@ -8690,7 +8674,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8722,7 @@
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8779,10 +8763,10 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17186</v>
+        <v>17187</v>
       </c>
       <c r="N148" s="3" t="n">
         <v>18821</v>
@@ -8792,7 +8776,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8835,12 +8819,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25094</v>
+        <v>25095</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8863,14 +8847,14 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
         <v>27</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15748</v>
+        <v>15714</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8894,17 +8878,17 @@
         <v>15684</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39210</v>
+        <v>39211</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8915,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>37642</v>
@@ -8958,17 +8942,17 @@
         <v>37642</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>62686</v>
+        <v>62687</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75283</v>
+        <v>75284</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9009,20 +8993,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>101946</v>
+        <v>101948</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>101946</v>
+        <v>101948</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>203892</v>
+        <v>203895</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9060,7 @@
         <v>157</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10260</v>
+        <v>10261</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>314</v>
@@ -9086,7 +9070,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9134,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9206,11 +9190,11 @@
         <v>1568</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9244,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9294,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9354,17 +9338,17 @@
         <v>784</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1568397</v>
+        <v>1568426</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1568</v>
       </c>
       <c r="O158" s="2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9402,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9456,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9529,14 +9513,14 @@
         <v>1568</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>1725</v>
+        <v>314</v>
       </c>
       <c r="O161" s="2" t="n">
         <v>420</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9555,18 +9539,18 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>1832</v>
+        <v>2131</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1747</v>
+        <v>1802</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -9587,20 +9571,20 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>2131</v>
+        <v>2218</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>29925</v>
+        <v>29926</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>1708</v>
+        <v>1866</v>
       </c>
       <c r="O162" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9635,7 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="M163" s="3" t="n">
         <v>3816</v>
@@ -9664,7 +9648,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9683,18 +9667,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3791</v>
+        <v>4073</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3668</v>
+        <v>3681</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9715,7 +9699,7 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3833</v>
+        <v>4268</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>10195</v>
@@ -9724,11 +9708,11 @@
         <v>6274</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9747,18 +9731,18 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -9788,11 +9772,11 @@
         <v>314</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9830,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9865,18 +9849,18 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>957</v>
+        <v>627</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>894</v>
+        <v>841</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -9900,7 +9884,7 @@
         <v>1553</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9639</v>
+        <v>9640</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1255</v>
@@ -9910,7 +9894,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9933,11 +9917,11 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G168" s="3" t="n">
         <v>1568</v>
@@ -9970,11 +9954,11 @@
         <v>1725</v>
       </c>
       <c r="O168" s="2" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10015,7 +9999,7 @@
         </is>
       </c>
       <c r="L169" s="3" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M169" s="3" t="n">
         <v>15684</v>
@@ -10024,11 +10008,11 @@
         <v>314</v>
       </c>
       <c r="O169" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10031,7 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>94104</v>
+        <v>94106</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -10058,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>94104</v>
+        <v>94106</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -10079,20 +10063,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94104</v>
+        <v>94106</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94104</v>
+        <v>94106</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>125472</v>
+        <v>125474</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10140,7 +10124,7 @@
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10174,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10224,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10268,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10318,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10371,10 +10355,10 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11292</v>
+        <v>11293</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11292</v>
+        <v>11293</v>
       </c>
       <c r="N176" s="3" t="n">
         <v>22585</v>
@@ -10384,7 +10368,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10424,17 +10408,17 @@
         <v>15684</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>15762</v>
+        <v>15763</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10468,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10516,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10570,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10618,7 @@
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10675,10 +10659,10 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="N182" s="3" t="n">
         <v>18821</v>
@@ -10688,7 +10672,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10731,12 +10715,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28231</v>
+        <v>28232</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10777,10 +10761,10 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21173</v>
+        <v>21174</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21173</v>
+        <v>21174</v>
       </c>
       <c r="N184" s="3" t="n">
         <v>42347</v>
@@ -10790,7 +10774,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10831,20 +10815,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28231</v>
+        <v>28232</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28231</v>
+        <v>28232</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56462</v>
+        <v>56463</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10872,7 @@
         <v>157</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>314</v>
@@ -10898,7 +10882,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10926,7 @@
         <v>157</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>314</v>
@@ -10952,7 +10936,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11006,7 +10990,7 @@
         <v>157</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102043</v>
+        <v>102045</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>314</v>
@@ -11016,7 +11000,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11048,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11102,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11146,7 @@
         <v>157</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>154853</v>
+        <v>154855</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>314</v>
@@ -11172,7 +11156,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11210,7 @@
         <v>157</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>314</v>
@@ -11236,7 +11220,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11268,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11338,7 +11322,7 @@
         <v>157</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>314</v>
@@ -11348,7 +11332,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11392,17 +11376,17 @@
         <v>157</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11456,17 +11440,17 @@
         <v>157</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11498,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11562,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11616,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11680,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11724,7 @@
         <v>5019</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10685</v>
+        <v>10686</v>
       </c>
       <c r="N201" s="3" t="n">
         <v>7528</v>
@@ -11750,7 +11734,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11788,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11832,7 @@
         <v>8156</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>273795</v>
+        <v>273800</v>
       </c>
       <c r="N203" s="3" t="n">
         <v>13802</v>
@@ -11858,7 +11842,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11883,7 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15497</v>
+        <v>15498</v>
       </c>
       <c r="M204" s="3" t="n">
         <v>15907</v>
@@ -11912,7 +11896,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11953,10 +11937,10 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20075</v>
+        <v>20076</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>48383</v>
+        <v>48384</v>
       </c>
       <c r="N205" s="3" t="n">
         <v>37642</v>
@@ -11966,7 +11950,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12014,7 +11998,7 @@
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12062,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12116,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12170,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12234,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12304,7 +12288,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12342,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12390,7 @@
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12453,14 +12437,14 @@
         <v>15684</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12498,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12568,7 +12552,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12612,17 +12596,17 @@
         <v>13802</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>29100</v>
+        <v>29101</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25094</v>
+        <v>25095</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12676,7 +12660,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12714,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12773,12 +12757,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12816,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12896,7 +12880,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12934,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13004,7 +12988,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13032,7 @@
         <v>1532</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>7644</v>
+        <v>7645</v>
       </c>
       <c r="N225" s="3" t="n">
         <v>1568</v>
@@ -13058,7 +13042,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13112,7 +13096,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13130,13 +13114,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D227" s="3" t="inlineStr"/>
-      <c r="E227" s="2" t="inlineStr"/>
-      <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" s="3" t="inlineStr"/>
+      <c r="D227" s="3" t="n">
+        <v>3137</v>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>3137</v>
+      </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I227" s="2" t="n">
@@ -13153,7 +13147,7 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3137</v>
+        <v>3157</v>
       </c>
       <c r="M227" s="3" t="n">
         <v>3750</v>
@@ -13162,11 +13156,11 @@
         <v>6274</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13204,7 @@
         <v>157</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>314</v>
@@ -13220,7 +13214,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13264,17 +13258,17 @@
         <v>157</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13293,7 +13287,7 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>44332</v>
+        <v>44333</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -13304,7 +13298,7 @@
         <v>1</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>44332</v>
+        <v>44333</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -13328,17 +13322,17 @@
         <v>157</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13382,17 +13376,17 @@
         <v>784</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1568</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13450,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13504,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13568,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13628,7 +13622,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13676,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13724,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13778,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13832,7 +13826,7 @@
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13874,7 @@
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13907,10 +13901,10 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>19154</v>
+        <v>19547</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -13934,17 +13928,17 @@
         <v>22323</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30386</v>
+        <v>30387</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -13963,7 +13957,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>37643</v>
+        <v>37644</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -13995,20 +13989,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>56160</v>
+        <v>56161</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75283</v>
+        <v>75284</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14035,10 +14029,10 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>18458</v>
+        <v>18708</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14055,20 +14049,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>18476</v>
+        <v>18733</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31367939</v>
+        <v>31368512</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14111,12 +14105,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25094</v>
+        <v>25095</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14164,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14197,10 +14191,10 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2732</v>
+        <v>2754</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14221,7 +14215,7 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2713</v>
+        <v>2834</v>
       </c>
       <c r="M246" s="3" t="n">
         <v>6274</v>
@@ -14234,7 +14228,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14278,7 +14272,7 @@
         <v>15402</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23124</v>
+        <v>23125</v>
       </c>
       <c r="N247" s="3" t="n">
         <v>17566</v>
@@ -14288,7 +14282,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14336,7 +14330,7 @@
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14380,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14430,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14474,7 @@
         <v>157</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>96442</v>
+        <v>96444</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>314</v>
@@ -14490,7 +14484,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14541,10 +14535,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>49975</v>
+        <v>49976</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>49975</v>
+        <v>49976</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6274</v>
@@ -14554,7 +14548,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14612,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14666,7 +14660,7 @@
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14720,7 +14714,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14768,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14822,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14851,14 +14845,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -14882,17 +14876,17 @@
         <v>314</v>
       </c>
       <c r="M258" s="3" t="n">
-        <v>15679</v>
+        <v>15680</v>
       </c>
       <c r="N258" s="3" t="n">
-        <v>864</v>
+        <v>828</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14946,7 +14940,7 @@
         <v>1208</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21209</v>
+        <v>21210</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1568</v>
@@ -14956,7 +14950,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14991,7 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2326</v>
+        <v>2409</v>
       </c>
       <c r="M260" s="3" t="n">
         <v>3642</v>
@@ -15006,11 +15000,11 @@
         <v>3137</v>
       </c>
       <c r="O260" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15064,7 +15058,7 @@
         <v>3137</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>6957</v>
+        <v>6958</v>
       </c>
       <c r="N261" s="3" t="n">
         <v>6274</v>
@@ -15074,7 +15068,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15093,18 +15087,18 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>7803</v>
+        <v>6274</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6492</v>
+        <v>6465</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15134,11 +15128,11 @@
         <v>12547</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15196,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15250,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15298,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15362,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15419,7 +15413,7 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>2713</v>
+        <v>2717</v>
       </c>
       <c r="M267" s="3" t="n">
         <v>19290</v>
@@ -15432,7 +15426,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15490,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15544,7 +15538,7 @@
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15587,12 +15581,12 @@
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="3" t="n">
-        <v>25094</v>
+        <v>25095</v>
       </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15611,7 +15605,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>28231</v>
+        <v>28232</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15622,7 +15616,7 @@
         <v>3</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>23682</v>
+        <v>23683</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15656,7 +15650,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15694,7 @@
         <v>157</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>314</v>
@@ -15710,7 +15704,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15768,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15818,7 +15812,7 @@
         <v>157</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31471</v>
+        <v>31472</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>314</v>
@@ -15828,7 +15822,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15882,7 +15876,7 @@
         <v>157</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15762</v>
+        <v>15763</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>314</v>
@@ -15892,7 +15886,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -15936,17 +15930,17 @@
         <v>157</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>156368</v>
+        <v>156370</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16000,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16024,23 +16018,13 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D278" s="3" t="n">
-        <v>4392</v>
-      </c>
-      <c r="E278" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F278" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G278" s="3" t="n">
-        <v>4392</v>
-      </c>
+      <c r="D278" s="3" t="inlineStr"/>
+      <c r="E278" s="2" t="inlineStr"/>
+      <c r="F278" s="2" t="inlineStr"/>
+      <c r="G278" s="3" t="inlineStr"/>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I278" s="2" t="n">
@@ -16070,7 +16054,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16114,7 +16098,7 @@
         <v>5019</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9813</v>
+        <v>9814</v>
       </c>
       <c r="N279" s="3" t="n">
         <v>7528</v>
@@ -16124,7 +16108,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16162,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16226,7 +16210,7 @@
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16258,7 @@
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16317,12 +16301,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25094</v>
+        <v>25095</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16363,10 +16347,10 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>20075</v>
+        <v>20076</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33441</v>
+        <v>33442</v>
       </c>
       <c r="N284" s="3" t="n">
         <v>37642</v>
@@ -16376,7 +16360,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16395,18 +16379,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>10322</v>
+        <v>11450</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>8847</v>
+        <v>9229</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16427,20 +16411,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>10693</v>
+        <v>12478</v>
       </c>
       <c r="M285" s="3" t="n">
         <v>15684</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>9492</v>
+        <v>10275</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16488,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16523,18 +16507,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5582</v>
+        <v>5838</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5258</v>
+        <v>5299</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16551,20 +16535,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5616</v>
+        <v>6159</v>
       </c>
       <c r="M287" s="3" t="n">
         <v>6159</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>6104</v>
+        <v>6231</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16611,20 +16595,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7621</v>
+        <v>7549</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>7695</v>
+        <v>7764</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7470</v>
+        <v>7469</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16643,18 +16627,18 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>8250</v>
+        <v>8736</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>10466</v>
+        <v>10461</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16671,20 +16655,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9705</v>
+        <v>8735</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11576</v>
+        <v>11577</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>11043</v>
+        <v>10229</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16732,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16799,7 +16783,7 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>3843</v>
+        <v>3494</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>4862</v>
@@ -16808,11 +16792,11 @@
         <v>3137</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16876,7 +16860,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16924,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16959,18 +16943,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>8024</v>
+        <v>6658</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
         <v>23</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7559</v>
+        <v>7451</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -16997,14 +16981,14 @@
         <v>14440</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>8375</v>
+        <v>8096</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17045,20 +17029,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>50978</v>
+        <v>50979</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>692825</v>
+        <v>692838</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39210</v>
+        <v>39211</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17061,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17088,7 +17072,7 @@
         <v>4</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17109,20 +17093,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68192</v>
+        <v>68194</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39210</v>
+        <v>39211</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17141,7 +17125,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>62736</v>
+        <v>62737</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17152,7 +17136,7 @@
         <v>6</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>62736</v>
+        <v>62737</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17173,20 +17157,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>62736</v>
+        <v>62737</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>125472</v>
+        <v>125474</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>78420</v>
+        <v>78421</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17205,18 +17189,18 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>125472</v>
+        <v>125474</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>125472</v>
+        <v>125474</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17237,20 +17221,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>125472</v>
+        <v>125474</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>125475</v>
+        <v>125477</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>156840</v>
+        <v>156843</v>
       </c>
       <c r="O298" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17269,18 +17253,18 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>250944</v>
+        <v>250948</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>250944</v>
+        <v>250948</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17301,20 +17285,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>250944</v>
+        <v>250948</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>250945</v>
+        <v>250950</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>313679</v>
+        <v>313685</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17333,7 +17317,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>439151</v>
+        <v>439159</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17344,7 +17328,7 @@
         <v>4</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>439151</v>
+        <v>439159</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17365,20 +17349,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>439151</v>
+        <v>439159</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>943778</v>
+        <v>943795</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>627359</v>
+        <v>627370</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17397,18 +17381,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>2111</v>
+        <v>2086</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
         <v>45</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17429,20 +17413,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>2037</v>
+        <v>2135</v>
       </c>
       <c r="M301" s="3" t="n">
         <v>18821</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>3461</v>
+        <v>3270</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17469,10 +17453,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17499,14 +17483,14 @@
         <v>14417</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2484</v>
+        <v>2531</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17529,14 +17513,14 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4421</v>
+        <v>4436</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17557,7 +17541,7 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4705</v>
+        <v>5144</v>
       </c>
       <c r="M303" s="3" t="n">
         <v>15684</v>
@@ -17566,11 +17550,11 @@
         <v>5176</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17621,20 +17605,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2715</v>
+        <v>2524</v>
       </c>
       <c r="M304" s="3" t="n">
         <v>18821</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>2371</v>
+        <v>2196</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17682,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17725,7 +17709,7 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G306" s="3" t="n">
         <v>157</v>
@@ -17758,11 +17742,11 @@
         <v>314</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>20531</v>
+        <v>20643</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17826,7 +17810,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17880,17 +17864,17 @@
         <v>2039</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1254718</v>
+        <v>1254740</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>3921</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17928,7 @@
         <v>4392</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>31713</v>
+        <v>31714</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6274</v>
@@ -17954,7 +17938,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -17977,14 +17961,14 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G310" s="3" t="n">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
@@ -18005,7 +17989,7 @@
         </is>
       </c>
       <c r="L310" s="3" t="n">
-        <v>1568</v>
+        <v>1871</v>
       </c>
       <c r="M310" s="3" t="n">
         <v>5976</v>
@@ -18014,11 +17998,11 @@
         <v>3137</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18072,7 +18056,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18120,7 +18104,7 @@
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18139,7 +18123,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18150,7 +18134,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18171,7 +18155,7 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="M313" s="3" t="n">
         <v>25932</v>
@@ -18184,7 +18168,7 @@
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18231,14 +18215,14 @@
         <v>15344</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25094</v>
+        <v>25095</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18292,17 +18276,17 @@
         <v>15684</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1568397</v>
+        <v>1568426</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18359,14 +18343,14 @@
         <v>37642</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75283</v>
+        <v>75284</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18385,7 +18369,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>101946</v>
+        <v>101948</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18396,7 +18380,7 @@
         <v>2</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>101946</v>
+        <v>101948</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18417,20 +18401,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>101946</v>
+        <v>101948</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>101946</v>
+        <v>101948</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>203892</v>
+        <v>203895</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18433,7 @@
         </is>
       </c>
       <c r="D318" s="3" t="n">
-        <v>939</v>
+        <v>1173</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
@@ -18460,7 +18444,7 @@
         <v>8</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>808</v>
+        <v>837</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18481,20 +18465,20 @@
         </is>
       </c>
       <c r="L318" s="3" t="n">
-        <v>1408</v>
+        <v>1241</v>
       </c>
       <c r="M318" s="3" t="n">
         <v>2034</v>
       </c>
       <c r="N318" s="3" t="n">
-        <v>913</v>
+        <v>1128</v>
       </c>
       <c r="O318" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18548,7 +18532,7 @@
         <v>1382</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15577</v>
+        <v>15578</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>1520</v>
@@ -18558,7 +18542,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18585,10 +18569,10 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>2034</v>
+        <v>1956</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18612,17 +18596,17 @@
         <v>1098</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9744</v>
+        <v>9745</v>
       </c>
       <c r="N320" s="3" t="n">
         <v>2196</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18670,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18750,7 +18734,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18777,10 +18761,10 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>2453</v>
+        <v>2510</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18807,14 +18791,14 @@
         <v>18821</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>4914</v>
+        <v>2196</v>
       </c>
       <c r="O323" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18878,7 +18862,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -18897,7 +18881,7 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>3320</v>
+        <v>3294</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -18908,7 +18892,7 @@
         <v>17</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2953</v>
+        <v>2978</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18929,20 +18913,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>3294</v>
+        <v>3309</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15577</v>
+        <v>15578</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>3433</v>
+        <v>3465</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19006,7 +18990,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19066,11 +19050,11 @@
         <v>2196</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19089,18 +19073,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>26399</v>
+        <v>26306</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
         <v>29</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>24465</v>
+        <v>24583</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19121,20 +19105,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>26305</v>
+        <v>26094</v>
       </c>
       <c r="M328" s="3" t="n">
         <v>30300</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>27100</v>
+        <v>27407</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19153,7 +19137,7 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7685</v>
+        <v>7655</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
@@ -19161,10 +19145,10 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7284</v>
+        <v>7275</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19185,20 +19169,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7597</v>
+        <v>8096</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9686</v>
+        <v>9687</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8333</v>
+        <v>8324</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19225,10 +19209,10 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5802</v>
+        <v>5791</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19249,20 +19233,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>7270</v>
+        <v>6794</v>
       </c>
       <c r="M330" s="3" t="n">
         <v>8582</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6771</v>
+        <v>6868</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19310,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19349,14 +19333,14 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
         <v>23</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1412</v>
+        <v>1439</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19377,20 +19361,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="M332" s="3" t="n">
         <v>15684</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1642</v>
+        <v>1670</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19438,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19492,7 @@
         <v>386</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9341</v>
+        <v>9342</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>423</v>
@@ -19518,7 +19502,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19545,10 +19529,10 @@
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1799</v>
+        <v>2033</v>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
@@ -19569,20 +19553,20 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1924</v>
+        <v>2280</v>
       </c>
       <c r="M335" s="3" t="n">
         <v>15684</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2710</v>
+        <v>4213</v>
       </c>
       <c r="O335" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19646,7 +19630,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19673,10 +19657,10 @@
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19710,7 +19694,7 @@
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19745,7 @@
         </is>
       </c>
       <c r="L338" s="3" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M338" s="3" t="n">
         <v>971</v>
@@ -19774,7 +19758,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19838,7 +19822,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19898,11 +19882,11 @@
         <v>1132</v>
       </c>
       <c r="O340" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19925,14 +19909,14 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
         <v>16</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>1186</v>
+        <v>1237</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19959,14 +19943,14 @@
         <v>2412</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>1666</v>
+        <v>1703</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20014,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20078,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20132,7 @@
         <v>2817</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57209</v>
+        <v>57210</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3137</v>
@@ -20158,7 +20142,7 @@
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20161,7 @@
         </is>
       </c>
       <c r="D345" s="3" t="n">
-        <v>2039</v>
+        <v>2191</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
@@ -20185,10 +20169,10 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>3095</v>
+        <v>3045</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20209,20 +20193,20 @@
         </is>
       </c>
       <c r="L345" s="3" t="n">
-        <v>2135</v>
+        <v>2039</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>75161</v>
+        <v>75162</v>
       </c>
       <c r="N345" s="3" t="n">
         <v>3921</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20270,7 +20254,7 @@
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20330,11 +20314,11 @@
         <v>6274</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20375,10 +20359,10 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="N348" s="3" t="n">
         <v>12547</v>
@@ -20388,7 +20372,7 @@
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20407,18 +20391,18 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20439,7 +20423,7 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9410</v>
+        <v>9411</v>
       </c>
       <c r="M349" s="3" t="n">
         <v>19447</v>
@@ -20448,11 +20432,11 @@
         <v>18821</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20495,12 +20479,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25094</v>
+        <v>25095</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20519,18 +20503,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>19243</v>
+        <v>18638</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17526</v>
+        <v>17623</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20551,20 +20535,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>18451</v>
+        <v>18347</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31368</v>
+        <v>31369</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20583,7 +20567,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>47516</v>
+        <v>47517</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20591,10 +20575,10 @@
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>44751</v>
+        <v>44884</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20614,15 +20598,21 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L352" s="3" t="inlineStr"/>
-      <c r="M352" s="3" t="inlineStr"/>
+      <c r="L352" s="3" t="n">
+        <v>48536</v>
+      </c>
+      <c r="M352" s="3" t="n">
+        <v>48536</v>
+      </c>
       <c r="N352" s="3" t="n">
-        <v>75283</v>
-      </c>
-      <c r="O352" s="2" t="inlineStr"/>
+        <v>75284</v>
+      </c>
+      <c r="O352" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20641,7 +20631,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>115765</v>
+        <v>115767</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20652,7 +20642,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>115765</v>
+        <v>115767</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20675,12 +20665,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>203892</v>
+        <v>203895</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20699,18 +20689,18 @@
         </is>
       </c>
       <c r="D354" s="3" t="n">
-        <v>928</v>
+        <v>772</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F354" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G354" s="3" t="n">
-        <v>709</v>
+        <v>750</v>
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
@@ -20731,20 +20721,20 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="M354" s="3" t="n">
         <v>1407</v>
       </c>
       <c r="N354" s="3" t="n">
-        <v>1021</v>
+        <v>869</v>
       </c>
       <c r="O354" s="2" t="n">
-        <v>654</v>
+        <v>578</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20804,11 +20794,11 @@
         <v>17566</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20862,17 +20852,17 @@
         <v>8783</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>54894</v>
+        <v>54895</v>
       </c>
       <c r="N356" s="3" t="n">
         <v>17566</v>
       </c>
       <c r="O356" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20929,14 +20919,14 @@
         <v>15684</v>
       </c>
       <c r="N357" s="3" t="n">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="O357" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -20955,18 +20945,18 @@
         </is>
       </c>
       <c r="D358" s="3" t="n">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F358" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G358" s="3" t="n">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
@@ -20987,20 +20977,20 @@
         </is>
       </c>
       <c r="L358" s="3" t="n">
-        <v>356</v>
+        <v>405</v>
       </c>
       <c r="M358" s="3" t="n">
         <v>762</v>
       </c>
       <c r="N358" s="3" t="n">
-        <v>314</v>
+        <v>391</v>
       </c>
       <c r="O358" s="2" t="n">
-        <v>512</v>
+        <v>313</v>
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21038,7 @@
       <c r="O359" s="2" t="inlineStr"/>
       <c r="P359" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -21078,7 +21068,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>156.839696</v>
+        <v>156.842558</v>
       </c>
     </row>
     <row r="2">
@@ -21089,7 +21079,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 24 Oct 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 25 Oct 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21101,7 +21091,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -11,7 +11,7 @@
     <sheet name="注記" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品一覧'!$A$1:$P$359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品一覧'!$A$1:$P$360</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P359"/>
+  <dimension ref="A1:P360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -578,14 +578,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3331</v>
+        <v>3258</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -609,17 +609,17 @@
         <v>3137</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1568426</v>
+        <v>1568720</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -638,18 +638,18 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>95879</v>
+        <v>95897</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25095</v>
+        <v>25100</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23526</v>
+        <v>23531</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23526</v>
+        <v>23531</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -800,12 +800,12 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>47053</v>
+        <v>47062</v>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -856,20 +856,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>84695</v>
+        <v>84711</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>125474</v>
+        <v>125498</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>141158</v>
+        <v>141185</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>250948</v>
+        <v>250995</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -964,20 +964,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>352896</v>
+        <v>352962</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>352896</v>
+        <v>352962</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>705792</v>
+        <v>705924</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -996,18 +996,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6116</v>
+        <v>6056</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1028,20 +1028,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6015</v>
+        <v>5811</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1568426</v>
+        <v>1568720</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8626</v>
+        <v>8628</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1060,18 +1060,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>9608</v>
+        <v>8208</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8507</v>
+        <v>8502</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1092,20 +1092,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>9026</v>
+        <v>9318</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>148960</v>
+        <v>148988</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17253</v>
+        <v>17256</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1124,18 +1124,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13802</v>
+        <v>13805</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14031</v>
+        <v>14023</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1156,20 +1156,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13802</v>
+        <v>13805</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42111</v>
+        <v>42119</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34505</v>
+        <v>34512</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>8783</v>
+        <v>8785</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39211</v>
+        <v>39218</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>21958</v>
+        <v>21962</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1264,20 +1264,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>93194</v>
+        <v>93212</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>93194</v>
+        <v>93212</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>21958</v>
+        <v>21962</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1318,20 +1318,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>188211</v>
+        <v>188246</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1568426</v>
+        <v>1568720</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1372,20 +1372,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>33999</v>
+        <v>34005</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>63538</v>
+        <v>63550</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5333</v>
+        <v>5334</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1426,20 +1426,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22352</v>
+        <v>22356</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>63538</v>
+        <v>63550</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5333</v>
+        <v>5334</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         <v>784</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1568426</v>
+        <v>1568720</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O17" s="2" t="n">
         <v>552</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>225867</v>
+        <v>225910</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3137</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1591,17 +1591,17 @@
         <v>3137</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>266632</v>
+        <v>266682</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1642,20 +1642,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>21958</v>
+        <v>21962</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11293</v>
+        <v>11295</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1696,20 +1696,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>10979</v>
+        <v>10981</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36654</v>
+        <v>36661</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>21958</v>
+        <v>21962</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1750,20 +1750,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21174</v>
+        <v>21178</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>138445</v>
+        <v>138471</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1804,20 +1804,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39211</v>
+        <v>39218</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>318917</v>
+        <v>318977</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>78421</v>
+        <v>78436</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>1934</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>1440</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>314</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1990,17 +1990,17 @@
         <v>1255</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>1147</v>
@@ -2051,20 +2051,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1263</v>
+        <v>1054</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1564260</v>
+        <v>1564554</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2083,18 +2083,18 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>26</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1568426</v>
+        <v>1568720</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3137</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2151,14 +2151,14 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3145</v>
+        <v>3147</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2182,17 +2182,17 @@
         <v>3137</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>16898</v>
+        <v>16901</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
         <v>627</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1568426</v>
+        <v>1568720</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1255</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2310,17 +2310,17 @@
         <v>2353</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11442</v>
+        <v>11444</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1200</v>
+        <v>963</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2371,20 +2371,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>853</v>
+        <v>784</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>627370</v>
+        <v>627488</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>6</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>2480</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12706</v>
+        <v>12708</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3137</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2467,18 +2467,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3653</v>
+        <v>3435</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>54</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3434</v>
+        <v>3424</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2499,20 +2499,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3736</v>
+        <v>3479</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>20965</v>
+        <v>20969</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2531,18 +2531,18 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6632</v>
+        <v>6633</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2563,20 +2563,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30316</v>
+        <v>30322</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2626,17 +2626,17 @@
         <v>784</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6228</v>
+        <v>6229</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O36" s="2" t="n">
         <v>54</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="3" t="n">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4122</v>
+        <v>4123</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>3137</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2719,11 +2719,11 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>3137</v>
@@ -2746,17 +2746,17 @@
         <v>3137</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>313685</v>
+        <v>313744</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>2</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>143585</v>
+        <v>143612</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3137</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2871,20 +2871,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4426</v>
+        <v>4425</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17254</v>
+        <v>17257</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2903,18 +2903,18 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2935,20 +2935,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15005</v>
+        <v>15008</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O41" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2998,17 +2998,17 @@
         <v>3556</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6075</v>
+        <v>6076</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>2196</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6431</v>
+        <v>6432</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6816</v>
+        <v>6817</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3055,20 +3055,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6545</v>
+        <v>5825</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8815</v>
+        <v>8816</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>7074</v>
+        <v>7075</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3087,18 +3087,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9591</v>
+        <v>8231</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>44</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9649</v>
+        <v>9601</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3115,20 +3115,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9592</v>
+        <v>9591</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>13658</v>
+        <v>13660</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10625</v>
+        <v>10376</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>2</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8647</v>
+        <v>8648</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3137</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3246,17 +3246,17 @@
         <v>3137</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
         <v>767</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>5825</v>
+        <v>5826</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>784</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3364,17 +3364,17 @@
         <v>1266</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O48" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
         <v>3137</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>3137</v>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>2312</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>4112</v>
+        <v>4113</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>784</v>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3535,20 +3535,20 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>4327</v>
+        <v>4328</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4327</v>
+        <v>4328</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3585,10 +3585,10 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6744</v>
+        <v>6745</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>3137</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
         <v>784</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>863</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3716,17 +3716,17 @@
         <v>1882</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11200</v>
+        <v>11202</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O54" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30338</v>
+        <v>30344</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3137</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>3</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>6722</v>
+        <v>6723</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3831,20 +3831,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>8159</v>
+        <v>7767</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>8159</v>
+        <v>8160</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>6570</v>
+        <v>6571</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3863,18 +3863,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9411</v>
+        <v>9335</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>46</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9434</v>
+        <v>9441</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3895,20 +3895,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9299</v>
+        <v>8992</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30377</v>
+        <v>30383</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3927,18 +3927,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3863</v>
+        <v>2905</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3640</v>
+        <v>3626</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3959,20 +3959,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3882</v>
+        <v>3680</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10239</v>
+        <v>10241</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4106</v>
+        <v>4013</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -4023,20 +4023,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11214</v>
+        <v>11216</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4080,17 +4080,17 @@
         <v>1098</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4131,20 +4131,20 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9724</v>
+        <v>9726</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4233,20 +4233,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4383,20 +4383,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50190</v>
+        <v>50199</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4437,20 +4437,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>8783</v>
+        <v>8785</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>21958</v>
+        <v>21962</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>21958</v>
+        <v>21962</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4542,17 +4542,17 @@
         <v>317</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O69" s="2" t="n">
         <v>82</v>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
         <v>627</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>4995</v>
+        <v>4996</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>3137</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4647,20 +4647,20 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4161</v>
+        <v>4162</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>4988</v>
+        <v>4989</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4701,20 +4701,20 @@
         </is>
       </c>
       <c r="L72" s="3" t="n">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1471249</v>
+        <v>1471525</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11293</v>
+        <v>11295</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4755,20 +4755,20 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4713</v>
+        <v>4714</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7414</v>
+        <v>7415</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4809,20 +4809,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8626</v>
+        <v>8628</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20780</v>
+        <v>20784</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17253</v>
+        <v>17256</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4863,20 +4863,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17253</v>
+        <v>17256</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>26823</v>
+        <v>26828</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>298</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6321</v>
+        <v>6322</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>314</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
         <v>627</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5143</v>
+        <v>5144</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>627</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5083,20 +5083,20 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5139,12 +5139,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5185,20 +5185,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>22940</v>
+        <v>22944</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>22940</v>
+        <v>22944</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10038</v>
+        <v>10040</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5241,12 +5241,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20076</v>
+        <v>20080</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5296,17 +5296,17 @@
         <v>238</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1568269</v>
+        <v>1568563</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>784</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5356,17 +5356,17 @@
         <v>348</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34286</v>
+        <v>34292</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1986</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>3137</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5473,20 +5473,20 @@
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="n">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10038</v>
+        <v>10040</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5569,12 +5569,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14116</v>
+        <v>14118</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17253</v>
+        <v>17256</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
         <v>3</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -5665,20 +5665,20 @@
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="3" t="n">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>85241</v>
+        <v>85257</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>784</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5718,17 +5718,17 @@
         <v>784</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O91" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5765,10 +5765,10 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>3137</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5821,14 +5821,14 @@
         <v>2709</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O93" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10038</v>
+        <v>10040</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5911,12 +5911,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14116</v>
+        <v>14118</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5955,12 +5955,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17253</v>
+        <v>17256</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6004,17 +6004,17 @@
         <v>1586</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="O97" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6071,14 +6071,14 @@
         <v>3440</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6129,20 +6129,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>5133</v>
+        <v>5134</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5133</v>
+        <v>5134</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9724</v>
+        <v>9726</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6183,20 +6183,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6285,20 +6285,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>17819</v>
+        <v>17822</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>17819</v>
+        <v>17822</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50190</v>
+        <v>50199</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6364,13 +6364,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr"/>
-      <c r="E104" s="2" t="inlineStr"/>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="3" t="inlineStr"/>
+      <c r="D104" s="3" t="n">
+        <v>1098</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>1098</v>
+      </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
@@ -6390,17 +6400,17 @@
         <v>1098</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="O104" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6443,12 +6453,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6491,12 +6501,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9724</v>
+        <v>9726</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6549,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6597,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6635,12 +6645,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6683,12 +6693,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50190</v>
+        <v>50199</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6741,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>78421</v>
+        <v>78436</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6754,23 +6764,13 @@
           <t>乗り物 / 輸送機</t>
         </is>
       </c>
-      <c r="D112" s="3" t="n">
-        <v>86263</v>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>86263</v>
-      </c>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="3" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
@@ -6787,20 +6787,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>86263</v>
+        <v>86280</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>96292</v>
+        <v>96310</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>109790</v>
+        <v>109810</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>109790</v>
+        <v>109810</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>2</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>109790</v>
+        <v>109810</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6851,20 +6851,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>109790</v>
+        <v>109810</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>109790</v>
+        <v>109810</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>141158</v>
+        <v>141185</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6905,20 +6905,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>125474</v>
+        <v>125498</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>125474</v>
+        <v>125498</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>188211</v>
+        <v>188246</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -6991,18 +6991,18 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>211737</v>
+        <v>211777</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>211737</v>
+        <v>211777</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -7023,20 +7023,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>211737</v>
+        <v>211777</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>250948</v>
+        <v>250995</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>250948</v>
+        <v>250995</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7131,20 +7131,20 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3761</v>
+        <v>3762</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7233,20 +7233,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14116</v>
+        <v>14118</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14116</v>
+        <v>14118</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22585</v>
+        <v>22590</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7335,20 +7335,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7389,20 +7389,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>40719</v>
+        <v>40727</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7510,17 +7510,17 @@
         <v>2218</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5632</v>
+        <v>5633</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7561,20 +7561,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>5692</v>
+        <v>5693</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6405</v>
+        <v>6407</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7615,20 +7615,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11784</v>
+        <v>11786</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14116</v>
+        <v>14118</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22585</v>
+        <v>22590</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7813,20 +7813,20 @@
         </is>
       </c>
       <c r="L131" s="3" t="n">
-        <v>4881</v>
+        <v>4882</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>4881</v>
+        <v>4882</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O131" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7867,20 +7867,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7921,20 +7921,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15771</v>
+        <v>15773</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -7977,12 +7977,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28232</v>
+        <v>28237</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8023,20 +8023,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21174</v>
+        <v>21178</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21174</v>
+        <v>21178</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47053</v>
+        <v>47062</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8077,20 +8077,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28232</v>
+        <v>28237</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28232</v>
+        <v>28237</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>70579</v>
+        <v>70592</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8131,20 +8131,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>6</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8195,20 +8195,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12637</v>
+        <v>12639</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
         <v>4</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>753</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5121</v>
+        <v>5122</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>314</v>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>3</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -8387,20 +8387,20 @@
         </is>
       </c>
       <c r="L141" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M141" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="O141" s="2" t="n">
         <v>235</v>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="L142" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>13372</v>
+        <v>13375</v>
       </c>
       <c r="N142" s="3" t="n">
         <v>314</v>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
         <v>2055</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>3137</v>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8559,20 +8559,20 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10646</v>
+        <v>10648</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="O144" s="2" t="n">
         <v>48</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8615,12 +8615,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8664,17 +8664,17 @@
         <v>4392</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53041</v>
+        <v>53051</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O146" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8763,20 +8763,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17187</v>
+        <v>17190</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25095</v>
+        <v>25100</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8843,18 +8843,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15714</v>
+        <v>15711</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8875,20 +8875,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39211</v>
+        <v>39218</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>15</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8939,20 +8939,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>62687</v>
+        <v>62699</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75284</v>
+        <v>75299</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -8993,20 +8993,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>101948</v>
+        <v>101967</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>101948</v>
+        <v>101967</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>203895</v>
+        <v>203934</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
         <v>157</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10261</v>
+        <v>10263</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>314</v>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>1</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="L154" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M154" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="N154" s="3" t="n">
         <v>314</v>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9184,17 +9184,17 @@
         <v>784</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15367</v>
+        <v>1568720</v>
       </c>
       <c r="N155" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
         <v>1603</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="N156" s="3" t="n">
         <v>3137</v>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9284,17 +9284,17 @@
         <v>3137</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9338,17 +9338,17 @@
         <v>784</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1568426</v>
+        <v>1568720</v>
       </c>
       <c r="N158" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O158" s="2" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c r="L159" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19020</v>
+        <v>19024</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3137</v>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9446,17 +9446,17 @@
         <v>3137</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6561</v>
+        <v>6562</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>2</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -9507,20 +9507,20 @@
         </is>
       </c>
       <c r="L161" s="3" t="n">
-        <v>941</v>
+        <v>1569</v>
       </c>
       <c r="M161" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="N161" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>420</v>
+        <v>145</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
@@ -9574,17 +9574,17 @@
         <v>2218</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>29926</v>
+        <v>29931</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>1866</v>
+        <v>2105</v>
       </c>
       <c r="O162" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
         <v>3451</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3816</v>
+        <v>3817</v>
       </c>
       <c r="N163" s="3" t="n">
         <v>3137</v>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9667,18 +9667,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>4073</v>
+        <v>3137</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3681</v>
+        <v>3645</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9699,20 +9699,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>4268</v>
+        <v>3770</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>10195</v>
+        <v>10197</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9731,18 +9731,18 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>184</v>
+        <v>282</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -9763,20 +9763,20 @@
         </is>
       </c>
       <c r="L165" s="3" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>4870</v>
+        <v>4871</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9881,20 +9881,20 @@
         </is>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1553</v>
+        <v>1402</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9640</v>
+        <v>9641</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1255</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>2</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -9945,20 +9945,20 @@
         </is>
       </c>
       <c r="L168" s="3" t="n">
-        <v>941</v>
+        <v>1569</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5348</v>
+        <v>5349</v>
       </c>
       <c r="N168" s="3" t="n">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="O168" s="2" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9999,20 +9999,20 @@
         </is>
       </c>
       <c r="L169" s="3" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O169" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>94106</v>
+        <v>94123</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>94106</v>
+        <v>94123</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -10063,20 +10063,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94106</v>
+        <v>94123</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94106</v>
+        <v>94123</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>125474</v>
+        <v>125498</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10119,12 +10119,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10211,20 +10211,20 @@
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="3" t="n">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="M173" s="3" t="n">
         <v>3341</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10263,12 +10263,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10305,20 +10305,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14086</v>
+        <v>14089</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14116</v>
+        <v>14118</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10355,20 +10355,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11293</v>
+        <v>11295</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11293</v>
+        <v>11295</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22585</v>
+        <v>22590</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10405,20 +10405,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>15763</v>
+        <v>15766</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>18978</v>
+        <v>18982</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10557,20 +10557,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10613,12 +10613,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10659,20 +10659,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10715,12 +10715,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28232</v>
+        <v>28237</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10761,20 +10761,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21174</v>
+        <v>21178</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21174</v>
+        <v>21178</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42347</v>
+        <v>42355</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10815,20 +10815,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28232</v>
+        <v>28237</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28232</v>
+        <v>28237</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56463</v>
+        <v>56474</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
         <v>157</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>314</v>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
         <v>157</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>314</v>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
         <v>157</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102045</v>
+        <v>102064</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>314</v>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
         <v>157</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>28928</v>
+        <v>28933</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>314</v>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
         <v>157</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>154855</v>
+        <v>154884</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>314</v>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11210,7 @@
         <v>157</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>314</v>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
         <v>157</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>314</v>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
         <v>157</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>314</v>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>21122</v>
+        <v>21126</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>21122</v>
+        <v>21126</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>157</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>314</v>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11517,7 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="L198" s="3" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>957</v>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11603,20 +11603,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20424</v>
+        <v>20428</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20424</v>
+        <v>20428</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11667,20 +11667,20 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>6118</v>
+        <v>6120</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6253</v>
+        <v>6254</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11721,20 +11721,20 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10686</v>
+        <v>10688</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7528</v>
+        <v>7530</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11775,20 +11775,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10264</v>
+        <v>10266</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10038</v>
+        <v>10040</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11829,20 +11829,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8156</v>
+        <v>8157</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>273800</v>
+        <v>273851</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>13802</v>
+        <v>13805</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11883,20 +11883,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15498</v>
+        <v>15501</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>15907</v>
+        <v>15910</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11937,20 +11937,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20076</v>
+        <v>20080</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>48384</v>
+        <v>48393</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22585</v>
+        <v>22590</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
         <v>624</v>
       </c>
       <c r="M207" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="N207" s="3" t="n">
         <v>314</v>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12106,7 @@
         <v>521</v>
       </c>
       <c r="M208" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="N208" s="3" t="n">
         <v>314</v>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="L209" s="3" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="M209" s="3" t="n">
         <v>2977</v>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12224,17 +12224,17 @@
         <v>2039</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4434</v>
+        <v>4435</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12275,20 +12275,20 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12329,20 +12329,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14116</v>
+        <v>14118</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12385,12 +12385,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22585</v>
+        <v>22590</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12431,20 +12431,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12542,17 +12542,17 @@
         <v>2039</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11777</v>
+        <v>11780</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="O216" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12593,20 +12593,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>13802</v>
+        <v>13805</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>29101</v>
+        <v>29106</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25095</v>
+        <v>25100</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12647,20 +12647,20 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>4823</v>
+        <v>4824</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>4835</v>
+        <v>4836</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12701,20 +12701,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7058</v>
+        <v>7059</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14116</v>
+        <v>14118</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12757,12 +12757,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12803,20 +12803,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>18829</v>
+        <v>18832</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12873,14 +12873,14 @@
         <v>2817</v>
       </c>
       <c r="N222" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O222" s="2" t="n">
         <v>26</v>
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12921,7 +12921,7 @@
         </is>
       </c>
       <c r="L223" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M223" s="3" t="n">
         <v>4014</v>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -12978,17 +12978,17 @@
         <v>3137</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13029,20 +13029,20 @@
         </is>
       </c>
       <c r="L225" s="3" t="n">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>7645</v>
+        <v>7646</v>
       </c>
       <c r="N225" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O225" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>2905</v>
+        <v>2717</v>
       </c>
       <c r="M226" s="3" t="n">
         <v>3446</v>
@@ -13096,7 +13096,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13147,20 +13147,20 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>3750</v>
+        <v>3751</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13204,7 +13204,7 @@
         <v>157</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>314</v>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13258,7 @@
         <v>157</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>314</v>
@@ -13268,7 +13268,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13287,7 +13287,7 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>44333</v>
+        <v>44341</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>1</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>44333</v>
+        <v>44341</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>157</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>314</v>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13376,17 +13376,17 @@
         <v>784</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N231" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>1</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -13437,20 +13437,20 @@
         </is>
       </c>
       <c r="L232" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M232" s="3" t="n">
-        <v>3866</v>
+        <v>3867</v>
       </c>
       <c r="N232" s="3" t="n">
         <v>3137</v>
       </c>
       <c r="O232" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13494,17 +13494,17 @@
         <v>3137</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7146</v>
+        <v>7147</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>34</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13609,10 +13609,10 @@
         </is>
       </c>
       <c r="L235" s="3" t="n">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>3904</v>
+        <v>3905</v>
       </c>
       <c r="N235" s="3" t="n">
         <v>3137</v>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13663,20 +13663,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6468</v>
+        <v>6469</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13719,12 +13719,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13765,20 +13765,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8761</v>
+        <v>8763</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>10933</v>
+        <v>10936</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13821,12 +13821,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13869,12 +13869,12 @@
       <c r="L240" s="3" t="inlineStr"/>
       <c r="M240" s="3" t="inlineStr"/>
       <c r="N240" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13893,18 +13893,18 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>21156</v>
+        <v>22328</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>19547</v>
+        <v>20137</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -13925,20 +13925,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>22323</v>
+        <v>22240</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30387</v>
+        <v>30392</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O241" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -13957,7 +13957,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>37644</v>
+        <v>37651</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -13965,10 +13965,10 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38976</v>
+        <v>39651</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -13989,20 +13989,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>56161</v>
+        <v>56171</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58113</v>
+        <v>58124</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75284</v>
+        <v>75299</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>18261</v>
+        <v>18265</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>18708</v>
+        <v>18714</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14049,20 +14049,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>18733</v>
+        <v>18737</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31368512</v>
+        <v>31374403</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14105,12 +14105,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25095</v>
+        <v>25100</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14194,7 +14194,7 @@
         <v>13</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2754</v>
+        <v>2755</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14215,10 +14215,10 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2834</v>
+        <v>2910</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6274</v>
+        <v>15687</v>
       </c>
       <c r="N246" s="3" t="n">
         <v>2963</v>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14269,20 +14269,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15402</v>
+        <v>15405</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23125</v>
+        <v>23129</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17566</v>
+        <v>17570</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14325,12 +14325,12 @@
       <c r="L248" s="3" t="inlineStr"/>
       <c r="M248" s="3" t="inlineStr"/>
       <c r="N248" s="3" t="n">
-        <v>17566</v>
+        <v>17570</v>
       </c>
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14370,17 +14370,17 @@
         <v>784</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9208</v>
+        <v>9210</v>
       </c>
       <c r="N249" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O249" s="2" t="n">
         <v>76</v>
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14417,20 +14417,20 @@
       </c>
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="3" t="n">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="M250" s="3" t="n">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="N250" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O250" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
         <v>157</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>96444</v>
+        <v>96462</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>314</v>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14535,20 +14535,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>49976</v>
+        <v>49986</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>49976</v>
+        <v>49986</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14567,18 +14567,18 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F253" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -14599,20 +14599,20 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>5019</v>
+        <v>5393</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>8440</v>
+        <v>8441</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>7528</v>
+        <v>7530</v>
       </c>
       <c r="O253" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14655,12 +14655,12 @@
       <c r="L254" s="3" t="inlineStr"/>
       <c r="M254" s="3" t="inlineStr"/>
       <c r="N254" s="3" t="n">
-        <v>10038</v>
+        <v>10040</v>
       </c>
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14812,7 +14812,7 @@
         <v>289</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>314</v>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
@@ -14876,7 +14876,7 @@
         <v>314</v>
       </c>
       <c r="M258" s="3" t="n">
-        <v>15680</v>
+        <v>15682</v>
       </c>
       <c r="N258" s="3" t="n">
         <v>828</v>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14905,18 +14905,18 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>784</v>
+        <v>1208</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>784</v>
+        <v>996</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -14937,20 +14937,20 @@
         </is>
       </c>
       <c r="L259" s="3" t="n">
-        <v>1208</v>
+        <v>966</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21210</v>
+        <v>21214</v>
       </c>
       <c r="N259" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O259" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -14991,10 +14991,10 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3642</v>
+        <v>3643</v>
       </c>
       <c r="N260" s="3" t="n">
         <v>3137</v>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15058,17 +15058,17 @@
         <v>3137</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>6958</v>
+        <v>6959</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>8</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6465</v>
+        <v>6466</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15119,20 +15119,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15186,17 +15186,17 @@
         <v>784</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10474</v>
+        <v>10476</v>
       </c>
       <c r="N263" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O263" s="2" t="n">
         <v>62</v>
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15237,7 @@
         </is>
       </c>
       <c r="L264" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M264" s="3" t="n">
         <v>1600</v>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>2</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15349,20 +15349,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6735</v>
+        <v>6736</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9558</v>
+        <v>9560</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15392,7 @@
         <v>4</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15416,17 +15416,17 @@
         <v>2717</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19290</v>
+        <v>19294</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="O267" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8156</v>
+        <v>8157</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>1</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8156</v>
+        <v>8157</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15477,20 +15477,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>12519</v>
+        <v>12522</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14128</v>
+        <v>14131</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>13802</v>
+        <v>13805</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15533,12 +15533,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15581,12 +15581,12 @@
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="3" t="n">
-        <v>25095</v>
+        <v>25100</v>
       </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>28232</v>
+        <v>28237</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>3</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>23683</v>
+        <v>23687</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15637,20 +15637,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24279</v>
+        <v>24284</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>24279</v>
+        <v>24284</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15694,7 +15694,7 @@
         <v>157</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>314</v>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="D273" s="3" t="n">
-        <v>14897</v>
+        <v>14900</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>1</v>
       </c>
       <c r="G273" s="3" t="n">
-        <v>14897</v>
+        <v>14900</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -15758,17 +15758,17 @@
         <v>157</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>20772</v>
+        <v>20776</v>
       </c>
       <c r="N273" s="3" t="n">
-        <v>16385</v>
+        <v>16388</v>
       </c>
       <c r="O273" s="2" t="n">
         <v>204</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
         <v>157</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31472</v>
+        <v>31478</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>314</v>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
         <v>157</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15763</v>
+        <v>15766</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>314</v>
@@ -15886,7 +15886,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15930,7 @@
         <v>157</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>156370</v>
+        <v>156400</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>314</v>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -15993,14 +15993,14 @@
         <v>2094</v>
       </c>
       <c r="N277" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="O277" s="2" t="n">
         <v>103</v>
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16044,17 +16044,17 @@
         <v>4392</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>6942</v>
+        <v>6943</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>26</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16095,20 +16095,20 @@
         </is>
       </c>
       <c r="L279" s="3" t="n">
-        <v>5019</v>
+        <v>5020</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9814</v>
+        <v>9815</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7528</v>
+        <v>7530</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16149,20 +16149,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8535</v>
+        <v>8537</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10038</v>
+        <v>10040</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16205,12 +16205,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>13802</v>
+        <v>13805</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16253,12 +16253,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16301,12 +16301,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25095</v>
+        <v>25100</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16347,20 +16347,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>20076</v>
+        <v>20080</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33442</v>
+        <v>33448</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16379,18 +16379,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>11450</v>
+        <v>10194</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9229</v>
+        <v>9313</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16411,20 +16411,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>12478</v>
+        <v>12187</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10275</v>
+        <v>10380</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16478,7 @@
         <v>157</v>
       </c>
       <c r="M286" s="3" t="n">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="N286" s="3" t="n">
         <v>314</v>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5838</v>
+        <v>5839</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
@@ -16515,10 +16515,10 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5299</v>
+        <v>5298</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16535,20 +16535,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>6159</v>
+        <v>5630</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>6159</v>
+        <v>6160</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>6231</v>
+        <v>6233</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16567,18 +16567,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>7265</v>
+        <v>7539</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6540</v>
+        <v>6571</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16595,20 +16595,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7549</v>
+        <v>7544</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>7764</v>
+        <v>7765</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7469</v>
+        <v>7535</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16627,18 +16627,18 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>8736</v>
+        <v>9132</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>10461</v>
+        <v>10011</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16655,20 +16655,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>8735</v>
+        <v>9133</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11577</v>
+        <v>11579</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>10229</v>
+        <v>9917</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="D290" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
@@ -16719,20 +16719,20 @@
         </is>
       </c>
       <c r="L290" s="3" t="n">
-        <v>3137</v>
+        <v>1649</v>
       </c>
       <c r="M290" s="3" t="n">
         <v>3137</v>
       </c>
       <c r="N290" s="3" t="n">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="O290" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16783,10 +16783,10 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="M291" s="3" t="n">
-        <v>4862</v>
+        <v>4863</v>
       </c>
       <c r="N291" s="3" t="n">
         <v>3137</v>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>3855</v>
+        <v>3856</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>3</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4410</v>
+        <v>4411</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16847,20 +16847,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>5333</v>
+        <v>5334</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O292" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16878,23 +16878,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D293" s="3" t="n">
-        <v>251</v>
-      </c>
-      <c r="E293" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="F293" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G293" s="3" t="n">
-        <v>251</v>
-      </c>
+      <c r="D293" s="3" t="inlineStr"/>
+      <c r="E293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="3" t="inlineStr"/>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I293" s="2" t="n">
@@ -16924,7 +16914,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -16943,18 +16933,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>6658</v>
+        <v>8899</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7451</v>
+        <v>7357</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -16975,20 +16965,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>6310</v>
+        <v>6311</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>14440</v>
+        <v>12671</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>8096</v>
+        <v>8421</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17029,20 +17019,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>50979</v>
+        <v>50412</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>692838</v>
+        <v>692968</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39211</v>
+        <v>39218</v>
       </c>
       <c r="O295" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17051,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17069,10 +17059,10 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17093,20 +17083,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68194</v>
+        <v>68206</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39211</v>
+        <v>39218</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17125,7 +17115,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>62737</v>
+        <v>62749</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17133,10 +17123,10 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>62737</v>
+        <v>62749</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17157,20 +17147,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>62737</v>
+        <v>62749</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>125474</v>
+        <v>125498</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>78421</v>
+        <v>78436</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17189,7 +17179,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>125474</v>
+        <v>125498</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17200,7 +17190,7 @@
         <v>4</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>125474</v>
+        <v>125498</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17221,20 +17211,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>125474</v>
+        <v>125498</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>125477</v>
+        <v>125501</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>156843</v>
+        <v>156872</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17243,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>250948</v>
+        <v>250995</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17264,7 +17254,7 @@
         <v>3</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>250948</v>
+        <v>250995</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17285,20 +17275,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>250948</v>
+        <v>250995</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>250950</v>
+        <v>250997</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>313685</v>
+        <v>313744</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17317,7 +17307,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>439159</v>
+        <v>439242</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17328,7 +17318,7 @@
         <v>4</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>439159</v>
+        <v>439242</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17349,20 +17339,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>439159</v>
+        <v>439242</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>943795</v>
+        <v>841178</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>627370</v>
+        <v>627488</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17381,18 +17371,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>2086</v>
+        <v>2010</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17413,20 +17403,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>2135</v>
+        <v>2038</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>3270</v>
+        <v>3045</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17445,7 +17435,7 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
@@ -17453,10 +17443,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1978</v>
+        <v>1964</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17477,20 +17467,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>14417</v>
+        <v>14420</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2531</v>
+        <v>2196</v>
       </c>
       <c r="O302" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17509,18 +17499,18 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4705</v>
+        <v>5020</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F303" s="2" t="n">
         <v>19</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4436</v>
+        <v>4487</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17541,20 +17531,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>5144</v>
+        <v>5255</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>5176</v>
+        <v>5246</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17573,18 +17563,18 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>2157</v>
+        <v>2715</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1865</v>
+        <v>1972</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17605,20 +17595,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2524</v>
+        <v>2312</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>2196</v>
+        <v>2987</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17682,7 +17672,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17705,7 +17695,7 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F306" s="2" t="n">
@@ -17736,17 +17726,17 @@
         <v>157</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>314</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>20643</v>
+        <v>20657</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17800,7 +17790,7 @@
         <v>913</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>314</v>
@@ -17810,7 +17800,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17837,7 +17827,7 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G308" s="3" t="n">
         <v>2039</v>
@@ -17864,17 +17854,17 @@
         <v>2039</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1254740</v>
+        <v>1254976</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17928,17 +17918,17 @@
         <v>4392</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>31714</v>
+        <v>31720</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O309" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -17957,7 +17947,7 @@
         </is>
       </c>
       <c r="D310" s="3" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
@@ -17989,20 +17979,20 @@
         </is>
       </c>
       <c r="L310" s="3" t="n">
-        <v>1871</v>
+        <v>1569</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="N310" s="3" t="n">
         <v>3137</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18043,20 +18033,20 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>5119</v>
+        <v>5120</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>5985</v>
+        <v>5986</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18099,12 +18089,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18113,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18134,7 +18124,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18155,20 +18145,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>25932</v>
+        <v>25937</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>42</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18209,20 +18199,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15344</v>
+        <v>15347</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15344</v>
+        <v>15347</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25095</v>
+        <v>25100</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18241,7 +18231,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18249,10 +18239,10 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18273,20 +18263,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1568426</v>
+        <v>1568720</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18295,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18316,7 +18306,7 @@
         <v>9</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18337,20 +18327,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>37642</v>
+        <v>37649</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75284</v>
+        <v>75299</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18359,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>101948</v>
+        <v>101967</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18377,10 +18367,10 @@
         </is>
       </c>
       <c r="F317" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>101948</v>
+        <v>101967</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18401,20 +18391,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>101948</v>
+        <v>101967</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>101948</v>
+        <v>101967</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>203895</v>
+        <v>203934</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18441,10 +18431,10 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18468,7 +18458,7 @@
         <v>1241</v>
       </c>
       <c r="M318" s="3" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="N318" s="3" t="n">
         <v>1128</v>
@@ -18478,7 +18468,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18532,7 +18522,7 @@
         <v>1382</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15578</v>
+        <v>15581</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>1520</v>
@@ -18542,7 +18532,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18596,7 +18586,7 @@
         <v>1098</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9745</v>
+        <v>9746</v>
       </c>
       <c r="N320" s="3" t="n">
         <v>2196</v>
@@ -18606,7 +18596,7 @@
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18625,7 +18615,7 @@
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
@@ -18636,7 +18626,7 @@
         <v>5</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18660,7 +18650,7 @@
         <v>3294</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>8200</v>
+        <v>8201</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>3617</v>
@@ -18670,7 +18660,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18689,7 +18679,7 @@
         </is>
       </c>
       <c r="D322" s="3" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
@@ -18724,7 +18714,7 @@
         <v>450</v>
       </c>
       <c r="M322" s="3" t="n">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="N322" s="3" t="n">
         <v>314</v>
@@ -18734,7 +18724,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18753,7 +18743,7 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>4468</v>
+        <v>4469</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -18785,10 +18775,10 @@
         </is>
       </c>
       <c r="L323" s="3" t="n">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="N323" s="3" t="n">
         <v>2196</v>
@@ -18798,7 +18788,7 @@
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18849,10 +18839,10 @@
         </is>
       </c>
       <c r="L324" s="3" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>314</v>
@@ -18862,7 +18852,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18881,18 +18871,18 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>3294</v>
+        <v>3310</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
         <v>17</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2978</v>
+        <v>3004</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18913,20 +18903,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>3309</v>
+        <v>3286</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15578</v>
+        <v>15581</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>3465</v>
+        <v>3490</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -18945,7 +18935,7 @@
         </is>
       </c>
       <c r="D326" s="3" t="n">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
@@ -18956,7 +18946,7 @@
         <v>6</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -18980,17 +18970,17 @@
         <v>2135</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19010,7 @@
         <v>6</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19044,7 +19034,7 @@
         <v>1098</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N327" s="3" t="n">
         <v>2196</v>
@@ -19054,7 +19044,7 @@
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19073,18 +19063,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>26306</v>
+        <v>25652</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
         <v>29</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>24583</v>
+        <v>24704</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19105,20 +19095,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>26094</v>
+        <v>25537</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>30300</v>
+        <v>30306</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>27407</v>
+        <v>28039</v>
       </c>
       <c r="O328" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19137,18 +19127,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7655</v>
+        <v>8098</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7275</v>
+        <v>7305</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19169,20 +19159,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>8096</v>
+        <v>8104</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9687</v>
+        <v>9688</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8324</v>
+        <v>8393</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19201,18 +19191,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5825</v>
+        <v>6796</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5791</v>
+        <v>5811</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19233,20 +19223,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6794</v>
+        <v>6789</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8582</v>
+        <v>8584</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6868</v>
+        <v>6931</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19287,7 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1057</v>
+        <v>1118</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>3137</v>
@@ -19310,7 +19300,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19329,18 +19319,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1439</v>
+        <v>1510</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19361,20 +19351,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1521</v>
+        <v>1547</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19401,10 +19391,10 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19428,7 +19418,7 @@
         <v>234</v>
       </c>
       <c r="M333" s="3" t="n">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="N333" s="3" t="n">
         <v>314</v>
@@ -19438,7 +19428,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19492,17 +19482,17 @@
         <v>386</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9342</v>
+        <v>9343</v>
       </c>
       <c r="N334" s="3" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O334" s="2" t="n">
         <v>31</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19521,7 +19511,7 @@
         </is>
       </c>
       <c r="D335" s="3" t="n">
-        <v>3830</v>
+        <v>3831</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
@@ -19553,20 +19543,20 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>4213</v>
+        <v>2196</v>
       </c>
       <c r="O335" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19620,7 +19610,7 @@
         <v>386</v>
       </c>
       <c r="M336" s="3" t="n">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="N336" s="3" t="n">
         <v>455</v>
@@ -19630,7 +19620,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19657,10 +19647,10 @@
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19684,7 +19674,7 @@
         <v>182</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15356</v>
+        <v>15359</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>314</v>
@@ -19694,7 +19684,7 @@
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19721,10 +19711,10 @@
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G338" s="3" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
@@ -19758,7 +19748,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19802,7 @@
         <v>684</v>
       </c>
       <c r="M339" s="3" t="n">
-        <v>4671</v>
+        <v>4672</v>
       </c>
       <c r="N339" s="3" t="n">
         <v>673</v>
@@ -19822,7 +19812,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19841,7 +19831,7 @@
         </is>
       </c>
       <c r="D340" s="3" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
@@ -19873,20 +19863,20 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="M340" s="3" t="n">
         <v>3137</v>
       </c>
       <c r="N340" s="3" t="n">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="O340" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19905,18 +19895,18 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>1568</v>
+        <v>1920</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>1237</v>
+        <v>1277</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19940,17 +19930,17 @@
         <v>1493</v>
       </c>
       <c r="M341" s="3" t="n">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>1703</v>
+        <v>1879</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20004,7 +19994,7 @@
         <v>507</v>
       </c>
       <c r="M342" s="3" t="n">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="N342" s="3" t="n">
         <v>314</v>
@@ -20014,7 +20004,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20068,7 +20058,7 @@
         <v>579</v>
       </c>
       <c r="M343" s="3" t="n">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="N343" s="3" t="n">
         <v>513</v>
@@ -20078,7 +20068,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20097,18 +20087,18 @@
         </is>
       </c>
       <c r="D344" s="3" t="n">
-        <v>2222</v>
+        <v>2130</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>2061</v>
+        <v>2118</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20132,7 +20122,7 @@
         <v>2817</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57210</v>
+        <v>57221</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3137</v>
@@ -20142,7 +20132,7 @@
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20161,18 +20151,18 @@
         </is>
       </c>
       <c r="D345" s="3" t="n">
-        <v>2191</v>
+        <v>2110</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>3045</v>
+        <v>2996</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20193,20 +20183,20 @@
         </is>
       </c>
       <c r="L345" s="3" t="n">
-        <v>2039</v>
+        <v>2392</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>75162</v>
+        <v>75176</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20249,12 +20239,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20308,17 +20298,17 @@
         <v>4392</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>7870</v>
+        <v>7872</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20359,20 +20349,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12547</v>
+        <v>12550</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20381,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20402,7 +20392,7 @@
         <v>5</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20423,20 +20413,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9411</v>
+        <v>9412</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19447</v>
+        <v>19451</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>18821</v>
+        <v>18825</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20479,12 +20469,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25095</v>
+        <v>25100</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20503,18 +20493,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>18638</v>
+        <v>16221</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17623</v>
+        <v>17681</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20535,20 +20525,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>18347</v>
+        <v>17606</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31369</v>
+        <v>31374</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20557,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>47517</v>
+        <v>47526</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20578,7 +20568,7 @@
         <v>11</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>44884</v>
+        <v>44893</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20599,20 +20589,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>48536</v>
+        <v>48546</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>48536</v>
+        <v>48546</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>75284</v>
+        <v>75299</v>
       </c>
       <c r="O352" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20631,7 +20621,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>115767</v>
+        <v>115789</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20642,7 +20632,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>115767</v>
+        <v>115789</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20665,12 +20655,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>203895</v>
+        <v>203934</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20697,10 +20687,10 @@
         </is>
       </c>
       <c r="F354" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G354" s="3" t="n">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
@@ -20734,7 +20724,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20743,7 @@
         </is>
       </c>
       <c r="D355" s="3" t="n">
-        <v>8783</v>
+        <v>8785</v>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
@@ -20764,7 +20754,7 @@
         <v>2</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>8783</v>
+        <v>8785</v>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
@@ -20785,20 +20775,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>8783</v>
+        <v>8785</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>18782</v>
+        <v>18785</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17566</v>
+        <v>17570</v>
       </c>
       <c r="O355" s="2" t="n">
         <v>87</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20817,7 +20807,7 @@
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>8783</v>
+        <v>8785</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -20828,7 +20818,7 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>8783</v>
+        <v>8785</v>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
@@ -20849,20 +20839,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>8783</v>
+        <v>8785</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>54895</v>
+        <v>54905</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17566</v>
+        <v>17570</v>
       </c>
       <c r="O356" s="2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20889,10 +20879,10 @@
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
@@ -20916,17 +20906,17 @@
         <v>480</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>15684</v>
+        <v>15687</v>
       </c>
       <c r="N357" s="3" t="n">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="O357" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -20986,11 +20976,11 @@
         <v>391</v>
       </c>
       <c r="O358" s="2" t="n">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -21038,12 +21028,62 @@
       <c r="O359" s="2" t="inlineStr"/>
       <c r="P359" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>9周年･栄光殿堂チケットBOX（取引可能）</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>不明（カテゴリタグなし）</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="inlineStr"/>
+      <c r="E360" s="2" t="inlineStr"/>
+      <c r="F360" s="2" t="inlineStr"/>
+      <c r="G360" s="3" t="inlineStr"/>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>直近30日間の取引データなし</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="n">
+        <v>1882</v>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>9th Anniversary · Hall of Glory Exclusive Draw Ticket Gift Box (Tradable)</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="3" t="n">
+        <v>8785</v>
+      </c>
+      <c r="M360" s="3" t="n">
+        <v>8785</v>
+      </c>
+      <c r="N360" s="3" t="n">
+        <v>17570</v>
+      </c>
+      <c r="O360" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P360" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P359"/>
+  <autoFilter ref="A1:P360"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21068,7 +21108,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>156.842558</v>
+        <v>156.872016</v>
       </c>
     </row>
     <row r="2">
@@ -21079,7 +21119,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sun, 25 Oct 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Mon, 26 Oct 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21091,7 +21131,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -578,14 +578,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3262</v>
+        <v>3210</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3158</v>
+        <v>4473</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6316</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>6316</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>96521</v>
+        <v>96529</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -736,12 +736,12 @@
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="n">
-        <v>25263</v>
+        <v>25265</v>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23684</v>
+        <v>23686</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23684</v>
+        <v>23686</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -794,12 +794,12 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>47368</v>
+        <v>47372</v>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85262</v>
+        <v>85269</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -904,20 +904,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>126314</v>
+        <v>126324</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>142103</v>
+        <v>142115</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>252628</v>
+        <v>252649</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -958,20 +958,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>355259</v>
+        <v>355287</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>355259</v>
+        <v>355287</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>710517</v>
+        <v>710574</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -990,18 +990,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5829</v>
+        <v>5394</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6043</v>
+        <v>6001</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5831</v>
+        <v>5819</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8684</v>
+        <v>8685</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>123</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1054,18 +1054,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>9174</v>
+        <v>9547</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8597</v>
+        <v>8610</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1086,20 +1086,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>9221</v>
+        <v>9732</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>149957</v>
+        <v>149969</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17368</v>
+        <v>17370</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1118,18 +1118,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13895</v>
+        <v>13896</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
         <v>23</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14105</v>
+        <v>14106</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1150,20 +1150,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13895</v>
+        <v>13896</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42393</v>
+        <v>42396</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34736</v>
+        <v>34739</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1204,20 +1204,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>17278</v>
+        <v>17280</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39473</v>
+        <v>39476</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22105</v>
+        <v>22107</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1258,20 +1258,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>93818</v>
+        <v>93826</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>93818</v>
+        <v>93826</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22105</v>
+        <v>22107</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1312,20 +1312,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>189471</v>
+        <v>189486</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1366,20 +1366,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>29147</v>
+        <v>29149</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>63964</v>
+        <v>63969</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5368</v>
+        <v>5369</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1420,20 +1420,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22501</v>
+        <v>22503</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>63964</v>
+        <v>63969</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5368</v>
+        <v>5369</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1579</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         <v>1579</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>227380</v>
+        <v>227398</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3158</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
         <v>3158</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>268418</v>
+        <v>268439</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6316</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1636,20 +1636,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22105</v>
+        <v>22107</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11368</v>
+        <v>11369</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1690,20 +1690,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11052</v>
+        <v>11053</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36900</v>
+        <v>36902</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22105</v>
+        <v>22107</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1744,20 +1744,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21316</v>
+        <v>21317</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>139372</v>
+        <v>139383</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1798,20 +1798,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39473</v>
+        <v>39476</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>321053</v>
+        <v>321078</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>78946</v>
+        <v>78953</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1863,20 +1863,20 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>2043</v>
+        <v>1939</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>316</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2013,18 +2013,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1147</v>
+        <v>1157</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2045,20 +2045,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1271</v>
+        <v>1290</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1574733</v>
+        <v>1574860</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1579</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
         <v>26</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
         <v>1579</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3158</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2176,7 +2176,7 @@
         <v>3158</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17011</v>
+        <v>17013</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6316</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
         <v>632</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1263</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11518</v>
+        <v>11519</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>4737</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2333,18 +2333,18 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>969</v>
+        <v>790</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>969</v>
+        <v>880</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2365,20 +2365,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>789</v>
+        <v>960</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>631571</v>
+        <v>631621</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1579</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12791</v>
+        <v>12792</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3158</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2461,18 +2461,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3504</v>
+        <v>3540</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3450</v>
+        <v>3455</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2493,20 +2493,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3687</v>
+        <v>3589</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21106</v>
+        <v>21107</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>6316</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2529,14 +2529,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6653</v>
+        <v>6634</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2560,17 +2560,17 @@
         <v>6316</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30519</v>
+        <v>30522</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>6270</v>
@@ -2626,11 +2626,11 @@
         <v>1579</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>2444</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4149</v>
+        <v>4150</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>3158</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>3158</v>
@@ -2737,20 +2737,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3158</v>
+        <v>3689</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>315785</v>
+        <v>315811</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6316</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
         <v>1579</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>144546</v>
+        <v>144558</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3158</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4454</v>
+        <v>4455</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17370</v>
+        <v>17371</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>6316</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -2932,17 +2932,17 @@
         <v>6316</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15106</v>
+        <v>15107</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -2989,20 +2989,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>3579</v>
+        <v>3580</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6115</v>
+        <v>6116</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6695</v>
+        <v>6526</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3081,18 +3081,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9227</v>
+        <v>9144</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9591</v>
+        <v>9582</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3109,20 +3109,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9655</v>
+        <v>9129</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>13749</v>
+        <v>13750</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10331</v>
+        <v>10280</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
         <v>3158</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>6316</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3284,17 @@
         <v>772</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>5864</v>
+        <v>5865</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>902</v>
+        <v>1025</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -3459,20 +3459,20 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>4140</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O50" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3519,10 +3519,10 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>4356</v>
+        <v>4357</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4356</v>
+        <v>4357</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1579</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3569,10 +3569,10 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6789</v>
+        <v>6790</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>3158</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -3633,20 +3633,20 @@
         </is>
       </c>
       <c r="L53" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4814</v>
+        <v>4815</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>868</v>
+        <v>790</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>1895</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11275</v>
+        <v>11276</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1579</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30541</v>
+        <v>30544</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3158</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>2</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3815,20 +3815,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>7795</v>
+        <v>7796</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>7817</v>
+        <v>7818</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>6614</v>
+        <v>6615</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3847,18 +3847,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10031</v>
+        <v>9593</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9506</v>
+        <v>9529</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3879,20 +3879,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>10055</v>
+        <v>10057</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30581</v>
+        <v>30583</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
         <v>33</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3637</v>
+        <v>3644</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3943,20 +3943,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3876</v>
+        <v>3168</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10307</v>
+        <v>10308</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3980</v>
+        <v>4076</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11289</v>
+        <v>11290</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>3076</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>5053</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4171,12 +4171,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9789</v>
+        <v>9790</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4217,20 +4217,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4273,12 +4273,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4321,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4367,20 +4367,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50526</v>
+        <v>50530</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4421,20 +4421,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22105</v>
+        <v>22107</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22105</v>
+        <v>22107</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4532,11 +4532,11 @@
         <v>1579</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>3887</v>
+        <v>3888</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>5021</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4688,17 @@
         <v>2526</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1481100</v>
+        <v>1481219</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11368</v>
+        <v>11369</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4793,20 +4793,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8684</v>
+        <v>8685</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20919</v>
+        <v>20921</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17368</v>
+        <v>17370</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4847,20 +4847,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17368</v>
+        <v>17370</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27003</v>
+        <v>27005</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
         <v>300</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6363</v>
+        <v>6364</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>1236</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
         <v>535</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>632</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>2526</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5169,20 +5169,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23093</v>
+        <v>23095</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23093</v>
+        <v>23095</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10105</v>
+        <v>10106</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5225,12 +5225,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20210</v>
+        <v>20212</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>31692</v>
+        <v>31695</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>5</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>6487</v>
+        <v>6488</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5280,17 +5280,17 @@
         <v>240</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1578769</v>
+        <v>1578896</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>17561</v>
+        <v>17562</v>
       </c>
       <c r="O83" s="2" t="n">
         <v>355</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
         <v>351</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34515</v>
+        <v>34518</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1579</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
         <v>1579</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>3158</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="n">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="M86" s="3" t="n">
         <v>6316</v>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10105</v>
+        <v>10106</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5553,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14210</v>
+        <v>14211</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5597,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17368</v>
+        <v>17370</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5652,17 +5652,17 @@
         <v>292</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>85812</v>
+        <v>85818</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O90" s="2" t="n">
         <v>59</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5699,10 +5699,10 @@
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5248</v>
+        <v>5249</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1579</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10105</v>
+        <v>10106</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5895,12 +5895,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14210</v>
+        <v>14211</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17368</v>
+        <v>17370</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6119,14 +6119,14 @@
         <v>5168</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9789</v>
+        <v>9790</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6167,20 +6167,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6223,12 +6223,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6269,20 +6269,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>17938</v>
+        <v>17940</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>17938</v>
+        <v>17940</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50526</v>
+        <v>50530</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6485,12 +6485,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9789</v>
+        <v>9790</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6581,12 +6581,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6677,12 +6677,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50526</v>
+        <v>50530</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6725,12 +6725,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>78946</v>
+        <v>78953</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6771,20 +6771,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>86841</v>
+        <v>86848</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>96937</v>
+        <v>96944</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>110525</v>
+        <v>110534</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>110525</v>
+        <v>110534</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>2</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>110525</v>
+        <v>110534</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6835,20 +6835,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>110525</v>
+        <v>110534</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>110525</v>
+        <v>110534</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>142103</v>
+        <v>142115</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6889,20 +6889,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>126314</v>
+        <v>126324</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>126314</v>
+        <v>126324</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6943,20 +6943,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>189471</v>
+        <v>189486</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>213155</v>
+        <v>213172</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>3</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>213155</v>
+        <v>213172</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -7007,20 +7007,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>213155</v>
+        <v>213172</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>252628</v>
+        <v>252649</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>252628</v>
+        <v>252649</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7067,14 +7067,14 @@
         <v>2263</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O117" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7115,20 +7115,20 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3786</v>
+        <v>3787</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>5839</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7217,20 +7217,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14210</v>
+        <v>14211</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14210</v>
+        <v>14211</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7273,12 +7273,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22737</v>
+        <v>22738</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7319,20 +7319,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>40992</v>
+        <v>40995</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7443,14 +7443,14 @@
         <v>1922</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O124" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7497,14 +7497,14 @@
         <v>5670</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
         <v>5730</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6448</v>
+        <v>6449</v>
       </c>
       <c r="N126" s="3" t="n">
         <v>7895</v>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7599,20 +7599,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11862</v>
+        <v>11863</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14210</v>
+        <v>14211</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22737</v>
+        <v>22738</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7703,12 +7703,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7756,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7854,17 +7854,17 @@
         <v>6316</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>10705</v>
+        <v>10706</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7908,17 +7908,17 @@
         <v>9474</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15876</v>
+        <v>15877</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7961,12 +7961,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28421</v>
+        <v>28423</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8007,20 +8007,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21316</v>
+        <v>21317</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21316</v>
+        <v>21317</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47368</v>
+        <v>47372</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8061,20 +8061,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28421</v>
+        <v>28423</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28421</v>
+        <v>28423</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71052</v>
+        <v>71057</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8115,20 +8115,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8182,17 +8182,17 @@
         <v>6316</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12721</v>
+        <v>12722</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O138" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
         <v>758</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>316</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8428,7 @@
         <v>1579</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>13462</v>
+        <v>13463</v>
       </c>
       <c r="N142" s="3" t="n">
         <v>316</v>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="L143" s="3" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="M143" s="3" t="n">
         <v>6316</v>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8546,17 +8546,17 @@
         <v>3314</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10718</v>
+        <v>10719</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="O144" s="2" t="n">
         <v>48</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
         <v>4421</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53396</v>
+        <v>53400</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>6316</v>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8701,12 +8701,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8750,17 +8750,17 @@
         <v>9474</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17302</v>
+        <v>17303</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8803,12 +8803,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25263</v>
+        <v>25265</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8827,18 +8827,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8859,20 +8859,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39473</v>
+        <v>39476</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8891,18 +8891,18 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8923,20 +8923,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>63107</v>
+        <v>63112</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75788</v>
+        <v>75795</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -8977,20 +8977,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>102630</v>
+        <v>102638</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>102630</v>
+        <v>102638</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>205260</v>
+        <v>205277</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
         <v>158</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10329</v>
+        <v>10330</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>316</v>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>1</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -9165,10 +9165,10 @@
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1579</v>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="L158" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1579</v>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
         <v>1579</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19148</v>
+        <v>19149</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3158</v>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>2226</v>
+        <v>2061</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30126</v>
+        <v>30128</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>2119</v>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9587,18 +9587,18 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>2368</v>
+        <v>3474</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>2572</v>
+        <v>2753</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -9619,20 +9619,20 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3474</v>
+        <v>3626</v>
       </c>
       <c r="M163" s="3" t="n">
         <v>3842</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3158</v>
+        <v>3213</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9651,18 +9651,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3493</v>
+        <v>3834</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3672</v>
+        <v>3658</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3834</v>
+        <v>3877</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>10263</v>
+        <v>10264</v>
       </c>
       <c r="N164" s="3" t="n">
         <v>6316</v>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
         <v>4</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1453</v>
+        <v>1356</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9704</v>
+        <v>9705</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1263</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
         <v>1579</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5384</v>
+        <v>5385</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>1737</v>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9983,20 +9983,20 @@
         </is>
       </c>
       <c r="L169" s="3" t="n">
-        <v>3279</v>
+        <v>534</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O169" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>94736</v>
+        <v>94743</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>94736</v>
+        <v>94743</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -10047,20 +10047,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94736</v>
+        <v>94743</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94736</v>
+        <v>94743</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>126314</v>
+        <v>126324</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10103,12 +10103,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10145,20 +10145,20 @@
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O172" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10201,14 +10201,14 @@
         <v>3363</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10289,20 +10289,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14180</v>
+        <v>14181</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14210</v>
+        <v>14211</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10339,20 +10339,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11368</v>
+        <v>11369</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11368</v>
+        <v>11369</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22737</v>
+        <v>22738</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10389,20 +10389,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>27213</v>
+        <v>27215</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10439,20 +10439,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19105</v>
+        <v>19107</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10597,12 +10597,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10649,14 +10649,14 @@
         <v>9474</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28421</v>
+        <v>28423</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10745,20 +10745,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21316</v>
+        <v>21317</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21316</v>
+        <v>21317</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42631</v>
+        <v>42634</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10799,20 +10799,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28421</v>
+        <v>28423</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28421</v>
+        <v>28423</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56841</v>
+        <v>56846</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
         <v>158</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>316</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
         <v>158</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>316</v>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
         <v>158</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102728</v>
+        <v>102736</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>316</v>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
         <v>158</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29122</v>
+        <v>29124</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>316</v>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
         <v>158</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>155892</v>
+        <v>155905</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>316</v>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11158,23 +11158,13 @@
           <t>チップ / チップ</t>
         </is>
       </c>
-      <c r="D192" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G192" s="3" t="n">
-        <v>158</v>
-      </c>
+      <c r="D192" s="3" t="inlineStr"/>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="3" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I192" s="2" t="n">
@@ -11194,7 +11184,7 @@
         <v>158</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>316</v>
@@ -11204,7 +11194,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11242,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11296,7 @@
         <v>158</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>316</v>
@@ -11316,7 +11306,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11350,7 @@
         <v>158</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>316</v>
@@ -11370,7 +11360,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11379,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>21263</v>
+        <v>21265</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -11400,7 +11390,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>21263</v>
+        <v>21265</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -11424,7 +11414,7 @@
         <v>158</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>316</v>
@@ -11434,7 +11424,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11472,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11502,7 @@
         <v>3</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -11536,7 +11526,7 @@
         <v>976</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>963</v>
@@ -11546,7 +11536,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11587,20 +11577,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11651,20 +11641,20 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>6159</v>
+        <v>4421</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6295</v>
+        <v>6296</v>
       </c>
       <c r="N200" s="3" t="n">
         <v>6316</v>
       </c>
       <c r="O200" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11698,7 @@
         <v>5053</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10757</v>
+        <v>10758</v>
       </c>
       <c r="N201" s="3" t="n">
         <v>7579</v>
@@ -11718,7 +11708,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11762,17 +11752,17 @@
         <v>6316</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10332</v>
+        <v>10333</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10105</v>
+        <v>10106</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11813,20 +11803,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8210</v>
+        <v>8211</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>275633</v>
+        <v>275655</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>13895</v>
+        <v>13896</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11867,20 +11857,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15601</v>
+        <v>15603</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16013</v>
+        <v>16015</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11921,20 +11911,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20210</v>
+        <v>20212</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>48708</v>
+        <v>48712</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -11977,12 +11967,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22737</v>
+        <v>22738</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12046,7 +12036,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12090,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12147,14 +12137,14 @@
         <v>2997</v>
       </c>
       <c r="N209" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O209" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12201,14 +12191,14 @@
         <v>4464</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>4105</v>
+        <v>4106</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12239,7 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="M211" s="3" t="n">
         <v>7895</v>
@@ -12262,7 +12252,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12303,20 +12293,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14210</v>
+        <v>14211</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12359,12 +12349,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22737</v>
+        <v>22738</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12405,20 +12395,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12465,14 +12455,14 @@
         <v>2727</v>
       </c>
       <c r="N215" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O215" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12516,17 +12506,17 @@
         <v>2053</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11856</v>
+        <v>11857</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>4105</v>
+        <v>4106</v>
       </c>
       <c r="O216" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12567,20 +12557,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>13895</v>
+        <v>15547</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>29295</v>
+        <v>29298</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25263</v>
+        <v>25265</v>
       </c>
       <c r="O217" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12611,7 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>4855</v>
+        <v>4856</v>
       </c>
       <c r="M218" s="3" t="n">
         <v>4868</v>
@@ -12634,7 +12624,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12643,7 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
@@ -12664,7 +12654,7 @@
         <v>1</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -12685,20 +12675,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7105</v>
+        <v>7106</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14210</v>
+        <v>14211</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12741,12 +12731,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12787,20 +12777,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>18955</v>
+        <v>18957</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12809,7 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
@@ -12830,7 +12820,7 @@
         <v>2</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -12851,7 +12841,7 @@
         </is>
       </c>
       <c r="L222" s="3" t="n">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M222" s="3" t="n">
         <v>2836</v>
@@ -12860,11 +12850,11 @@
         <v>1579</v>
       </c>
       <c r="O222" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12898,7 @@
         <v>1579</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="N223" s="3" t="n">
         <v>3158</v>
@@ -12918,7 +12908,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12962,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13016,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13070,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13131,10 +13121,10 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="N227" s="3" t="n">
         <v>6316</v>
@@ -13144,7 +13134,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13178,7 @@
         <v>158</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>316</v>
@@ -13198,7 +13188,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13232,7 @@
         <v>158</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>316</v>
@@ -13252,7 +13242,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13271,7 +13261,7 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>44630</v>
+        <v>44634</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -13282,7 +13272,7 @@
         <v>1</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>44630</v>
+        <v>44634</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -13306,7 +13296,7 @@
         <v>158</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>316</v>
@@ -13316,7 +13306,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13357,10 +13347,10 @@
         </is>
       </c>
       <c r="L231" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1579</v>
@@ -13370,7 +13360,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13424,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13488,7 +13478,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13532,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13586,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13637,20 +13627,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6511</v>
+        <v>6512</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13698,7 +13688,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13739,10 +13729,10 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8820</v>
+        <v>8821</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11007</v>
+        <v>11008</v>
       </c>
       <c r="N238" s="3" t="n">
         <v>6316</v>
@@ -13752,7 +13742,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13795,12 +13785,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13843,12 +13833,12 @@
       <c r="L240" s="3" t="inlineStr"/>
       <c r="M240" s="3" t="inlineStr"/>
       <c r="N240" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13867,7 +13857,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>22473</v>
+        <v>22475</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -13878,7 +13868,7 @@
         <v>8</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>20268</v>
+        <v>20270</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -13899,20 +13889,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>22193</v>
+        <v>22195</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30590</v>
+        <v>30593</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13921,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>37896</v>
+        <v>37899</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -13942,7 +13932,7 @@
         <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>39909</v>
+        <v>39912</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -13963,20 +13953,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>56537</v>
+        <v>56541</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58502</v>
+        <v>58507</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75788</v>
+        <v>75795</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -13995,7 +13985,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14006,7 +13996,7 @@
         <v>10</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>18662</v>
+        <v>18664</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14023,20 +14013,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>17960</v>
+        <v>17962</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31578536</v>
+        <v>31581074</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14079,12 +14069,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25263</v>
+        <v>25265</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14128,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14157,7 +14147,7 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
@@ -14165,10 +14155,10 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2860</v>
+        <v>2955</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14189,20 +14179,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="M246" s="3" t="n">
         <v>6316</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>3035</v>
+        <v>3073</v>
       </c>
       <c r="O246" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14243,20 +14233,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15505</v>
+        <v>15506</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23280</v>
+        <v>23282</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17684</v>
+        <v>17685</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14299,12 +14289,12 @@
       <c r="L248" s="3" t="inlineStr"/>
       <c r="M248" s="3" t="inlineStr"/>
       <c r="N248" s="3" t="n">
-        <v>17684</v>
+        <v>17685</v>
       </c>
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14341,10 +14331,10 @@
       </c>
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9270</v>
+        <v>9271</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1579</v>
@@ -14354,7 +14344,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14404,7 +14394,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14438,7 @@
         <v>158</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97090</v>
+        <v>97098</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>316</v>
@@ -14458,7 +14448,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14509,10 +14499,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50311</v>
+        <v>50315</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50311</v>
+        <v>50315</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6316</v>
@@ -14522,7 +14512,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14573,10 +14563,10 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>8496</v>
+        <v>8497</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>8496</v>
+        <v>8497</v>
       </c>
       <c r="N253" s="3" t="n">
         <v>7579</v>
@@ -14586,7 +14576,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14629,12 +14619,12 @@
       <c r="L254" s="3" t="inlineStr"/>
       <c r="M254" s="3" t="inlineStr"/>
       <c r="N254" s="3" t="n">
-        <v>10105</v>
+        <v>10106</v>
       </c>
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14678,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14742,7 +14732,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14786,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14819,14 +14809,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -14850,17 +14840,17 @@
         <v>316</v>
       </c>
       <c r="M258" s="3" t="n">
-        <v>15785</v>
+        <v>15786</v>
       </c>
       <c r="N258" s="3" t="n">
         <v>632</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14914,7 +14904,7 @@
         <v>973</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21352</v>
+        <v>21354</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1579</v>
@@ -14924,7 +14914,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -14965,10 +14955,10 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2313</v>
+        <v>2132</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="N260" s="3" t="n">
         <v>3158</v>
@@ -14978,7 +14968,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15022,7 @@
         <v>3158</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7004</v>
+        <v>7005</v>
       </c>
       <c r="N261" s="3" t="n">
         <v>6316</v>
@@ -15042,7 +15032,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15065,14 +15055,14 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6508</v>
+        <v>6487</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15096,17 +15086,17 @@
         <v>6316</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15125,7 +15115,7 @@
         </is>
       </c>
       <c r="D263" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
@@ -15136,7 +15126,7 @@
         <v>1</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -15157,10 +15147,10 @@
         </is>
       </c>
       <c r="L263" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10544</v>
+        <v>10545</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1579</v>
@@ -15170,7 +15160,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15214,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15262,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15326,17 +15316,17 @@
         <v>6780</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9622</v>
+        <v>9623</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15345,7 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -15390,7 +15380,7 @@
         <v>2735</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19419</v>
+        <v>19421</v>
       </c>
       <c r="N267" s="3" t="n">
         <v>632</v>
@@ -15400,7 +15390,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15419,7 +15409,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8210</v>
+        <v>8211</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15430,7 +15420,7 @@
         <v>1</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8210</v>
+        <v>8211</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15451,20 +15441,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>12603</v>
+        <v>12604</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14223</v>
+        <v>14224</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>13895</v>
+        <v>13896</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15507,12 +15497,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15555,12 +15545,12 @@
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="3" t="n">
-        <v>25263</v>
+        <v>25265</v>
       </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15569,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>28421</v>
+        <v>28423</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15590,7 +15580,7 @@
         <v>3</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>23841</v>
+        <v>23843</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15611,20 +15601,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24442</v>
+        <v>24283</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>24442</v>
+        <v>24283</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15658,7 @@
         <v>158</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>316</v>
@@ -15678,7 +15668,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15697,7 +15687,7 @@
         </is>
       </c>
       <c r="D273" s="3" t="n">
-        <v>14997</v>
+        <v>14998</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -15708,7 +15698,7 @@
         <v>1</v>
       </c>
       <c r="G273" s="3" t="n">
-        <v>14997</v>
+        <v>14998</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -15732,17 +15722,17 @@
         <v>158</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>20911</v>
+        <v>20913</v>
       </c>
       <c r="N273" s="3" t="n">
-        <v>16495</v>
+        <v>316</v>
       </c>
       <c r="O273" s="2" t="n">
         <v>204</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15776,7 @@
         <v>158</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31683</v>
+        <v>31685</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>316</v>
@@ -15796,7 +15786,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15840,7 @@
         <v>158</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15868</v>
+        <v>15869</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>316</v>
@@ -15860,7 +15850,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15894,7 @@
         <v>158</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>157417</v>
+        <v>157430</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>316</v>
@@ -15914,7 +15904,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -15933,7 +15923,7 @@
         </is>
       </c>
       <c r="D277" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -15944,7 +15934,7 @@
         <v>1</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -15961,7 +15951,7 @@
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="3" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M277" s="3" t="n">
         <v>2108</v>
@@ -15974,7 +15964,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16018,17 +16008,17 @@
         <v>4421</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>6988</v>
+        <v>6989</v>
       </c>
       <c r="N278" s="3" t="n">
         <v>6316</v>
       </c>
       <c r="O278" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16072,7 +16062,7 @@
         <v>5053</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9879</v>
+        <v>9880</v>
       </c>
       <c r="N279" s="3" t="n">
         <v>7579</v>
@@ -16082,7 +16072,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16129,14 +16119,14 @@
         <v>8593</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10105</v>
+        <v>10106</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16179,12 +16169,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>13895</v>
+        <v>13896</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16227,12 +16217,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16275,12 +16265,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25263</v>
+        <v>25265</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16321,20 +16311,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>20210</v>
+        <v>20212</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33666</v>
+        <v>33669</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16353,7 +16343,7 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>12265</v>
+        <v>12266</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -16385,20 +16375,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>12267</v>
+        <v>12268</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10752</v>
+        <v>12021</v>
       </c>
       <c r="O285" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16452,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16509,20 +16499,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5277</v>
+        <v>5280</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>6200</v>
+        <v>6201</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>6229</v>
+        <v>6245</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16541,18 +16531,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>7599</v>
+        <v>7600</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6674</v>
+        <v>6699</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16569,20 +16559,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7483</v>
+        <v>7628</v>
       </c>
       <c r="M288" s="3" t="n">
         <v>7816</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7754</v>
+        <v>7838</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16609,10 +16599,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>10006</v>
+        <v>9962</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16629,20 +16619,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9191</v>
+        <v>9192</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11654</v>
+        <v>11655</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>9813</v>
+        <v>9814</v>
       </c>
       <c r="O289" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16699,14 +16689,14 @@
         <v>3158</v>
       </c>
       <c r="N290" s="3" t="n">
-        <v>1667</v>
+        <v>1737</v>
       </c>
       <c r="O290" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16770,7 +16760,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16800,7 +16790,7 @@
         <v>3</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4439</v>
+        <v>4440</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16821,7 +16811,7 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>5368</v>
+        <v>5369</v>
       </c>
       <c r="M292" s="3" t="n">
         <v>6796</v>
@@ -16834,7 +16824,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16888,7 +16878,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16897,7 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>6227</v>
+        <v>6228</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -16915,10 +16905,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7389</v>
+        <v>7523</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -16942,17 +16932,17 @@
         <v>9695</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>12753</v>
+        <v>12754</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>8332</v>
+        <v>8067</v>
       </c>
       <c r="O294" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -16993,20 +16983,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>50740</v>
+        <v>50744</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>697477</v>
+        <v>697533</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39473</v>
+        <v>39476</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17015,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17033,10 +17023,10 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17057,20 +17047,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68650</v>
+        <v>68656</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39473</v>
+        <v>39476</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17079,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63157</v>
+        <v>63162</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17100,7 +17090,7 @@
         <v>5</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63157</v>
+        <v>63162</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17121,20 +17111,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63157</v>
+        <v>63162</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>126314</v>
+        <v>126324</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>78946</v>
+        <v>78953</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17143,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>126314</v>
+        <v>126324</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17164,7 +17154,7 @@
         <v>4</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>126314</v>
+        <v>126324</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17185,20 +17175,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>126314</v>
+        <v>126324</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>126317</v>
+        <v>126327</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>157893</v>
+        <v>157905</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17207,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>252628</v>
+        <v>252649</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17228,7 +17218,7 @@
         <v>3</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>252628</v>
+        <v>252649</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17249,20 +17239,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>252628</v>
+        <v>252649</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>252630</v>
+        <v>252650</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>315785</v>
+        <v>315811</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17281,18 +17271,18 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>442099</v>
+        <v>442135</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>442099</v>
+        <v>442135</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17313,20 +17303,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>442099</v>
+        <v>442135</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>846651</v>
+        <v>846719</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>631571</v>
+        <v>631621</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17345,18 +17335,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>1922</v>
+        <v>1841</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2516</v>
+        <v>2531</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17380,17 +17370,17 @@
         <v>1892</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2698</v>
+        <v>2534</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17417,10 +17407,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1903</v>
+        <v>1936</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17441,20 +17431,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>2245</v>
+        <v>2233</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>14513</v>
+        <v>14515</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O302" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17473,7 +17463,7 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>5289</v>
+        <v>5290</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -17484,7 +17474,7 @@
         <v>18</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4630</v>
+        <v>4631</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17505,20 +17495,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>5289</v>
+        <v>5290</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>5433</v>
+        <v>5524</v>
       </c>
       <c r="O303" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17545,10 +17535,10 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>2110</v>
+        <v>2278</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17569,20 +17559,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="O304" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17646,7 +17636,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17700,17 +17690,17 @@
         <v>158</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>20704</v>
+        <v>20604</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17754,7 @@
         <v>919</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>316</v>
@@ -17774,7 +17764,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17797,11 +17787,11 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G308" s="3" t="n">
         <v>2053</v>
@@ -17828,17 +17818,17 @@
         <v>2053</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1263141</v>
+        <v>1263243</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17882,7 @@
         <v>4421</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>31926</v>
+        <v>31928</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6316</v>
@@ -17902,7 +17892,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -17962,11 +17952,11 @@
         <v>3158</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18010,7 +18000,7 @@
         <v>5154</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>6025</v>
+        <v>6026</v>
       </c>
       <c r="N311" s="3" t="n">
         <v>4737</v>
@@ -18020,7 +18010,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18063,12 +18053,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18122,17 +18112,17 @@
         <v>9474</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26106</v>
+        <v>26108</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>41</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18173,20 +18163,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15447</v>
+        <v>15448</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15447</v>
+        <v>15448</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25263</v>
+        <v>25265</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18205,18 +18195,18 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18237,20 +18227,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1578927</v>
+        <v>1579054</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18269,7 +18259,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18280,7 +18270,7 @@
         <v>9</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18301,20 +18291,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>37894</v>
+        <v>37897</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75788</v>
+        <v>75795</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18323,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>102630</v>
+        <v>102638</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18344,7 +18334,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>102630</v>
+        <v>102638</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18365,20 +18355,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>102630</v>
+        <v>102638</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>102630</v>
+        <v>102638</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>205260</v>
+        <v>205277</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18435,14 +18425,14 @@
         <v>2048</v>
       </c>
       <c r="N318" s="3" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="O318" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18496,7 +18486,7 @@
         <v>1391</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15682</v>
+        <v>15683</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>1530</v>
@@ -18506,7 +18496,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18560,17 +18550,17 @@
         <v>1105</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9810</v>
+        <v>9811</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O320" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18589,18 +18579,18 @@
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>3632</v>
+        <v>3790</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3318</v>
+        <v>3370</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18621,20 +18611,20 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3789</v>
+        <v>3948</v>
       </c>
       <c r="M321" s="3" t="n">
         <v>8255</v>
       </c>
       <c r="N321" s="3" t="n">
-        <v>3785</v>
+        <v>3848</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18698,7 +18688,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18717,7 +18707,7 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>4498</v>
+        <v>4499</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -18752,17 +18742,17 @@
         <v>1944</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O323" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18816,7 +18806,7 @@
         <v>507</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5583</v>
+        <v>5584</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>316</v>
@@ -18826,7 +18816,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18853,10 +18843,10 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>3046</v>
+        <v>3062</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18877,20 +18867,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>3107</v>
+        <v>3059</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15682</v>
+        <v>15683</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>3564</v>
+        <v>3596</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18909,18 +18899,18 @@
         </is>
       </c>
       <c r="D326" s="3" t="n">
-        <v>2150</v>
+        <v>2915</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F326" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2162</v>
+        <v>2342</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -18944,17 +18934,17 @@
         <v>2149</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>2365</v>
+        <v>2785</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -18973,18 +18963,18 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>1680</v>
+        <v>1105</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>2126</v>
+        <v>1956</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19005,20 +18995,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>1105</v>
+        <v>1679</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19037,7 +19027,7 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>24259</v>
+        <v>24261</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
@@ -19045,10 +19035,10 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>24922</v>
+        <v>25065</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19069,20 +19059,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>23744</v>
+        <v>23700</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>30503</v>
+        <v>30506</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>27713</v>
+        <v>27716</v>
       </c>
       <c r="O328" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19101,18 +19091,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7917</v>
+        <v>7848</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
         <v>43</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7421</v>
+        <v>7435</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19133,20 +19123,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7478</v>
+        <v>8254</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9751</v>
+        <v>9752</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8539</v>
+        <v>8560</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19165,18 +19155,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>6834</v>
+        <v>6506</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
         <v>32</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5847</v>
+        <v>5862</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19197,20 +19187,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6832</v>
+        <v>6694</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8640</v>
+        <v>8641</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6783</v>
+        <v>7024</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19219,7 @@
         </is>
       </c>
       <c r="D331" s="3" t="n">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -19274,7 +19264,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19294,7 @@
         <v>19</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19325,20 +19315,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N332" s="3" t="n">
         <v>1693</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19402,7 +19392,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19453,10 +19443,10 @@
         </is>
       </c>
       <c r="L334" s="3" t="n">
-        <v>388</v>
+        <v>485</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9404</v>
+        <v>9405</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>426</v>
@@ -19466,7 +19456,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19520,17 +19510,17 @@
         <v>2296</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="O335" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19549,18 +19539,18 @@
         </is>
       </c>
       <c r="D336" s="3" t="n">
-        <v>819</v>
+        <v>387</v>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19587,14 +19577,14 @@
         <v>2893</v>
       </c>
       <c r="N336" s="3" t="n">
-        <v>679</v>
+        <v>594</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19617,14 +19607,14 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19648,17 +19638,17 @@
         <v>183</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15459</v>
+        <v>15461</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19722,7 +19712,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19749,10 +19739,10 @@
         </is>
       </c>
       <c r="F339" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G339" s="3" t="n">
-        <v>1313</v>
+        <v>1364</v>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
@@ -19786,7 +19776,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19850,7 +19840,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19869,18 +19859,18 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>2053</v>
+        <v>1533</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
         <v>17</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19904,17 +19894,17 @@
         <v>1533</v>
       </c>
       <c r="M341" s="3" t="n">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>1944</v>
+        <v>1937</v>
       </c>
       <c r="O341" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -19968,7 +19958,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20019,20 +20009,20 @@
         </is>
       </c>
       <c r="L343" s="3" t="n">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="M343" s="3" t="n">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="N343" s="3" t="n">
         <v>516</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20059,10 +20049,10 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>2177</v>
+        <v>2099</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20086,7 +20076,7 @@
         <v>1746</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57593</v>
+        <v>57598</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3158</v>
@@ -20096,7 +20086,7 @@
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20150,17 +20140,17 @@
         <v>2053</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>75665</v>
+        <v>75671</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20198,7 @@
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20262,17 +20252,17 @@
         <v>4421</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>7923</v>
+        <v>7924</v>
       </c>
       <c r="N347" s="3" t="n">
         <v>6316</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20319,14 +20309,14 @@
         <v>9474</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12631</v>
+        <v>12632</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20380,17 +20370,17 @@
         <v>9474</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19577</v>
+        <v>19579</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>18947</v>
+        <v>18949</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20433,12 +20423,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25263</v>
+        <v>25265</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20457,18 +20447,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>15821</v>
+        <v>15791</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17846</v>
+        <v>17885</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20489,20 +20479,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>17491</v>
+        <v>16976</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31579</v>
+        <v>31581</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20511,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>48861</v>
+        <v>48865</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20532,7 +20522,7 @@
         <v>10</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20553,20 +20543,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>43708</v>
+        <v>41760</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>47541</v>
+        <v>43707</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>75788</v>
+        <v>75795</v>
       </c>
       <c r="O352" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20585,7 +20575,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>116542</v>
+        <v>116552</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20596,7 +20586,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>116542</v>
+        <v>116552</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20619,12 +20609,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>205260</v>
+        <v>205277</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20675,7 +20665,7 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M354" s="3" t="n">
         <v>1416</v>
@@ -20688,7 +20678,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20707,7 +20697,7 @@
         </is>
       </c>
       <c r="D355" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
@@ -20718,7 +20708,7 @@
         <v>2</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
@@ -20739,20 +20729,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>18908</v>
+        <v>18909</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17684</v>
+        <v>17685</v>
       </c>
       <c r="O355" s="2" t="n">
         <v>87</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20761,7 @@
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -20782,7 +20772,7 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
@@ -20803,20 +20793,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55262</v>
+        <v>55267</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17684</v>
+        <v>17685</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>68</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20870,7 +20860,7 @@
         <v>483</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>15789</v>
+        <v>15791</v>
       </c>
       <c r="N357" s="3" t="n">
         <v>531</v>
@@ -20880,7 +20870,7 @@
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20931,7 +20921,7 @@
         </is>
       </c>
       <c r="L358" s="3" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M358" s="3" t="n">
         <v>767</v>
@@ -20944,7 +20934,7 @@
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -20992,7 +20982,7 @@
       <c r="O359" s="2" t="inlineStr"/>
       <c r="P359" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -21029,20 +21019,20 @@
       </c>
       <c r="K360" s="2" t="inlineStr"/>
       <c r="L360" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="M360" s="3" t="n">
-        <v>8842</v>
+        <v>8843</v>
       </c>
       <c r="N360" s="3" t="n">
-        <v>17684</v>
+        <v>17685</v>
       </c>
       <c r="O360" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P360" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21062,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>157.892678</v>
+        <v>157.90537</v>
       </c>
     </row>
     <row r="2">
@@ -21083,7 +21073,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Wed, 28 Oct 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Thu, 29 Oct 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21095,7 +21085,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -585,7 +585,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>4473</v>
+        <v>3410</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>96529</v>
+        <v>96515</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -736,12 +736,12 @@
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="n">
-        <v>25265</v>
+        <v>25261</v>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23686</v>
+        <v>23682</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23686</v>
+        <v>23682</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -794,12 +794,12 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>47372</v>
+        <v>47364</v>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85269</v>
+        <v>85256</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -904,20 +904,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>126324</v>
+        <v>126305</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>142115</v>
+        <v>142093</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>252649</v>
+        <v>252611</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -958,20 +958,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>355287</v>
+        <v>355234</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>355287</v>
+        <v>355234</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>710574</v>
+        <v>710467</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -990,18 +990,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5394</v>
+        <v>5545</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>36</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6001</v>
+        <v>5942</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5819</v>
+        <v>5764</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8685</v>
+        <v>8683</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1054,18 +1054,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>9547</v>
+        <v>10684</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8610</v>
+        <v>8690</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1086,20 +1086,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>9732</v>
+        <v>9746</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>149969</v>
+        <v>149946</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17370</v>
+        <v>17367</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1118,18 +1118,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13896</v>
+        <v>13894</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14106</v>
+        <v>14095</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1150,20 +1150,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13896</v>
+        <v>17425</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42396</v>
+        <v>42390</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34739</v>
+        <v>34734</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1204,20 +1204,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>17280</v>
+        <v>17277</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39476</v>
+        <v>39470</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22107</v>
+        <v>22103</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1258,20 +1258,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>93826</v>
+        <v>93812</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>93826</v>
+        <v>93812</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22107</v>
+        <v>22103</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1312,20 +1312,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>189486</v>
+        <v>189458</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1366,20 +1366,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>29149</v>
+        <v>29145</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>63969</v>
+        <v>63959</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5369</v>
+        <v>5368</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1420,20 +1420,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22503</v>
+        <v>22500</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>63969</v>
+        <v>63959</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5369</v>
+        <v>5368</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1579</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         <v>1579</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>227398</v>
+        <v>227364</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3158</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
         <v>3158</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>268439</v>
+        <v>268399</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1636,20 +1636,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5685</v>
+        <v>5684</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22107</v>
+        <v>22103</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11369</v>
+        <v>11367</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1690,20 +1690,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11053</v>
+        <v>11052</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36902</v>
+        <v>36897</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22107</v>
+        <v>22103</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1744,20 +1744,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21317</v>
+        <v>21314</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>139383</v>
+        <v>139362</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1798,20 +1798,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39476</v>
+        <v>39470</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>321078</v>
+        <v>321030</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>78953</v>
+        <v>78941</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1863,20 +1863,20 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1939</v>
+        <v>1932</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1968</v>
+        <v>2070</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>316</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
         <v>1263</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>7895</v>
+        <v>7894</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>2526</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2045,20 +2045,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1290</v>
+        <v>1269</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1574860</v>
+        <v>1574623</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1579</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2081,14 +2081,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1806</v>
+        <v>1797</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
         <v>1579</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3158</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2176,17 +2176,17 @@
         <v>3158</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17013</v>
+        <v>17010</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
         <v>632</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1263</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2269,18 +2269,18 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11519</v>
+        <v>11517</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4737</v>
+        <v>4736</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>960</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>631621</v>
+        <v>631526</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1579</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2397,18 +2397,18 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2152</v>
+        <v>2217</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2032</v>
+        <v>2055</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2429,20 +2429,20 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2410</v>
+        <v>2717</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12792</v>
+        <v>12790</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3158</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2461,15 +2461,15 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3540</v>
+        <v>3494</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>3455</v>
@@ -2493,20 +2493,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3589</v>
+        <v>3361</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21107</v>
+        <v>21104</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2525,18 +2525,18 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6634</v>
+        <v>6600</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30522</v>
+        <v>30517</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6270</v>
+        <v>6269</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1579</v>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>2444</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>3158</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2709,18 +2709,18 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3158</v>
+        <v>3423</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3158</v>
+        <v>3184</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2737,20 +2737,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3689</v>
+        <v>5684</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>315811</v>
+        <v>315763</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
         <v>1579</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>144558</v>
+        <v>144536</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3158</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2868,17 +2868,17 @@
         <v>4455</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17371</v>
+        <v>17369</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>14</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2929,20 +2929,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15107</v>
+        <v>15105</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2961,18 +2961,18 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3869</v>
+        <v>3579</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3176</v>
+        <v>3276</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2989,20 +2989,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>3580</v>
+        <v>3584</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6116</v>
+        <v>6115</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>2211</v>
+        <v>3936</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>5863</v>
+        <v>5862</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>4</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6526</v>
+        <v>6525</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6589</v>
+        <v>6588</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8874</v>
+        <v>8873</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>6785</v>
+        <v>6784</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3081,18 +3081,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9144</v>
+        <v>10202</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9582</v>
+        <v>9527</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3109,20 +3109,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9129</v>
+        <v>9257</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>13750</v>
+        <v>13748</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10280</v>
+        <v>10270</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3176,17 +3176,17 @@
         <v>1579</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8705</v>
+        <v>8704</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3158</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3230,17 +3230,17 @@
         <v>3158</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3284,17 @@
         <v>772</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>5865</v>
+        <v>5864</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
         <v>3158</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>3158</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -3459,20 +3459,20 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>4140</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O50" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3519,10 +3519,10 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>4357</v>
+        <v>4356</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4357</v>
+        <v>4356</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1579</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3569,10 +3569,10 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6790</v>
+        <v>6789</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>3158</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -3633,20 +3633,20 @@
         </is>
       </c>
       <c r="L53" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4815</v>
+        <v>4814</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>1895</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11276</v>
+        <v>11274</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1579</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30544</v>
+        <v>30539</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3158</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>2</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>5913</v>
+        <v>5912</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3815,20 +3815,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>7796</v>
+        <v>7795</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>7818</v>
+        <v>7817</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>6615</v>
+        <v>6315</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3847,18 +3847,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9593</v>
+        <v>13592</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9529</v>
+        <v>9654</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3879,20 +3879,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>10057</v>
+        <v>13644</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30583</v>
+        <v>30579</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3911,18 +3911,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3788</v>
+        <v>3532</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3644</v>
+        <v>3578</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3943,20 +3943,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3168</v>
+        <v>3800</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10308</v>
+        <v>10307</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4076</v>
+        <v>3993</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2646</v>
+        <v>2716</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4007,20 +4007,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>2721</v>
+        <v>1950</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11290</v>
+        <v>11289</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>3076</v>
+        <v>3199</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4070,11 +4070,11 @@
         <v>2842</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4115,20 +4115,20 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4171,12 +4171,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9790</v>
+        <v>9789</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4217,20 +4217,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4273,12 +4273,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4321,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4367,20 +4367,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50530</v>
+        <v>50522</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4421,20 +4421,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22107</v>
+        <v>22103</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22107</v>
+        <v>22103</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4631,20 +4631,20 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>5021</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4688,17 @@
         <v>2526</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1481219</v>
+        <v>1480996</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11369</v>
+        <v>11367</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4739,20 +4739,20 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4745</v>
+        <v>4744</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7464</v>
+        <v>7463</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4793,20 +4793,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8685</v>
+        <v>8683</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20921</v>
+        <v>20918</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17370</v>
+        <v>17367</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4847,20 +4847,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17370</v>
+        <v>17367</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27005</v>
+        <v>27001</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
         <v>300</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6364</v>
+        <v>6363</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>1236</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
         <v>535</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5178</v>
+        <v>5177</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>632</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5685</v>
+        <v>5684</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5685</v>
+        <v>5684</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>2526</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5123,12 +5123,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5169,20 +5169,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23095</v>
+        <v>23092</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23095</v>
+        <v>23092</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10106</v>
+        <v>10104</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5225,12 +5225,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20212</v>
+        <v>20209</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>31695</v>
+        <v>31690</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>5</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>6488</v>
+        <v>6487</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5280,17 +5280,17 @@
         <v>240</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1578896</v>
+        <v>1578658</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>17562</v>
+        <v>17560</v>
       </c>
       <c r="O83" s="2" t="n">
         <v>355</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5337,10 +5337,10 @@
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="3" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34518</v>
+        <v>34513</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1579</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
         <v>1579</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>3158</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5457,20 +5457,20 @@
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="n">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10106</v>
+        <v>10104</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5553,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14211</v>
+        <v>14209</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5597,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17370</v>
+        <v>17367</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5652,17 +5652,17 @@
         <v>292</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>85818</v>
+        <v>85805</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O90" s="2" t="n">
         <v>59</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5699,10 +5699,10 @@
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5249</v>
+        <v>5248</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1579</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
         <v>3870</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4737</v>
+        <v>4736</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>3158</v>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5805,14 +5805,14 @@
         <v>2727</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O93" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10106</v>
+        <v>10104</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5895,12 +5895,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14211</v>
+        <v>14209</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17370</v>
+        <v>17367</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>1</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -6049,20 +6049,20 @@
         </is>
       </c>
       <c r="L98" s="3" t="n">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6113,20 +6113,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>5168</v>
+        <v>5167</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5168</v>
+        <v>5167</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9790</v>
+        <v>9789</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6167,20 +6167,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6223,12 +6223,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6269,20 +6269,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>17940</v>
+        <v>17937</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>17940</v>
+        <v>17937</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50530</v>
+        <v>50522</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6485,12 +6485,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9790</v>
+        <v>9789</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6581,12 +6581,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6677,12 +6677,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50530</v>
+        <v>50522</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6725,12 +6725,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>78953</v>
+        <v>78941</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6771,20 +6771,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>86848</v>
+        <v>86835</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>96944</v>
+        <v>96930</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>110534</v>
+        <v>110517</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>110534</v>
+        <v>110517</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>2</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>110534</v>
+        <v>110517</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -6835,20 +6835,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>110534</v>
+        <v>110517</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>110534</v>
+        <v>110517</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>142115</v>
+        <v>142093</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6889,20 +6889,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>126324</v>
+        <v>126305</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>126324</v>
+        <v>126305</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6943,20 +6943,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>189486</v>
+        <v>189458</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>213172</v>
+        <v>213140</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>3</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>213172</v>
+        <v>213140</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -7007,20 +7007,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>213172</v>
+        <v>213140</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>252649</v>
+        <v>252611</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>252649</v>
+        <v>252611</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7064,17 +7064,17 @@
         <v>1683</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O117" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7115,20 +7115,20 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>5839</v>
+        <v>5838</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7171,12 +7171,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>7895</v>
+        <v>7894</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7217,20 +7217,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14211</v>
+        <v>14209</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14211</v>
+        <v>14209</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7273,12 +7273,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22738</v>
+        <v>22735</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7319,20 +7319,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>40995</v>
+        <v>40989</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7437,20 +7437,20 @@
         </is>
       </c>
       <c r="L124" s="3" t="n">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O124" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7491,20 +7491,20 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>5670</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7548,17 +7548,17 @@
         <v>5730</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6449</v>
+        <v>6448</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>7895</v>
+        <v>7894</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7599,20 +7599,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11863</v>
+        <v>11862</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14211</v>
+        <v>14209</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22738</v>
+        <v>22735</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7703,12 +7703,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7756,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7797,20 +7797,20 @@
         </is>
       </c>
       <c r="L131" s="3" t="n">
-        <v>4914</v>
+        <v>4913</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>4914</v>
+        <v>4913</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O131" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7851,20 +7851,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>10706</v>
+        <v>10704</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7905,20 +7905,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15877</v>
+        <v>15875</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7961,12 +7961,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28423</v>
+        <v>28419</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8007,20 +8007,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21317</v>
+        <v>21314</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21317</v>
+        <v>21314</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47372</v>
+        <v>47364</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8061,20 +8061,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28423</v>
+        <v>28419</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28423</v>
+        <v>28419</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71057</v>
+        <v>71047</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8115,20 +8115,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8147,18 +8147,18 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8179,20 +8179,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12722</v>
+        <v>12721</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>1</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -8243,20 +8243,20 @@
         </is>
       </c>
       <c r="L139" s="3" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="M139" s="3" t="n">
         <v>1822</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>1167</v>
+        <v>316</v>
       </c>
       <c r="O139" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
         <v>758</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5156</v>
+        <v>5155</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>316</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8428,7 @@
         <v>1579</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>13463</v>
+        <v>13461</v>
       </c>
       <c r="N142" s="3" t="n">
         <v>316</v>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="L143" s="3" t="n">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>3158</v>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8546,17 +8546,17 @@
         <v>3314</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10719</v>
+        <v>10717</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="O144" s="2" t="n">
         <v>48</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8599,12 +8599,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4737</v>
+        <v>4736</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8648,17 +8648,17 @@
         <v>4421</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53400</v>
+        <v>53392</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8701,12 +8701,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8747,20 +8747,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17303</v>
+        <v>17301</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8803,12 +8803,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25265</v>
+        <v>25261</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8827,18 +8827,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8859,20 +8859,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39476</v>
+        <v>39470</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8923,20 +8923,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>63112</v>
+        <v>63102</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>75795</v>
+        <v>75783</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8976,21 +8976,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L152" s="3" t="n">
-        <v>102638</v>
-      </c>
-      <c r="M152" s="3" t="n">
-        <v>102638</v>
-      </c>
+      <c r="L152" s="3" t="inlineStr"/>
+      <c r="M152" s="3" t="inlineStr"/>
       <c r="N152" s="3" t="n">
-        <v>205277</v>
-      </c>
-      <c r="O152" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>205246</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr"/>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9038,7 @@
         <v>158</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10330</v>
+        <v>10329</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>316</v>
@@ -9054,7 +9048,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9112,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9131,7 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
@@ -9148,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -9165,10 +9159,10 @@
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1579</v>
@@ -9178,7 +9172,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9212,7 @@
         <v>1579</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="N156" s="3" t="n">
         <v>3158</v>
@@ -9228,7 +9222,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9268,17 +9262,17 @@
         <v>3158</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9319,10 +9313,10 @@
         </is>
       </c>
       <c r="L158" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1579</v>
@@ -9332,7 +9326,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9376,17 +9370,17 @@
         <v>1579</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19149</v>
+        <v>19146</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3158</v>
       </c>
       <c r="O159" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9430,17 +9424,17 @@
         <v>3158</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6605</v>
+        <v>6604</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9498,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9555,10 +9549,10 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>2061</v>
+        <v>2146</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30128</v>
+        <v>30124</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>2119</v>
@@ -9568,7 +9562,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9587,7 +9581,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -9598,7 +9592,7 @@
         <v>5</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -9619,20 +9613,20 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3213</v>
+        <v>3821</v>
       </c>
       <c r="O163" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9651,18 +9645,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3834</v>
+        <v>3890</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3658</v>
+        <v>3665</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9683,20 +9677,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3877</v>
+        <v>4140</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>10264</v>
+        <v>10262</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9744,7 @@
         <v>292</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>4903</v>
+        <v>4902</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>316</v>
@@ -9760,7 +9754,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9808,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9838,7 @@
         <v>4</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -9865,20 +9859,20 @@
         </is>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9705</v>
+        <v>9703</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1263</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9932,7 +9926,7 @@
         <v>1579</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5385</v>
+        <v>5384</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>1737</v>
@@ -9942,7 +9936,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9980,7 @@
         <v>534</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>316</v>
@@ -9996,7 +9990,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10009,7 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>94743</v>
+        <v>94729</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>94743</v>
+        <v>94729</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -10047,20 +10041,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>94743</v>
+        <v>94729</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>94743</v>
+        <v>94729</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>126324</v>
+        <v>126305</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10103,12 +10097,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10145,20 +10139,20 @@
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O172" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10201,14 +10195,14 @@
         <v>3363</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10247,12 +10241,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>7895</v>
+        <v>7894</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10289,20 +10283,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14181</v>
+        <v>14179</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14211</v>
+        <v>14209</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10339,20 +10333,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11369</v>
+        <v>11367</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11369</v>
+        <v>11367</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22738</v>
+        <v>22735</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10389,20 +10383,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>27215</v>
+        <v>27211</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10439,20 +10433,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19107</v>
+        <v>19104</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10494,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10541,20 +10535,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10597,12 +10591,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10643,20 +10637,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10693,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28423</v>
+        <v>28419</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10745,20 +10739,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21317</v>
+        <v>21314</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21317</v>
+        <v>21314</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42634</v>
+        <v>42628</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10799,20 +10793,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28423</v>
+        <v>28419</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28423</v>
+        <v>28419</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56846</v>
+        <v>56837</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10850,7 @@
         <v>158</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>316</v>
@@ -10866,7 +10860,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10904,7 @@
         <v>158</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>316</v>
@@ -10920,7 +10914,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10968,7 @@
         <v>158</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>102736</v>
+        <v>102721</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>316</v>
@@ -10984,7 +10978,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11026,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11076,17 +11070,17 @@
         <v>158</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29124</v>
+        <v>29120</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11124,7 @@
         <v>158</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>155905</v>
+        <v>155881</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>316</v>
@@ -11140,7 +11134,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11178,7 @@
         <v>158</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>316</v>
@@ -11194,7 +11188,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11236,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11290,7 @@
         <v>158</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>316</v>
@@ -11306,7 +11300,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11344,7 @@
         <v>158</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>316</v>
@@ -11360,7 +11354,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11373,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>21265</v>
+        <v>21262</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -11390,7 +11384,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>21265</v>
+        <v>21262</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -11414,7 +11408,7 @@
         <v>158</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>316</v>
@@ -11424,7 +11418,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11466,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11496,7 @@
         <v>3</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -11526,7 +11520,7 @@
         <v>976</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>963</v>
@@ -11536,7 +11530,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11577,20 +11571,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11644,17 +11638,17 @@
         <v>4421</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6296</v>
+        <v>6295</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11695,20 +11689,20 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10758</v>
+        <v>10756</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7579</v>
+        <v>7578</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11749,20 +11743,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10333</v>
+        <v>10332</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10106</v>
+        <v>10104</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11803,20 +11797,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8211</v>
+        <v>8210</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>275655</v>
+        <v>275614</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>13896</v>
+        <v>13894</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11857,20 +11851,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15603</v>
+        <v>15600</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16015</v>
+        <v>16012</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11911,20 +11905,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20212</v>
+        <v>20209</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>48712</v>
+        <v>48705</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -11967,12 +11961,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22738</v>
+        <v>22735</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12030,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12084,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12137,14 +12131,14 @@
         <v>2997</v>
       </c>
       <c r="N209" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O209" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12185,20 +12179,20 @@
         </is>
       </c>
       <c r="L210" s="3" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4464</v>
+        <v>4463</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12239,20 +12233,20 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>7895</v>
+        <v>7894</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>7895</v>
+        <v>7894</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12293,20 +12287,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14211</v>
+        <v>14209</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12349,12 +12343,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22738</v>
+        <v>22735</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12395,20 +12389,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12455,14 +12449,14 @@
         <v>2727</v>
       </c>
       <c r="N215" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O215" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12503,20 +12497,20 @@
         </is>
       </c>
       <c r="L216" s="3" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11857</v>
+        <v>11855</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="O216" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12557,20 +12551,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15547</v>
+        <v>15545</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>29298</v>
+        <v>29293</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25265</v>
+        <v>25261</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12611,20 +12605,20 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>4856</v>
+        <v>4855</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>4868</v>
+        <v>4867</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>7895</v>
+        <v>7894</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12643,7 +12637,7 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
@@ -12654,7 +12648,7 @@
         <v>1</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -12675,20 +12669,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7106</v>
+        <v>7105</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14211</v>
+        <v>14209</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12731,12 +12725,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12777,20 +12771,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>18957</v>
+        <v>18954</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12809,7 +12803,7 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
@@ -12820,7 +12814,7 @@
         <v>2</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -12841,7 +12835,7 @@
         </is>
       </c>
       <c r="L222" s="3" t="n">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="M222" s="3" t="n">
         <v>2836</v>
@@ -12854,7 +12848,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12898,7 +12892,7 @@
         <v>1579</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="N223" s="3" t="n">
         <v>3158</v>
@@ -12908,7 +12902,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -12952,17 +12946,17 @@
         <v>3158</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7186</v>
+        <v>7185</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13006,7 +13000,7 @@
         <v>1543</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>7696</v>
+        <v>7695</v>
       </c>
       <c r="N225" s="3" t="n">
         <v>1579</v>
@@ -13016,7 +13010,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13064,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13121,20 +13115,20 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13178,7 +13172,7 @@
         <v>158</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>316</v>
@@ -13188,7 +13182,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13226,7 @@
         <v>158</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>316</v>
@@ -13242,7 +13236,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13261,18 +13255,18 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>44634</v>
+        <v>21126</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>44634</v>
+        <v>32876</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -13296,17 +13290,17 @@
         <v>158</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N230" s="3" t="n">
-        <v>316</v>
+        <v>23239</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13347,10 +13341,10 @@
         </is>
       </c>
       <c r="L231" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1579</v>
@@ -13360,7 +13354,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13418,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13468,17 +13462,17 @@
         <v>3158</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7194</v>
+        <v>7193</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O233" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13526,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13567,7 @@
         </is>
       </c>
       <c r="L235" s="3" t="n">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="M235" s="3" t="n">
         <v>3930</v>
@@ -13586,7 +13580,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13627,20 +13621,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6512</v>
+        <v>6511</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13683,12 +13677,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4737</v>
+        <v>4736</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13729,20 +13723,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8821</v>
+        <v>8819</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11008</v>
+        <v>11006</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13785,12 +13779,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13833,12 +13827,12 @@
       <c r="L240" s="3" t="inlineStr"/>
       <c r="M240" s="3" t="inlineStr"/>
       <c r="N240" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13851,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>22475</v>
+        <v>22471</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -13868,7 +13862,7 @@
         <v>8</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>20270</v>
+        <v>20267</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -13889,20 +13883,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>22195</v>
+        <v>22192</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30593</v>
+        <v>30588</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13921,7 +13915,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>37899</v>
+        <v>37893</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -13932,7 +13926,7 @@
         <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>39912</v>
+        <v>39906</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -13953,20 +13947,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>56541</v>
+        <v>56533</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58507</v>
+        <v>58498</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>75795</v>
+        <v>75783</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13979,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -13996,7 +13990,7 @@
         <v>10</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>18664</v>
+        <v>18661</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14013,20 +14007,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>17962</v>
+        <v>17945</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31581074</v>
+        <v>31576320</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14069,12 +14063,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25265</v>
+        <v>25261</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14128,7 +14122,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14147,7 +14141,7 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
@@ -14179,20 +14173,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="O246" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14233,20 +14227,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15506</v>
+        <v>15504</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23282</v>
+        <v>23278</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17685</v>
+        <v>17683</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14289,12 +14283,12 @@
       <c r="L248" s="3" t="inlineStr"/>
       <c r="M248" s="3" t="inlineStr"/>
       <c r="N248" s="3" t="n">
-        <v>17685</v>
+        <v>17683</v>
       </c>
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14331,10 +14325,10 @@
       </c>
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9271</v>
+        <v>9269</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1579</v>
@@ -14344,7 +14338,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14394,7 +14388,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14438,7 +14432,7 @@
         <v>158</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97098</v>
+        <v>97083</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>316</v>
@@ -14448,7 +14442,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14499,20 +14493,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50315</v>
+        <v>50307</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50315</v>
+        <v>50307</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14525,7 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
@@ -14542,7 +14536,7 @@
         <v>2</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -14563,20 +14557,20 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>8497</v>
+        <v>8496</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>8497</v>
+        <v>8496</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>7579</v>
+        <v>7578</v>
       </c>
       <c r="O253" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14619,12 +14613,12 @@
       <c r="L254" s="3" t="inlineStr"/>
       <c r="M254" s="3" t="inlineStr"/>
       <c r="N254" s="3" t="n">
-        <v>10106</v>
+        <v>10104</v>
       </c>
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14668,7 +14662,7 @@
         <v>947</v>
       </c>
       <c r="M255" s="3" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="N255" s="3" t="n">
         <v>316</v>
@@ -14678,7 +14672,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14726,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14776,7 +14770,7 @@
         <v>291</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>7895</v>
+        <v>7894</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>316</v>
@@ -14786,7 +14780,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14813,10 +14807,10 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -14840,17 +14834,17 @@
         <v>316</v>
       </c>
       <c r="M258" s="3" t="n">
-        <v>15786</v>
+        <v>15783</v>
       </c>
       <c r="N258" s="3" t="n">
         <v>632</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14898,7 @@
         <v>973</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21354</v>
+        <v>21350</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1579</v>
@@ -14914,7 +14908,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14955,10 +14949,10 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2132</v>
+        <v>1932</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="N260" s="3" t="n">
         <v>3158</v>
@@ -14968,7 +14962,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15022,17 +15016,17 @@
         <v>3158</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7005</v>
+        <v>7004</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15045,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -15062,7 +15056,7 @@
         <v>9</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15083,20 +15077,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12632</v>
+        <v>13772</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15115,7 +15109,7 @@
         </is>
       </c>
       <c r="D263" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
@@ -15126,7 +15120,7 @@
         <v>1</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -15147,10 +15141,10 @@
         </is>
       </c>
       <c r="L263" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10545</v>
+        <v>10543</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1579</v>
@@ -15160,7 +15154,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15204,7 +15198,7 @@
         <v>1579</v>
       </c>
       <c r="M264" s="3" t="n">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="N264" s="3" t="n">
         <v>3158</v>
@@ -15214,7 +15208,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15257,12 +15251,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15275,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15289,10 +15283,10 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15313,20 +15307,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6780</v>
+        <v>6779</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9623</v>
+        <v>9621</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15339,7 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -15380,7 +15374,7 @@
         <v>2735</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19421</v>
+        <v>19418</v>
       </c>
       <c r="N267" s="3" t="n">
         <v>632</v>
@@ -15390,7 +15384,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15403,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8211</v>
+        <v>8210</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15420,7 +15414,7 @@
         <v>1</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8211</v>
+        <v>8210</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15441,20 +15435,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>12604</v>
+        <v>12602</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14224</v>
+        <v>14222</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>13896</v>
+        <v>13894</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15497,12 +15491,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15545,12 +15539,12 @@
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
       <c r="N270" s="3" t="n">
-        <v>25265</v>
+        <v>25261</v>
       </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15563,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>28423</v>
+        <v>28419</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15580,7 +15574,7 @@
         <v>3</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>23843</v>
+        <v>23840</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15601,20 +15595,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24283</v>
+        <v>24279</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>24283</v>
+        <v>24279</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15652,7 @@
         <v>158</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>316</v>
@@ -15668,7 +15662,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15687,7 +15681,7 @@
         </is>
       </c>
       <c r="D273" s="3" t="n">
-        <v>14998</v>
+        <v>14996</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -15698,7 +15692,7 @@
         <v>1</v>
       </c>
       <c r="G273" s="3" t="n">
-        <v>14998</v>
+        <v>14996</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -15722,17 +15716,17 @@
         <v>158</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>20913</v>
+        <v>20910</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O273" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15776,17 +15770,17 @@
         <v>158</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31685</v>
+        <v>31681</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15840,7 +15834,7 @@
         <v>158</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15869</v>
+        <v>15867</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>316</v>
@@ -15850,7 +15844,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15894,17 +15888,17 @@
         <v>158</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>157430</v>
+        <v>157406</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15917,7 @@
         </is>
       </c>
       <c r="D277" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -15934,7 +15928,7 @@
         <v>1</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -15951,7 +15945,7 @@
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="3" t="n">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M277" s="3" t="n">
         <v>2108</v>
@@ -15964,7 +15958,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16008,17 +16002,17 @@
         <v>4421</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>6989</v>
+        <v>6988</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16059,20 +16053,20 @@
         </is>
       </c>
       <c r="L279" s="3" t="n">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9880</v>
+        <v>9879</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7579</v>
+        <v>7578</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16113,20 +16107,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8593</v>
+        <v>8592</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10106</v>
+        <v>10104</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16169,12 +16163,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>13896</v>
+        <v>13894</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16217,12 +16211,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16265,12 +16259,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25265</v>
+        <v>25261</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16311,20 +16305,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>20212</v>
+        <v>20209</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33669</v>
+        <v>33664</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16343,18 +16337,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>12266</v>
+        <v>12114</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9549</v>
+        <v>9740</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16375,20 +16369,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>12268</v>
+        <v>12261</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>12021</v>
+        <v>12165</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16452,7 +16446,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16465,7 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5277</v>
+        <v>5276</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
@@ -16479,10 +16473,10 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5329</v>
+        <v>5406</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16499,20 +16493,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5280</v>
+        <v>5065</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>6201</v>
+        <v>6200</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>6245</v>
+        <v>6244</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16531,18 +16525,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>7600</v>
+        <v>7627</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
         <v>34</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6699</v>
+        <v>6700</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16559,20 +16553,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7628</v>
+        <v>7671</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>7816</v>
+        <v>7815</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7838</v>
+        <v>8041</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16591,18 +16585,18 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9027</v>
+        <v>9236</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9962</v>
+        <v>9744</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16619,20 +16613,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9192</v>
+        <v>11181</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11655</v>
+        <v>11653</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>9814</v>
+        <v>9871</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16683,7 +16677,7 @@
         </is>
       </c>
       <c r="L290" s="3" t="n">
-        <v>1658</v>
+        <v>1460</v>
       </c>
       <c r="M290" s="3" t="n">
         <v>3158</v>
@@ -16696,7 +16690,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16750,7 +16744,7 @@
         <v>3505</v>
       </c>
       <c r="M291" s="3" t="n">
-        <v>4895</v>
+        <v>4894</v>
       </c>
       <c r="N291" s="3" t="n">
         <v>3158</v>
@@ -16760,7 +16754,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16790,7 +16784,7 @@
         <v>3</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4440</v>
+        <v>4439</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -16811,20 +16805,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>5369</v>
+        <v>5368</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>6796</v>
+        <v>6795</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O292" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16878,7 +16872,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16891,7 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>6228</v>
+        <v>6227</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -16908,7 +16902,7 @@
         <v>23</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>7523</v>
+        <v>7522</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -16929,20 +16923,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>9695</v>
+        <v>7593</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>12754</v>
+        <v>12752</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>8067</v>
+        <v>8066</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -16983,20 +16977,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>50744</v>
+        <v>50737</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>697533</v>
+        <v>697428</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39476</v>
+        <v>39470</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17015,18 +17009,18 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17047,20 +17041,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>68656</v>
+        <v>68645</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39476</v>
+        <v>39470</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17079,7 +17073,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63162</v>
+        <v>63153</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17090,7 +17084,7 @@
         <v>5</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63162</v>
+        <v>63153</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17111,20 +17105,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63162</v>
+        <v>63153</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>126324</v>
+        <v>126305</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>78953</v>
+        <v>78941</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17137,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>126324</v>
+        <v>126305</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17154,7 +17148,7 @@
         <v>4</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>126324</v>
+        <v>126305</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17175,20 +17169,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>126324</v>
+        <v>126305</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>126327</v>
+        <v>126308</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>157905</v>
+        <v>157882</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17207,7 +17201,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>252649</v>
+        <v>252611</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17218,7 +17212,7 @@
         <v>3</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>252649</v>
+        <v>252611</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17239,20 +17233,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>252649</v>
+        <v>252611</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>252650</v>
+        <v>252612</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>315811</v>
+        <v>315763</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17265,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>442135</v>
+        <v>442068</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17282,7 +17276,7 @@
         <v>5</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>442135</v>
+        <v>442068</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17303,20 +17297,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>442135</v>
+        <v>442068</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>846719</v>
+        <v>846591</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>631621</v>
+        <v>631526</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17335,7 +17329,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>1841</v>
+        <v>2043</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -17343,10 +17337,10 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>2531</v>
+        <v>2539</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17367,20 +17361,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2534</v>
+        <v>2507</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17399,18 +17393,18 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>1164</v>
+        <v>2232</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1936</v>
+        <v>1965</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17431,20 +17425,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>2233</v>
+        <v>2209</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>14515</v>
+        <v>14512</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17463,7 +17457,7 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>5290</v>
+        <v>5289</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -17474,7 +17468,7 @@
         <v>18</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4631</v>
+        <v>4630</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17495,20 +17489,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>5290</v>
+        <v>5289</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>5524</v>
+        <v>5523</v>
       </c>
       <c r="O303" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17559,20 +17553,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="O304" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17636,7 +17630,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17684,7 @@
         <v>158</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>316</v>
@@ -17700,7 +17694,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17754,7 +17748,7 @@
         <v>919</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>316</v>
@@ -17764,7 +17758,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17783,7 +17777,7 @@
         </is>
       </c>
       <c r="D308" s="3" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
@@ -17794,7 +17788,7 @@
         <v>4</v>
       </c>
       <c r="G308" s="3" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
@@ -17815,20 +17809,20 @@
         </is>
       </c>
       <c r="L308" s="3" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1263243</v>
+        <v>1263053</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="O308" s="2" t="n">
         <v>225</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17882,17 +17876,17 @@
         <v>4421</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>31928</v>
+        <v>31924</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O309" s="2" t="n">
         <v>121</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17915,14 +17909,14 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G310" s="3" t="n">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
@@ -17946,17 +17940,17 @@
         <v>1579</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>6016</v>
+        <v>6015</v>
       </c>
       <c r="N310" s="3" t="n">
         <v>3158</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -17997,20 +17991,20 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>5154</v>
+        <v>5153</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>6026</v>
+        <v>6025</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4737</v>
+        <v>4736</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18053,12 +18047,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18071,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18088,7 +18082,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18109,20 +18103,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26108</v>
+        <v>26104</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>41</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18163,20 +18157,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15448</v>
+        <v>15446</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15448</v>
+        <v>15446</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25265</v>
+        <v>25261</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18195,18 +18189,18 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18227,20 +18221,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1579054</v>
+        <v>1578816</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18253,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18270,7 +18264,7 @@
         <v>9</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18291,20 +18285,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>37897</v>
+        <v>37892</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>75795</v>
+        <v>75783</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18323,7 +18317,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>102638</v>
+        <v>102623</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18334,7 +18328,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>102638</v>
+        <v>102623</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18355,20 +18349,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>102638</v>
+        <v>102623</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>102638</v>
+        <v>102623</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>205277</v>
+        <v>205246</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18425,14 +18419,14 @@
         <v>2048</v>
       </c>
       <c r="N318" s="3" t="n">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="O318" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18486,17 +18480,17 @@
         <v>1391</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15683</v>
+        <v>15681</v>
       </c>
       <c r="N319" s="3" t="n">
-        <v>1530</v>
+        <v>316</v>
       </c>
       <c r="O319" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18526,7 +18520,7 @@
         <v>10</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18550,17 +18544,17 @@
         <v>1105</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9811</v>
+        <v>9809</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18573,7 @@
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
@@ -18611,10 +18605,10 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>8255</v>
+        <v>8254</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>3848</v>
@@ -18624,7 +18618,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18675,7 +18669,7 @@
         </is>
       </c>
       <c r="L322" s="3" t="n">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="M322" s="3" t="n">
         <v>1034</v>
@@ -18688,7 +18682,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18707,7 +18701,7 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>4499</v>
+        <v>4498</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -18718,7 +18712,7 @@
         <v>5</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18742,17 +18736,17 @@
         <v>1944</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18806,7 +18800,7 @@
         <v>507</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5584</v>
+        <v>5583</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>316</v>
@@ -18816,7 +18810,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18835,18 +18829,18 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>3158</v>
+        <v>3058</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>3062</v>
+        <v>3085</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -18867,20 +18861,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>3059</v>
+        <v>3074</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15683</v>
+        <v>15681</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>3596</v>
+        <v>3576</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18899,7 +18893,7 @@
         </is>
       </c>
       <c r="D326" s="3" t="n">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
@@ -18934,7 +18928,7 @@
         <v>2149</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N326" s="3" t="n">
         <v>2785</v>
@@ -18944,7 +18938,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -18974,7 +18968,7 @@
         <v>6</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -18995,20 +18989,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O327" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19027,7 +19021,7 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>24261</v>
+        <v>24257</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
@@ -19035,10 +19029,10 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>25065</v>
+        <v>25460</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19059,20 +19053,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>23700</v>
+        <v>22320</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>30506</v>
+        <v>30501</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>27716</v>
+        <v>27332</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19091,18 +19085,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7848</v>
+        <v>8210</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
         <v>43</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7435</v>
+        <v>7504</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19123,20 +19117,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>8254</v>
+        <v>7810</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9752</v>
+        <v>9751</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8560</v>
+        <v>8603</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19155,7 +19149,7 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>6506</v>
+        <v>6505</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -19163,10 +19157,10 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5862</v>
+        <v>5879</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19187,20 +19181,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6694</v>
+        <v>6691</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8641</v>
+        <v>8639</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>7024</v>
+        <v>7042</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19219,7 +19213,7 @@
         </is>
       </c>
       <c r="D331" s="3" t="n">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -19264,7 +19258,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19283,18 +19277,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>1557</v>
+        <v>1574</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19318,17 +19312,17 @@
         <v>1571</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1693</v>
+        <v>1708</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19355,10 +19349,10 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19382,17 +19376,17 @@
         <v>234</v>
       </c>
       <c r="M333" s="3" t="n">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N333" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19422,7 +19416,7 @@
         <v>6</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19446,7 +19440,7 @@
         <v>485</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9405</v>
+        <v>9403</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>426</v>
@@ -19456,7 +19450,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19469,7 @@
         </is>
       </c>
       <c r="D335" s="3" t="n">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
@@ -19510,17 +19504,17 @@
         <v>2296</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O335" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19571,20 +19565,20 @@
         </is>
       </c>
       <c r="L336" s="3" t="n">
-        <v>387</v>
+        <v>317</v>
       </c>
       <c r="M336" s="3" t="n">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N336" s="3" t="n">
         <v>594</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19611,10 +19605,10 @@
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19638,17 +19632,17 @@
         <v>183</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15461</v>
+        <v>15458</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>316</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19708,11 +19702,11 @@
         <v>316</v>
       </c>
       <c r="O338" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19770,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19840,7 +19834,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19859,18 +19853,18 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>1533</v>
+        <v>1653</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>1460</v>
+        <v>1471</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -19891,20 +19885,20 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>1533</v>
+        <v>1366</v>
       </c>
       <c r="M341" s="3" t="n">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>1937</v>
+        <v>1893</v>
       </c>
       <c r="O341" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19958,7 +19952,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -19977,7 +19971,7 @@
         </is>
       </c>
       <c r="D343" s="3" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
@@ -20012,7 +20006,7 @@
         <v>532</v>
       </c>
       <c r="M343" s="3" t="n">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="N343" s="3" t="n">
         <v>516</v>
@@ -20022,7 +20016,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20041,18 +20035,18 @@
         </is>
       </c>
       <c r="D344" s="3" t="n">
-        <v>2144</v>
+        <v>1746</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>2099</v>
+        <v>2060</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20073,20 +20067,20 @@
         </is>
       </c>
       <c r="L344" s="3" t="n">
-        <v>1746</v>
+        <v>2836</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57598</v>
+        <v>57589</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3158</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20116,7 +20110,7 @@
         <v>19</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
@@ -20137,20 +20131,20 @@
         </is>
       </c>
       <c r="L345" s="3" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>75671</v>
+        <v>75660</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20193,12 +20187,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4737</v>
+        <v>4736</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20252,17 +20246,17 @@
         <v>4421</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>7924</v>
+        <v>7922</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6316</v>
+        <v>6315</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20303,20 +20297,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12632</v>
+        <v>12631</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20335,7 +20329,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20343,10 +20337,10 @@
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20367,20 +20361,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9474</v>
+        <v>9473</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19579</v>
+        <v>19576</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>18949</v>
+        <v>18946</v>
       </c>
       <c r="O349" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20423,12 +20417,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25265</v>
+        <v>25261</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20447,18 +20441,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>15791</v>
+        <v>16956</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17885</v>
+        <v>17948</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20479,20 +20473,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>16976</v>
+        <v>15788</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31581</v>
+        <v>31576</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20511,18 +20505,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>48865</v>
+        <v>42726</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>46077</v>
+        <v>45766</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20543,20 +20537,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>41760</v>
+        <v>37892</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>43707</v>
+        <v>48634</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>75795</v>
+        <v>75783</v>
       </c>
       <c r="O352" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20575,7 +20569,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>116552</v>
+        <v>116534</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20586,7 +20580,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>116552</v>
+        <v>116534</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20609,12 +20603,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>205277</v>
+        <v>205246</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20665,7 +20659,7 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M354" s="3" t="n">
         <v>1416</v>
@@ -20678,7 +20672,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20691,7 @@
         </is>
       </c>
       <c r="D355" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
@@ -20708,7 +20702,7 @@
         <v>2</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
@@ -20729,20 +20723,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>18909</v>
+        <v>18906</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17685</v>
+        <v>17683</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20761,7 +20755,7 @@
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -20772,7 +20766,7 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
@@ -20793,20 +20787,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55267</v>
+        <v>55259</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17685</v>
+        <v>17683</v>
       </c>
       <c r="O356" s="2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20825,18 +20819,18 @@
         </is>
       </c>
       <c r="D357" s="3" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G357" s="3" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
@@ -20857,20 +20851,20 @@
         </is>
       </c>
       <c r="L357" s="3" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>15791</v>
+        <v>15788</v>
       </c>
       <c r="N357" s="3" t="n">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20928,7 @@
       </c>
       <c r="P358" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -20982,7 +20976,7 @@
       <c r="O359" s="2" t="inlineStr"/>
       <c r="P359" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -21019,20 +21013,20 @@
       </c>
       <c r="K360" s="2" t="inlineStr"/>
       <c r="L360" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="M360" s="3" t="n">
-        <v>8843</v>
+        <v>8841</v>
       </c>
       <c r="N360" s="3" t="n">
-        <v>17685</v>
+        <v>17683</v>
       </c>
       <c r="O360" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P360" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -21062,7 +21056,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>157.90537</v>
+        <v>157.881601</v>
       </c>
     </row>
     <row r="2">
@@ -21073,7 +21067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Thu, 29 Oct 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Fri, 30 Oct 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21085,7 +21079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
